--- a/Figure_Plot/figure_plot_4_a_b/source_data/dsfunction_May2025_exact_V5_k20.xlsx
+++ b/Figure_Plot/figure_plot_4_a_b/source_data/dsfunction_May2025_exact_V5_k20.xlsx
@@ -455,7 +455,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[[0.060170960951030736,33.55936901291673,-1860.0,1.0,1.0,4.0,-1.0],[33.55936901291673,34.67600894798226,-1187.2576,0.0,1.0,5.0,-1.0],[34.67600894798226,38.58424872071159,0.0,0.0,0.0,6.0,-1.0],[38.58424872071159,55.333847746694445,788.5,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[0.060170960951030736,33.55936901291673,-1860.0,1.0,1.0,4.0,-1.0],[33.55936901291673,34.67600894798226,-1187.2576,0.0,1.0,5.0,-1.0],[34.67600894798226,38.58424872071159,0.0,0.0,0.0,6.0,-1.0],[38.58424872071159,55.333847746694445,788.5001,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[[0.06465534703439174,33.23411054699684,-1860.0,1.0,1.0,1.0,-1.0],[33.23411054699684,37.30755241365889,0.0,0.0,0.0,3.0,-1.0],[37.30755241365889,57.67476174696917,788.5,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[0.06465534703439174,33.23411054699684,-1860.0,1.0,1.0,1.0,-1.0],[33.23411054699684,37.30755241365889,0.0,0.0,0.0,3.0,-1.0],[37.30755241365889,40.79907401365494,788.5,0.0,0.0,0.0,-1.0],[40.79907401365494,57.67476174696917,788.5001,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -481,7 +481,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[[0.06616840205486296,32.800398540187444,-1860.0,1.0,1.0,2.0,-1.0],[32.800398540187444,33.395566360880764,-1187.2576,0.0,1.0,1.0,-1.0],[33.395566360880764,36.96657328504068,0.0,0.0,0.0,2.0,-1.0],[36.96657328504068,58.987782650693504,788.5,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[0.06616840205486296,32.800398540187444,-1860.0,1.0,1.0,2.0,-1.0],[32.800398540187444,33.395566360880764,-1187.2576,0.0,1.0,1.0,-1.0],[33.395566360880764,36.96657328504068,0.0,0.0,0.0,2.0,-1.0],[36.96657328504068,37.561741105734,788.5,0.0,0.0,0.0,-1.0],[37.561741105734,58.987782650693504,788.5001,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -494,7 +494,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[[0.0670736637155955,33.99047647618151,-1860.0,1.0,1.0,1.0,-1.0],[33.99047647618151,38.08468026389292,0.0,0.0,0.0,1.0,-1.0],[38.08468026389292,57.9708129470626,788.5,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[0.0670736637155955,33.99047647618151,-1860.0,1.0,1.0,1.0,-1.0],[33.99047647618151,38.08468026389292,0.0,0.0,0.0,1.0,-1.0],[38.08468026389292,42.17888405160432,788.5,0.0,0.0,0.0,-1.0],[42.17888405160432,57.9708129470626,788.5001,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -507,7 +507,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[[0.06497865084935292,33.03424703297528,-1860.0,1.0,1.0,0.0,-1.0],[33.03424703297528,36.817605699776614,0.0,0.0,0.0,2.0,-1.0],[36.817605699776614,53.57247979561111,788.5,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[0.06497865084935292,33.03424703297528,-1860.0,1.0,1.0,0.0,-1.0],[33.03424703297528,36.817605699776614,0.0,0.0,0.0,2.0,-1.0],[36.817605699776614,40.600964366577955,788.5,0.0,0.0,0.0,-1.0],[40.600964366577955,53.57247979561111,788.5001,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -572,7 +572,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[[0.06779395822912662,19.75227599612784,-1860.0,8.0,0.0,0.0,1.0],[19.75227599612784,30.489266198618044,-733.6842,8.0,0.0,0.0,1.0],[30.489266198618044,34.068262932781444,0.0,8.0,8.0,1.0,-1.0],[34.068262932781444,36.454260755557044,227.85,8.0,8.0,0.0,-1.0],[36.454260755557044,59.12124007192525,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[0.06779395822912662,19.75227599612784,-1860.0,8.0,0.0,0.0,1.0],[19.75227599612784,30.489266198618044,-733.6842,8.0,0.0,0.0,1.0],[30.489266198618044,34.068262932781444,0.0,8.0,8.0,1.0,-1.0],[34.068262932781444,36.454260755557044,227.85,8.0,8.0,0.0,-1.0],[36.454260755557044,59.12124007192525,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -598,7 +598,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[0.06653263779102629,20.630675151460323,-1860.0,6.0,0.0,0.0,1.0],[20.630675151460323,31.190640226047257,-733.6842,6.0,0.0,0.0,1.0],[31.190640226047257,34.52536603907471,0.0,6.0,8.0,1.0,-1.0],[34.52536603907471,36.192728945588435,227.85,6.0,8.0,0.0,-1.0],[36.192728945588435,55.08950855274401,1860.0,6.0,8.0,0.0,-1.0]]</t>
+          <t>[[0.06653263779102629,20.630675151460323,-1860.0,5.0,0.0,0.0,1.0],[20.630675151460323,31.190640226047257,-733.6842,5.0,0.0,0.0,1.0],[31.190640226047257,34.52536603907471,0.0,5.0,8.0,1.0,-1.0],[34.52536603907471,36.192728945588435,227.85,5.0,8.0,0.0,-1.0],[36.192728945588435,55.08950855274401,1860.0,6.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -611,7 +611,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[[0.06338621875704924,20.490649315513156,-1860.0,5.0,0.0,0.0,1.0],[20.490649315513156,32.16337108508807,-733.6842,5.0,0.0,0.0,1.0],[32.16337108508807,35.66518761596055,0.0,5.0,8.0,1.0,-1.0],[35.66518761596055,36.83245979291804,227.85,5.0,8.0,0.0,-1.0],[36.83245979291804,57.84335897815289,1860.0,5.0,8.0,0.0,-1.0]]</t>
+          <t>[[0.06338621875704924,20.490649315513156,-1860.0,4.0,0.0,0.0,1.0],[20.490649315513156,32.16337108508807,-733.6842,4.0,0.0,0.0,1.0],[32.16337108508807,35.66518761596055,0.0,4.0,8.0,1.0,-1.0],[35.66518761596055,36.83245979291804,227.85,4.0,8.0,0.0,-1.0],[36.83245979291804,57.84335897815289,1860.0,5.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -624,7 +624,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[[0.06528634851762935,20.146638897019525,-1860.0,4.0,0.0,0.0,1.0],[20.146638897019525,30.47419163624907,-733.6842,4.0,0.0,0.0,1.0],[30.47419163624907,33.916709215992256,0.0,4.0,8.0,3.0,-1.0],[33.916709215992256,36.21172093582105,227.85,4.0,8.0,0.0,-1.0],[36.21172093582105,56.86682641428014,1860.0,4.0,8.0,0.0,-1.0]]</t>
+          <t>[[0.06528634851762935,20.146638897019525,-1860.0,3.0,0.0,0.0,1.0],[20.146638897019525,30.47419163624907,-733.6842,3.0,0.0,0.0,1.0],[30.47419163624907,33.916709215992256,0.0,3.0,8.0,3.0,-1.0],[33.916709215992256,36.21172093582105,227.85,3.0,8.0,0.0,-1.0],[36.21172093582105,56.86682641428014,1860.0,3.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -637,7 +637,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[[1.8166138653001007,30.920474953362262,-1860.0,4.0,8.0,0.0,-1.0],[30.920474953362262,32.01873386234574,-1607.5346,3.0,8.0,0.0,-1.0],[32.01873386234574,35.86264004378791,0.0,3.0,7.0,1.0,-1.0],[35.86264004378791,36.41176949827965,409.2,3.0,7.0,0.0,-1.0],[36.41176949827965,56.18042985998225,1860.0,3.0,7.0,0.0,-1.0]]</t>
+          <t>[[1.8166138653001007,30.920474953362262,-1860.0,3.0,8.0,0.0,-1.0],[30.920474953362262,32.01873386234574,-1607.5346,2.0,8.0,0.0,-1.0],[32.01873386234574,35.86264004378791,0.0,2.0,7.0,1.0,-1.0],[35.86264004378791,36.41176949827965,409.2,2.0,7.0,0.0,-1.0],[36.41176949827965,56.18042985998225,1860.0,2.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -650,7 +650,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[[1.7155904815176586,31.762469445016727,-1860.0,3.0,8.0,0.0,-1.0],[31.762469445016727,33.4632361787997,-1607.5346,2.0,8.0,0.0,-1.0],[33.4632361787997,36.86476964636562,0.0,2.0,7.0,1.0,-1.0],[36.86476964636562,37.43169189095995,409.2,2.0,7.0,1.0,-1.0],[37.43169189095995,57.840892696355546,1860.0,2.0,7.0,1.0,-1.0]]</t>
+          <t>[[1.7155904815176586,31.762469445016727,-1860.0,3.0,8.0,0.0,-1.0],[31.762469445016727,33.4632361787997,-1607.5346,2.0,8.0,0.0,-1.0],[33.4632361787997,36.86476964636562,0.0,1.0,7.0,1.0,-1.0],[36.86476964636562,37.43169189095995,409.2,2.0,7.0,1.0,-1.0],[37.43169189095995,57.840892696355546,1860.0,1.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[[1.9317174431021071,32.937582659746525,-1860.0,2.0,8.0,0.0,-1.0],[32.937582659746525,36.32004068338047,0.0,1.0,7.0,1.0,-1.0],[36.32004068338047,36.88378368731946,409.2,1.0,7.0,1.0,-1.0],[36.88378368731946,57.74227483306207,1860.0,1.0,7.0,1.0,-1.0]]</t>
+          <t>[[1.9317174431021071,32.937582659746525,-1860.0,1.0,8.0,0.0,-1.0],[32.937582659746525,36.32004068338047,0.0,1.0,7.0,1.0,-1.0],[36.32004068338047,36.88378368731946,409.2,1.0,7.0,1.0,-1.0],[36.88378368731946,57.74227483306207,1860.0,1.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -689,7 +689,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[[-1.9424211562153533,28.423180474808113,-733.6842,0.0,0.0,0.0,1.0],[28.423180474808113,31.400200242555513,0.0,0.0,8.0,3.0,-1.0],[31.400200242555513,35.56802791740187,227.85,0.0,8.0,0.0,-1.0],[35.56802791740187,57.00257024518314,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-1.9424211562153533,28.423180474808113,-733.6843,0.0,0.0,0.0,1.0],[28.423180474808113,31.400200242555513,0.0,0.0,8.0,3.0,-1.0],[31.400200242555513,35.56802791740187,227.85,0.0,8.0,0.0,-1.0],[35.56802791740187,57.00257024518314,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -702,7 +702,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[[-2.012018185287039,28.64544107970071,-733.6842,0.0,0.0,0.0,1.0],[28.64544107970071,31.94701361593016,0.0,0.0,8.0,2.0,-1.0],[31.94701361593016,32.41866683539151,227.85,0.0,8.0,1.0,-1.0],[32.41866683539151,44.68165054138661,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[-2.012018185287039,28.64544107970071,-733.6843,0.0,0.0,0.0,1.0],[28.64544107970071,31.94701361593016,0.0,0.0,8.0,2.0,-1.0],[31.94701361593016,32.41866683539151,227.85,0.0,8.0,1.0,-1.0],[32.41866683539151,44.68165054138661,1860.0,0.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -793,7 +793,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[[-1.8995333109743828,27.960678930205635,-1860.0,1.0,2.0,0.0,-1.0],[27.960678930205635,28.38725339079392,-1808.4765,0.0,2.0,1.0,-1.0],[28.38725339079392,31.37327461491192,0.0,0.0,1.0,2.0,-1.0],[31.37327461491192,32.2264235360885,227.85,0.0,1.0,1.0,-1.0],[32.2264235360885,40.33133828726593,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[-1.8995333109743828,27.960678930205635,-1860.0,0.0,2.0,0.0,-1.0],[27.960678930205635,28.38725339079392,-1808.4765,0.0,2.0,1.0,-1.0],[28.38725339079392,31.37327461491192,0.0,0.0,1.0,2.0,-1.0],[31.37327461491192,32.2264235360885,227.85,0.0,1.0,1.0,-1.0],[32.2264235360885,40.33133828726593,1860.0,0.0,1.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -819,7 +819,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[[-1.908971127352784,25.94695106833728,-1860.0,1.0,1.0,0.0,-1.0],[25.94695106833728,27.936659796600857,-1808.4765,0.0,1.0,0.0,-1.0],[27.936659796600857,31.120193761822577,0.0,0.0,0.0,1.0,-1.0],[31.120193761822577,37.487261692266024,227.85,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-1.908971127352784,25.94695106833728,-1860.0,1.0,1.0,0.0,-1.0],[25.94695106833728,27.936659796600857,-1808.4765,0.0,1.0,0.0,-1.0],[27.936659796600857,31.120193761822577,0.0,0.0,0.0,1.0,-1.0],[31.120193761822577,34.70166947269701,227.85,0.0,0.0,0.0,-1.0],[34.70166947269701,37.487261692266024,227.8501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -884,7 +884,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[[-1.988261951986372,10.563100188026741,-1860.0,8.0,0.0,0.0,1.0],[10.563100188026741,28.377936773851808,-733.6842,8.0,0.0,0.0,1.0],[28.377936773851808,31.616997971274543,0.0,8.0,8.0,4.0,-1.0],[31.616997971274543,38.09512036612002,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-1.988261951986372,10.563100188026741,-1860.0,6.0,0.0,0.0,1.0],[10.563100188026741,28.377936773851808,-733.6842,7.0,0.0,0.0,1.0],[28.377936773851808,31.616997971274543,0.0,6.0,8.0,4.0,-1.0],[31.616997971274543,38.09512036612002,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -897,7 +897,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[[-2.1054115346025535,28.216056015357637,-1860.0,8.0,0.0,0.0,1.0],[28.216056015357637,31.163976471603767,0.0,7.0,7.0,3.0,-1.0],[31.163976471603767,31.585107965353217,1071.35,7.0,7.0,0.0,-1.0],[31.585107965353217,39.58660634659271,1860.0,7.0,7.0,0.0,-1.0]]</t>
+          <t>[[-2.1054115346025535,28.216056015357637,-1860.0,7.0,0.0,0.0,1.0],[28.216056015357637,31.163976471603767,0.0,6.0,7.0,3.0,-1.0],[31.163976471603767,31.585107965353217,1071.35,7.0,7.0,0.0,-1.0],[31.585107965353217,39.58660634659271,1860.0,7.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -910,7 +910,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[[-2.0111242358530035,28.172706093507696,-1860.0,7.0,0.0,0.0,1.0],[28.172706093507696,31.34995139133514,0.0,6.0,7.0,4.0,-1.0],[31.34995139133514,37.30728632476159,1860.0,6.0,7.0,1.0,-1.0]]</t>
+          <t>[[-2.0111242358530035,28.172706093507696,-1860.0,6.0,0.0,0.0,1.0],[28.172706093507696,31.34995139133514,0.0,5.0,7.0,4.0,-1.0],[31.34995139133514,37.30728632476159,1860.0,6.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -923,7 +923,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[[-2.018065211083488,27.27166340726742,-1860.0,6.0,0.0,0.0,1.0],[27.27166340726742,28.45908483774111,-873.8504,5.0,8.0,3.0,-1.0],[28.45908483774111,31.625541985670935,0.0,5.0,7.0,4.0,-1.0],[31.625541985670935,32.41715627265339,1071.35,5.0,7.0,4.0,-1.0],[32.41715627265339,37.166841994548136,1860.0,5.0,8.0,3.0,-1.0]]</t>
+          <t>[[-2.018065211083488,27.27166340726742,-1860.0,5.0,0.0,0.0,1.0],[27.27166340726742,28.45908483774111,-873.8504,4.0,8.0,3.0,-1.0],[28.45908483774111,31.625541985670935,0.0,4.0,7.0,4.0,-1.0],[31.625541985670935,32.41715627265339,1071.35,5.0,7.0,4.0,-1.0],[32.41715627265339,37.166841994548136,1860.0,4.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -936,7 +936,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[[-2.0098448650053102,28.070507245416543,-1860.0,5.0,0.0,0.0,1.0],[28.070507245416543,28.906072581817153,-873.8504,4.0,8.0,3.0,-1.0],[28.906072581817153,31.830551259219273,0.0,4.0,7.0,4.0,-1.0],[31.830551259219273,32.24833392741957,1071.35,4.0,7.0,4.0,-1.0],[32.24833392741957,39.35063928682474,1860.0,4.0,7.0,4.0,-1.0]]</t>
+          <t>[[-2.0098448650053102,28.070507245416543,-1860.0,4.0,0.0,0.0,1.0],[28.070507245416543,28.906072581817153,-873.8504,3.0,8.0,3.0,-1.0],[28.906072581817153,31.830551259219273,0.0,3.0,7.0,4.0,-1.0],[31.830551259219273,32.24833392741957,1071.35,3.0,7.0,4.0,-1.0],[32.24833392741957,39.35063928682474,1860.0,2.0,7.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[[-1.9825007850115588,27.619586495747388,-1860.0,4.0,0.0,0.0,1.0],[27.619586495747388,28.430602585631195,-873.8504,3.0,8.0,4.0,-1.0],[28.430602585631195,31.269158900224518,0.0,3.0,7.0,5.0,-1.0],[31.269158900224518,38.162795664236874,1860.0,3.0,7.0,2.0,-1.0]]</t>
+          <t>[[-1.9825007850115588,27.619586495747388,-1860.0,3.0,0.0,0.0,1.0],[27.619586495747388,28.430602585631195,-873.8504,2.0,8.0,4.0,-1.0],[28.430602585631195,31.269158900224518,0.0,2.0,7.0,5.0,-1.0],[31.269158900224518,38.162795664236874,1860.0,2.0,7.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[[-2.012203340280024,27.527594329197264,-1860.0,2.0,0.0,0.0,1.0],[27.527594329197264,28.348144264460522,-873.8504,1.0,8.0,3.0,-1.0],[28.348144264460522,31.630344005513557,0.0,1.0,7.0,4.0,-1.0],[31.630344005513557,38.60501845525125,1860.0,1.0,7.0,4.0,-1.0]]</t>
+          <t>[[-2.012203340280024,27.527594329197264,-1860.0,1.0,0.0,0.0,1.0],[27.527594329197264,28.348144264460522,-873.8504,1.0,8.0,3.0,-1.0],[28.348144264460522,31.630344005513557,0.0,1.0,7.0,4.0,-1.0],[31.630344005513557,38.60501845525125,1860.0,1.0,7.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[[8.810626718004732,30.5894160099191,-0.0,0.0,0.0,1.0,1.0],[30.5894160099191,31.460567581595676,890.0,0.0,8.0,3.0,-1.0],[31.460567581595676,37.558628583331696,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[8.810626718004732,30.5894160099191,0.0,0.0,0.0,1.0,1.0],[30.5894160099191,31.460567581595676,890.0,0.0,8.0,3.0,-1.0],[31.460567581595676,37.558628583331696,1860.0,0.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[[9.00210244527421,27.343315870579815,-1860.0,1.0,8.0,1.0,-1.0],[27.343315870579815,27.93496791655742,-1074.7923,0.0,8.0,2.0,-1.0],[27.93496791655742,30.893228146445416,0.0,0.0,7.0,3.0,-1.0],[30.893228146445416,31.189054169434222,890.0,0.0,7.0,3.0,-1.0],[31.189054169434222,38.288878721165425,1860.0,0.0,7.0,3.0,-1.0]]</t>
+          <t>[[9.00210244527421,27.343315870579815,-1860.0,0.0,8.0,1.0,-1.0],[27.343315870579815,27.93496791655742,-1074.7923,0.0,8.0,2.0,-1.0],[27.93496791655742,30.893228146445416,0.0,0.0,7.0,3.0,-1.0],[30.893228146445416,31.189054169434222,890.0,0.0,7.0,3.0,-1.0],[31.189054169434222,38.288878721165425,1860.0,0.0,7.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[[9.000932317558064,27.535632913147765,-1860.0,1.0,6.0,1.0,-1.0],[27.535632913147765,30.855280781014578,-0.0,0.0,5.0,3.0,-1.0],[30.855280781014578,36.38802722745927,1860.0,0.0,5.0,2.0,-1.0]]</t>
+          <t>[[9.000932317558064,27.535632913147765,-1860.0,1.0,6.0,1.0,-1.0],[27.535632913147765,30.855280781014578,0.0,0.0,5.0,3.0,-1.0],[30.855280781014578,36.38802722745927,1860.0,0.0,5.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[[9.123094998532288,27.032695158751824,-1860.0,1.0,5.0,1.0,-1.0],[27.032695158751824,30.719965779973496,-0.0,0.0,4.0,3.0,-1.0],[30.719965779973496,35.19736582002838,1860.0,0.0,4.0,3.0,-1.0]]</t>
+          <t>[[9.123094998532288,27.032695158751824,-1860.0,1.0,5.0,1.0,-1.0],[27.032695158751824,30.719965779973496,0.0,0.0,4.0,3.0,-1.0],[30.719965779973496,35.19736582002838,1860.0,0.0,4.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[[8.912042912743143,27.59932076443066,-1860.0,1.0,4.0,1.0,-1.0],[27.59932076443066,30.757733922462357,-0.0,0.0,3.0,3.0,-1.0],[30.757733922462357,34.96895146650461,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[8.912042912743143,27.59932076443066,-1860.0,0.0,4.0,1.0,-1.0],[27.59932076443066,30.757733922462357,0.0,0.0,3.0,3.0,-1.0],[30.757733922462357,34.96895146650461,1860.0,0.0,3.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[[9.097615965395647,27.415981424534454,-1860.0,1.0,3.0,1.0,-1.0],[27.415981424534454,31.48672930434308,-0.0,0.0,2.0,3.0,-1.0],[31.48672930434308,34.28536847171151,1860.0,0.0,3.0,3.0,-1.0]]</t>
+          <t>[[9.097615965395647,27.415981424534454,-1860.0,1.0,3.0,1.0,-1.0],[27.415981424534454,31.48672930434308,0.0,0.0,2.0,3.0,-1.0],[31.48672930434308,34.28536847171151,1860.0,0.0,3.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1105,11 +1105,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>[[8.817587694406777,27.848276135806955,-1860.0,1.0,2.0,0.0,-1.0],[27.848276135806955,31.497997206760417,-0.0,0.0,1.0,2.0,-1.0],[31.497997206760417,34.62632955329195,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[8.817587694406777,27.848276135806955,-1860.0,0.0,2.0,0.0,-1.0],[27.848276135806955,31.497997206760417,0.0,0.0,1.0,2.0,-1.0],[31.497997206760417,34.62632955329195,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>[[8.74419367151912,26.17242353912569,-1860.0,1.0,2.0,0.0,-1.0],[26.17242353912569,30.70853816220137,-0.0,0.0,1.0,1.0,-1.0],[30.70853816220137,32.37973828649241,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[8.74419367151912,26.17242353912569,-1860.0,0.0,2.0,0.0,-1.0],[26.17242353912569,30.70853816220137,0.0,0.0,1.0,1.0,-1.0],[30.70853816220137,32.37973828649241,1860.0,0.0,1.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>[[9.066043689600008,22.674963057544133,-1860.0,9.0,2.0,2.0,1.0],[22.674963057544133,23.567351212819155,-733.6842,9.0,2.0,2.0,1.0],[23.567351212819155,29.367874222106813,0.0,0.0,2.0,1.0,-1.0],[29.367874222106813,31.152650532656864,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[9.066043689600008,22.674963057544133,-1860.0,8.0,2.0,2.0,1.0],[22.674963057544133,23.567351212819155,-733.6842,9.0,2.0,2.0,1.0],[23.567351212819155,29.367874222106813,0.0,0.0,2.0,1.0,-1.0],[29.367874222106813,31.152650532656864,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[[9.171067817334693,23.91575175274224,-1860.0,10.0,1.0,1.0,1.0],[23.91575175274224,24.585964658897126,-733.6842,9.0,1.0,2.0,1.0],[24.585964658897126,27.266816283516683,0.0,0.0,1.0,1.0,-1.0],[27.266816283516683,28.830646397878084,0.0,0.0,0.0,1.0,-1.0],[28.830646397878084,31.28809372044601,1860.0,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[9.171067817334693,23.91575175274224,-1860.0,10.0,1.0,1.0,1.0],[23.91575175274224,24.585964658897126,-733.6842,9.0,1.0,2.0,1.0],[24.585964658897126,27.49022058556831,0.0,0.0,1.0,1.0,-1.0],[27.49022058556831,28.830646397878084,0.0,0.0,0.0,1.0,-1.0],[28.830646397878084,31.28809372044601,1860.0,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>[[9.041946005126093,20.28750270023145,-1860.0,9.0,0.0,0.0,1.0],[20.28750270023145,22.756039535742385,-733.6842,8.0,0.0,1.0,1.0],[22.756039535742385,25.224576371253317,0.0,8.0,0.0,1.0,1.0],[25.224576371253317,27.69311320676425,1016.5,9.0,0.0,0.0,1.0],[27.69311320676425,36.19585119574635,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[9.041946005126093,20.28750270023145,-1860.0,9.0,0.0,0.0,1.0],[20.28750270023145,22.756039535742385,-733.6842,8.0,0.0,1.0,1.0],[22.756039535742385,25.224576371253317,0.0,8.0,0.0,1.0,1.0],[25.224576371253317,27.69311320676425,1016.5,8.0,0.0,0.0,1.0],[27.69311320676425,36.19585119574635,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>[[8.856569223926636,26.629476736272274,-1860.0,9.0,0.0,0.0,1.0],[26.629476736272274,26.894744012575934,-1275.7341,10.0,10.0,2.0,-1.0],[26.894744012575934,29.812684051916264,0.0,10.0,10.0,2.0,-1.0],[29.812684051916264,30.077951328219932,527.3,11.0,10.0,1.0,-1.0],[30.077951328219932,35.11802957798959,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[8.856569223926636,26.629476736272274,-1860.0,8.0,0.0,0.0,1.0],[26.629476736272274,26.894744012575934,-1275.7341,10.0,10.0,2.0,-1.0],[26.894744012575934,29.812684051916264,0.0,10.0,10.0,2.0,-1.0],[29.812684051916264,30.077951328219932,527.3,10.0,10.0,1.0,-1.0],[30.077951328219932,35.11802957798959,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[[8.883721641699175,26.023060795421237,-1860.0,8.0,0.0,0.0,1.0],[26.023060795421237,26.308716447983272,-1074.7923,8.0,9.0,5.0,-1.0],[26.308716447983272,28.879617321041582,0.0,8.0,9.0,5.0,-1.0],[28.879617321041582,37.16363124534058,1860.0,9.0,9.0,4.0,-1.0]]</t>
+          <t>[[8.883721641699175,26.023060795421237,-1860.0,8.0,0.0,0.0,1.0],[26.023060795421237,26.308716447983272,-1074.7923,8.0,9.0,5.0,-1.0],[26.308716447983272,28.879617321041582,0.0,8.0,9.0,5.0,-1.0],[28.879617321041582,37.16363124534058,1860.0,8.0,9.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[[-5.818061373212677,25.915850407123074,-1860.0,7.0,0.0,0.0,1.0],[25.915850407123074,28.917706926884563,0.0,7.0,9.0,5.0,-1.0],[28.917706926884563,29.346543572564777,708.65,8.0,9.0,4.0,-1.0],[29.346543572564777,36.636766549128396,1860.0,8.0,9.0,4.0,-1.0]]</t>
+          <t>[[-5.818061373212677,25.915850407123074,-1860.0,6.0,0.0,0.0,1.0],[25.915850407123074,28.917706926884563,0.0,6.0,9.0,5.0,-1.0],[28.917706926884563,29.346543572564777,708.65,8.0,9.0,4.0,-1.0],[29.346543572564777,36.636766549128396,1860.0,8.0,9.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>[[-6.662870971355539,26.731532219809445,-1860.0,6.0,0.0,0.0,1.0],[26.731532219809445,29.439186532606605,0.0,6.0,8.0,6.0,-1.0],[29.439186532606605,29.890462251406134,890.0,6.0,8.0,5.0,-1.0],[29.890462251406134,38.013425189797616,1860.0,6.0,9.0,4.0,-1.0]]</t>
+          <t>[[-6.662870971355539,26.731532219809445,-1860.0,4.0,0.0,0.0,1.0],[26.731532219809445,29.439186532606605,0.0,5.0,8.0,6.0,-1.0],[29.439186532606605,29.890462251406134,890.0,5.0,8.0,5.0,-1.0],[29.890462251406134,38.013425189797616,1860.0,5.0,9.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>[[-6.50381465897646,26.412303512129107,-1860.0,5.0,0.0,0.0,1.0],[26.412303512129107,29.444051238415142,0.0,5.0,8.0,5.0,-1.0],[29.444051238415142,36.37376032706895,1860.0,5.0,8.0,5.0,-1.0]]</t>
+          <t>[[-6.50381465897646,26.412303512129107,-1860.0,4.0,0.0,0.0,1.0],[26.412303512129107,29.444051238415142,0.0,4.0,8.0,5.0,-1.0],[29.444051238415142,36.37376032706895,1860.0,4.0,8.0,5.0,-1.0]]</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>[[-7.334748459522696,25.94414888309117,-1860.0,4.0,0.0,0.0,1.0],[25.94414888309117,26.382029111283455,-1074.7923,4.0,9.0,5.0,-1.0],[26.382029111283455,29.009310480437183,0.0,4.0,8.0,6.0,-1.0],[29.009310480437183,30.32295116501405,890.0,4.0,8.0,6.0,-1.0],[30.32295116501405,36.015394131513794,1860.0,4.0,9.0,5.0,-1.0]]</t>
+          <t>[[-7.334748459522696,25.94414888309117,-1860.0,4.0,0.0,0.0,1.0],[25.94414888309117,26.382029111283455,-1074.7923,4.0,9.0,5.0,-1.0],[26.382029111283455,29.009310480437183,0.0,3.0,8.0,6.0,-1.0],[29.009310480437183,30.32295116501405,890.0,4.0,8.0,6.0,-1.0],[30.32295116501405,36.015394131513794,1860.0,3.0,9.0,5.0,-1.0]]</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>[[-7.005196674078064,25.867468543704604,-1860.0,3.0,0.0,0.0,1.0],[25.867468543704604,28.60685731185316,0.0,3.0,9.0,4.0,-1.0],[28.60685731185316,29.51998690123601,708.65,4.0,9.0,3.0,-1.0],[29.51998690123601,38.19471800037311,1860.0,4.0,9.0,3.0,-1.0]]</t>
+          <t>[[-7.005196674078064,25.867468543704604,-1860.0,2.0,0.0,0.0,1.0],[25.867468543704604,28.60685731185316,0.0,3.0,9.0,4.0,-1.0],[28.60685731185316,29.51998690123601,708.65,4.0,9.0,3.0,-1.0],[29.51998690123601,38.19471800037311,1860.0,4.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>[[-7.267607775967381,27.574744159808855,-0.0,0.0,0.0,1.0,1.0],[27.574744159808855,29.36153143856661,708.65,1.0,9.0,4.0,-1.0],[29.36153143856661,36.95537737328708,1860.0,1.0,10.0,3.0,-1.0]]</t>
+          <t>[[-7.267607775967381,27.574744159808855,0.0,0.0,0.0,1.0,1.0],[27.574744159808855,29.36153143856661,708.65,1.0,9.0,4.0,-1.0],[29.36153143856661,36.95537737328708,1860.0,1.0,10.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>[[-7.3821907424165625,25.733054553881573,-1860.0,2.0,9.0,2.0,-1.0],[25.733054553881573,26.18668805109114,-1275.7341,1.0,9.0,2.0,-1.0],[26.18668805109114,28.908489034348513,0.0,1.0,9.0,2.0,-1.0],[28.908489034348513,37.52752548133022,1860.0,2.0,9.0,1.0,-1.0]]</t>
+          <t>[[-7.3821907424165625,25.733054553881573,-1860.0,1.0,9.0,2.0,-1.0],[25.733054553881573,26.18668805109114,-1275.7341,1.0,9.0,2.0,-1.0],[26.18668805109114,28.908489034348513,0.0,1.0,9.0,2.0,-1.0],[28.908489034348513,37.52752548133022,1860.0,2.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>[[-6.608616881100971,26.200571197575094,-1860.0,2.0,7.0,1.0,-1.0],[26.200571197575094,26.713214761304407,-1476.6759,2.0,7.0,1.0,-1.0],[26.713214761304407,29.276432579950978,0.0,2.0,6.0,2.0,-1.0],[29.276432579950978,44.14309592810107,1860.0,2.0,6.0,2.0,-1.0]]</t>
+          <t>[[-6.608616881100971,26.200571197575094,-1860.0,2.0,7.0,1.0,-1.0],[26.200571197575094,26.713214761304407,-1476.6759,2.0,7.0,1.0,-1.0],[26.713214761304407,29.276432579950978,0.0,1.0,6.0,2.0,-1.0],[29.276432579950978,44.14309592810107,1860.0,2.0,6.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>[[-6.98926725343526,25.153675226563507,-1860.0,2.0,6.0,1.0,-1.0],[25.153675226563507,25.65590870281349,-1275.7341,1.0,6.0,2.0,-1.0],[25.65590870281349,28.669309560313373,0.0,1.0,5.0,3.0,-1.0],[28.669309560313373,29.17154303656335,708.65,1.0,5.0,3.0,-1.0],[29.17154303656335,42.73184689531283,1860.0,1.0,5.0,3.0,-1.0]]</t>
+          <t>[[-6.98926725343526,25.153675226563507,-1860.0,2.0,6.0,1.0,-1.0],[25.153675226563507,25.65590870281349,-1275.7341,1.0,6.0,2.0,-1.0],[25.65590870281349,28.669309560313373,0.0,1.0,5.0,3.0,-1.0],[28.669309560313373,29.17154303656335,708.65,0.0,5.0,3.0,-1.0],[29.17154303656335,42.73184689531283,1860.0,0.0,5.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>[[-7.282536128271969,25.780529853585662,-1860.0,2.0,5.0,1.0,-1.0],[25.780529853585662,28.880192289384816,0.0,1.0,4.0,3.0,-1.0],[28.880192289384816,29.39680269535134,708.65,1.0,4.0,2.0,-1.0],[29.39680269535134,43.86189406241405,1860.0,1.0,5.0,1.0,-1.0]]</t>
+          <t>[[-7.282536128271969,25.780529853585662,-1860.0,1.0,5.0,1.0,-1.0],[25.780529853585662,28.880192289384816,0.0,0.0,4.0,3.0,-1.0],[28.880192289384816,29.39680269535134,708.65,0.0,4.0,2.0,-1.0],[29.39680269535134,43.86189406241405,1860.0,1.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>[[-6.931448681315284,26.766024967401567,-1860.0,9.0,12.0,2.0,0.0],[26.766024967401567,27.787160532514203,-1275.7341,1.0,5.0,1.0,-1.0],[27.787160532514203,30.8505672278521,0.0,1.0,4.0,2.0,-1.0],[30.8505672278521,43.614761791759996,1860.0,1.0,4.0,2.0,-1.0]]</t>
+          <t>[[-6.931448681315284,26.766024967401567,-1860.0,8.0,12.0,2.0,0.0],[26.766024967401567,27.787160532514203,-1275.7341,0.0,5.0,1.0,-1.0],[27.787160532514203,30.8505672278521,0.0,0.0,4.0,2.0,-1.0],[30.8505672278521,43.614761791759996,1860.0,1.0,4.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>[[-7.031478070497841,25.3124637578032,-1860.0,8.0,1.0,1.0,1.0],[25.3124637578032,26.877493201108088,-1808.4765,8.0,1.0,1.0,1.0],[26.877493201108088,27.399169682209717,-1023.2687,9.0,10.0,4.0,0.0],[27.399169682209717,30.529228568819498,0.0,9.0,9.0,5.0,0.0],[30.529228568819498,44.6144935585635,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-7.031478070497841,25.3124637578032,-1860.0,7.0,1.0,1.0,1.0],[25.3124637578032,26.877493201108088,-1808.4765,8.0,1.0,1.0,1.0],[26.877493201108088,27.399169682209717,-1023.2687,9.0,10.0,4.0,0.0],[27.399169682209717,30.529228568819498,0.0,8.0,9.0,5.0,0.0],[30.529228568819498,44.6144935585635,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>[[-6.95385357622328,27.934473498843133,-1860.0,8.0,0.0,1.0,1.0],[27.934473498843133,28.45519479847099,-1808.4765,8.0,0.0,1.0,1.0],[28.45519479847099,31.579522596238135,0.0,8.0,0.0,1.0,1.0],[31.579522596238135,32.100243895865994,46.5,9.0,0.0,0.0,1.0],[32.100243895865994,44.59755508693456,708.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-6.95385357622328,27.934473498843133,-1860.0,8.0,0.0,1.0,1.0],[27.934473498843133,28.45519479847099,-1808.4765,8.0,0.0,1.0,1.0],[28.45519479847099,31.579522596238135,0.0,8.0,0.0,1.0,1.0],[31.579522596238135,32.100243895865994,46.5,9.0,0.0,0.0,1.0],[32.100243895865994,44.59755508693456,708.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>[[-6.973173071348222,28.30589884125289,-1860.0,8.0,0.0,0.0,1.0],[28.30589884125289,29.35900546550964,-1023.2687,9.0,9.0,4.0,-1.0],[29.35900546550964,32.51832533827989,0.0,9.0,9.0,4.0,-1.0],[32.51832533827989,45.155604829360875,708.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-6.973173071348222,28.30589884125289,-1860.0,8.0,0.0,0.0,1.0],[28.30589884125289,29.35900546550964,-1023.2687,9.0,9.0,4.0,-1.0],[29.35900546550964,32.51832533827989,0.0,9.0,9.0,4.0,-1.0],[32.51832533827989,45.155604829360875,708.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>[[-7.080457594970696,27.59013405290203,-1860.0,7.0,0.0,0.0,1.0],[27.59013405290203,29.600023423793203,-1808.4765,7.0,0.0,0.0,1.0],[29.600023423793203,30.102495766516,-1023.2687,8.0,9.0,4.0,-1.0],[30.102495766516,33.11732982285276,0.0,8.0,9.0,4.0,-1.0],[33.11732982285276,34.624746851021136,755.15,9.0,9.0,3.0,-1.0],[34.624746851021136,42.66430433458583,1860.0,9.0,9.0,3.0,-1.0]]</t>
+          <t>[[-7.080457594970696,27.59013405290203,-1860.0,6.0,0.0,0.0,1.0],[27.59013405290203,29.600023423793203,-1808.4765,7.0,0.0,0.0,1.0],[29.600023423793203,30.102495766516,-1023.2687,8.0,9.0,4.0,-1.0],[30.102495766516,33.11732982285276,0.0,8.0,9.0,4.0,-1.0],[33.11732982285276,34.624746851021136,755.15,9.0,9.0,3.0,-1.0],[34.624746851021136,42.66430433458583,1860.0,9.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>[[-7.080243864962062,27.00854689121286,-1860.0,6.0,0.0,0.0,1.0],[27.00854689121286,28.4694950664775,-1808.4765,6.0,0.0,0.0,1.0],[28.4694950664775,31.39139141700678,0.0,8.0,9.0,3.0,-1.0],[31.39139141700678,32.36535686718321,755.15,8.0,9.0,3.0,-1.0],[32.36535686718321,41.13104591877104,1860.0,8.0,9.0,3.0,-1.0]]</t>
+          <t>[[-7.080243864962062,27.00854689121286,-1860.0,6.0,0.0,0.0,1.0],[27.00854689121286,28.4694950664775,-1808.4765,5.0,0.0,0.0,1.0],[28.4694950664775,31.39139141700678,0.0,7.0,9.0,3.0,-1.0],[31.39139141700678,32.36535686718321,755.15,8.0,9.0,3.0,-1.0],[32.36535686718321,41.13104591877104,1860.0,7.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>[[-2.266535582554761,27.53854110422391,-1860.0,5.0,0.0,0.0,1.0],[27.53854110422391,29.372699669564135,-1808.4765,5.0,0.0,0.0,1.0],[29.372699669564135,29.831239310899193,-1023.2687,6.0,9.0,4.0,-1.0],[29.831239310899193,33.041016800244584,0.0,6.0,8.0,5.0,-1.0],[33.041016800244584,43.128888909615824,1860.0,6.0,9.0,4.0,-1.0]]</t>
+          <t>[[-2.266535582554761,27.53854110422391,-1860.0,4.0,0.0,0.0,1.0],[27.53854110422391,29.372699669564135,-1808.4765,4.0,0.0,0.0,1.0],[29.372699669564135,29.831239310899193,-1023.2687,5.0,9.0,4.0,-1.0],[29.831239310899193,33.041016800244584,0.0,5.0,8.0,5.0,-1.0],[33.041016800244584,43.128888909615824,1860.0,5.0,9.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>[[3.36619092463286,29.340287645617497,-1860.0,7.0,9.0,2.0,-1.0],[29.340287645617497,29.72796073100533,-1023.2687,6.0,9.0,3.0,-1.0],[29.72796073100533,32.82934541410797,0.0,6.0,9.0,3.0,-1.0],[32.82934541410797,33.99236467027146,755.15,7.0,9.0,2.0,-1.0],[33.99236467027146,41.74582637802807,1860.0,4.0,6.0,1.0,-1.0]]</t>
+          <t>[[3.36619092463286,29.340287645617497,-1860.0,6.0,9.0,2.0,-1.0],[29.340287645617497,29.72796073100533,-1023.2687,5.0,9.0,3.0,-1.0],[29.72796073100533,32.82934541410797,0.0,5.0,9.0,3.0,-1.0],[32.82934541410797,33.99236467027146,755.15,6.0,9.0,2.0,-1.0],[33.99236467027146,41.74582637802807,1860.0,3.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>[[6.098201703062192,29.545879098244402,-1860.0,5.0,9.0,3.0,-1.0],[29.545879098244402,30.30225578841157,-1023.2687,5.0,9.0,3.0,-1.0],[30.30225578841157,33.70595089416383,0.0,5.0,9.0,3.0,-1.0],[33.70595089416383,34.08413923924741,755.15,6.0,9.0,2.0,-1.0],[34.08413923924741,34.84051592941458,1299.2,3.0,6.0,1.0,-1.0],[34.84051592941458,43.538847866337015,1860.0,3.0,6.0,1.0,-1.0]]</t>
+          <t>[[6.098201703062192,29.545879098244402,-1860.0,4.0,9.0,3.0,-1.0],[29.545879098244402,30.30225578841157,-1023.2687,4.0,9.0,3.0,-1.0],[30.30225578841157,33.70595089416383,0.0,4.0,9.0,3.0,-1.0],[33.70595089416383,34.08413923924741,755.15,5.0,9.0,2.0,-1.0],[34.08413923924741,34.84051592941458,1299.2,2.0,6.0,1.0,-1.0],[34.84051592941458,43.538847866337015,1860.0,2.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>[[6.385288520844072,29.8579772501956,-1860.0,5.0,10.0,2.0,-1.0],[29.8579772501956,30.230559610978958,-1224.2105,5.0,10.0,2.0,-1.0],[30.230559610978958,33.58380085802918,0.0,5.0,10.0,2.0,-1.0],[33.58380085802918,34.70154794037925,1299.2,2.0,6.0,1.0,-1.0],[34.70154794037925,43.27094223839647,1860.0,2.0,6.0,1.0,-1.0]]</t>
+          <t>[[6.385288520844072,29.8579772501956,-1860.0,5.0,10.0,2.0,-1.0],[29.8579772501956,30.230559610978958,-1224.2105,4.0,10.0,2.0,-1.0],[30.230559610978958,33.58380085802918,0.0,4.0,10.0,2.0,-1.0],[33.58380085802918,34.70154794037925,1299.2,2.0,6.0,1.0,-1.0],[34.70154794037925,43.27094223839647,1860.0,2.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>[[6.398895967454417,29.52315472353404,-1860.0,4.0,9.0,3.0,-1.0],[29.52315472353404,30.574257394264933,-1023.2687,3.0,9.0,3.0,-1.0],[30.574257394264933,33.72756540645761,0.0,3.0,8.0,4.0,-1.0],[33.72756540645761,34.07793296336791,936.5,3.0,8.0,4.0,-1.0],[34.07793296336791,41.08528410157385,1860.0,3.0,9.0,3.0,-1.0]]</t>
+          <t>[[6.398895967454417,29.52315472353404,-1860.0,3.0,9.0,3.0,-1.0],[29.52315472353404,30.574257394264933,-1023.2687,2.0,9.0,3.0,-1.0],[30.574257394264933,33.72756540645761,0.0,3.0,8.0,4.0,-1.0],[33.72756540645761,34.07793296336791,936.5,2.0,8.0,4.0,-1.0],[34.07793296336791,41.08528410157385,1860.0,2.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>[[6.71034681312255,28.479060754392393,-1808.4765,0.0,0.0,0.0,1.0],[28.479060754392393,28.848022007634256,-1023.2687,1.0,9.0,3.0,-1.0],[28.848022007634256,32.168673286811014,0.0,1.0,9.0,3.0,-1.0],[32.168673286811014,34.013479553020325,755.15,2.0,9.0,2.0,-1.0],[34.013479553020325,43.237510884066864,1860.0,2.0,10.0,1.0,-1.0]]</t>
+          <t>[[6.71034681312255,28.479060754392393,-1808.4766,0.0,0.0,0.0,1.0],[28.479060754392393,28.848022007634256,-1023.2687,1.0,9.0,3.0,-1.0],[28.848022007634256,32.168673286811014,0.0,1.0,9.0,3.0,-1.0],[32.168673286811014,34.013479553020325,755.15,2.0,9.0,2.0,-1.0],[34.013479553020325,43.237510884066864,1860.0,2.0,10.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>[[6.187173382665312,28.758009927775554,-1808.4765,0.0,0.0,0.0,1.0],[28.758009927775554,29.48610142923072,-822.3269,0.0,8.0,4.0,-1.0],[29.48610142923072,32.398467435051394,0.0,0.0,8.0,4.0,-1.0],[32.398467435051394,42.22770270469618,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[6.187173382665312,28.758009927775554,-1808.4766,0.0,0.0,0.0,1.0],[28.758009927775554,29.48610142923072,-822.3269,0.0,8.0,4.0,-1.0],[29.48610142923072,32.398467435051394,0.0,0.0,8.0,4.0,-1.0],[32.398467435051394,42.22770270469618,1860.0,1.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>[[6.094123538194833,29.680539472691198,-1860.0,9.0,11.0,3.0,0.0],[29.680539472691198,30.134124394508436,-1607.5346,9.0,11.0,3.0,0.0],[30.134124394508436,34.21638869086358,-0.0,1.0,2.0,1.0,-1.0],[34.21638869086358,50.99903079810138,1860.0,1.0,3.0,1.0,-1.0]]</t>
+          <t>[[6.094123538194833,29.680539472691198,-1860.0,9.0,11.0,3.0,0.0],[29.680539472691198,30.134124394508436,-1607.5346,9.0,11.0,3.0,0.0],[30.134124394508436,34.21638869086358,0.0,1.0,2.0,1.0,-1.0],[34.21638869086358,50.99903079810138,1860.0,1.0,3.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>[[6.05963658236621,26.560727622221183,-1860.0,9.0,3.0,0.0,1.0],[26.560727622221183,28.51321248315975,-733.6842,8.0,3.0,1.0,1.0],[28.51321248315975,31.930060989802246,0.0,8.0,2.0,2.0,1.0],[31.930060989802246,32.90630342027153,1197.85,8.0,2.0,2.0,1.0],[32.90630342027153,54.38363689059579,1860.0,8.0,3.0,1.0,1.0]]</t>
+          <t>[[6.05963658236621,26.560727622221183,-1860.0,8.0,3.0,0.0,1.0],[26.560727622221183,28.51321248315975,-733.6842,8.0,3.0,1.0,1.0],[28.51321248315975,31.930060989802246,0.0,8.0,2.0,2.0,1.0],[31.930060989802246,32.90630342027153,1197.85,8.0,2.0,2.0,1.0],[32.90630342027153,54.38363689059579,1860.0,8.0,3.0,1.0,1.0]]</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>[[6.457575473822436,25.83903520552078,-1860.0,9.0,1.0,0.0,1.0],[25.83903520552078,27.879188861489027,-733.6842,8.0,1.0,1.0,1.0],[27.879188861489027,30.9394193454414,0.0,8.0,0.0,2.0,1.0],[30.9394193454414,31.95949617342552,1197.85,8.0,0.0,2.0,1.0],[31.95949617342552,56.951378459036555,1860.0,8.0,1.0,1.0,1.0]]</t>
+          <t>[[6.457575473822436,25.83903520552078,-1860.0,8.0,1.0,0.0,1.0],[25.83903520552078,27.879188861489027,-733.6842,8.0,1.0,1.0,1.0],[27.879188861489027,30.9394193454414,0.0,8.0,0.0,2.0,1.0],[30.9394193454414,31.95949617342552,1197.85,8.0,0.0,2.0,1.0],[31.95949617342552,56.951378459036555,1860.0,7.0,1.0,1.0,1.0]]</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>[[6.31652131096733,26.269679136685227,-1860.0,9.0,0.0,0.0,1.0],[26.269679136685227,28.702991066650824,-733.6842,8.0,0.0,1.0,1.0],[28.702991066650824,32.10962776860266,0.0,8.0,0.0,1.0,1.0],[32.10962776860266,39.40956355849945,1016.5,9.0,0.0,0.0,1.0],[39.40956355849945,54.49609752428615,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[6.31652131096733,26.269679136685227,-1860.0,8.0,0.0,0.0,1.0],[26.269679136685227,28.702991066650824,-733.6842,8.0,0.0,1.0,1.0],[28.702991066650824,32.10962776860266,0.0,7.0,0.0,1.0,1.0],[32.10962776860266,39.40956355849945,1016.5,9.0,0.0,0.0,1.0],[39.40956355849945,54.49609752428615,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>[[6.186252771594396,29.884053141634652,-1860.0,8.0,0.0,0.0,1.0],[29.884053141634652,31.742704151049576,-733.6842,8.0,0.0,0.0,1.0],[31.742704151049576,34.99534341752569,0.0,8.0,0.0,1.0,1.0],[34.99534341752569,40.106633693416725,1016.5,9.0,0.0,0.0,1.0],[40.106633693416725,52.18786525461372,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[6.186252771594396,29.884053141634652,-1860.0,7.0,0.0,0.0,1.0],[29.884053141634652,31.742704151049576,-733.6842,8.0,0.0,0.0,1.0],[31.742704151049576,34.99534341752569,0.0,7.0,0.0,1.0,1.0],[34.99534341752569,40.106633693416725,1016.5,9.0,0.0,0.0,1.0],[40.106633693416725,52.18786525461372,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>[[6.042334770243211,30.736623411644523,-1860.0,7.0,0.0,0.0,1.0],[30.736623411644523,34.53574474109087,-733.6842,7.0,0.0,0.0,1.0],[34.53574474109087,37.85997590435644,0.0,7.0,0.0,1.0,1.0],[37.85997590435644,40.709316901441206,1016.5,8.0,0.0,0.0,1.0],[40.709316901441206,53.056461222141856,1860.0,8.0,9.0,3.0,-1.0]]</t>
+          <t>[[6.042334770243211,30.736623411644523,-1860.0,6.0,0.0,0.0,1.0],[30.736623411644523,34.53574474109087,-733.6842,7.0,0.0,0.0,1.0],[34.53574474109087,37.85997590435644,0.0,6.0,0.0,1.0,1.0],[37.85997590435644,40.709316901441206,1016.5,8.0,0.0,0.0,1.0],[40.709316901441206,53.056461222141856,1860.0,8.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>[[6.200485742445525,29.17403952937586,-1860.0,6.0,0.0,0.0,1.0],[29.17403952937586,31.618034613091854,-733.6842,6.0,0.0,0.0,1.0],[31.618034613091854,35.03962773029424,0.0,6.0,0.0,1.0,1.0],[35.03962773029424,39.92761789772622,1016.5,7.0,0.0,0.0,1.0],[39.92761789772622,41.394014947955824,1725.15,8.0,9.0,2.0,-1.0],[41.394014947955824,54.59158840002218,1860.0,8.0,9.0,2.0,-1.0]]</t>
+          <t>[[6.200485742445525,29.17403952937586,-1860.0,6.0,0.0,0.0,1.0],[29.17403952937586,31.618034613091854,-733.6842,5.0,0.0,0.0,1.0],[31.618034613091854,35.03962773029424,0.0,6.0,0.0,1.0,1.0],[35.03962773029424,39.92761789772622,1016.5,7.0,0.0,0.0,1.0],[39.92761789772622,41.394014947955824,1725.15,8.0,9.0,2.0,-1.0],[41.394014947955824,54.59158840002218,1860.0,8.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>[[6.225850190061506,28.014124484041044,-1860.0,5.0,0.0,0.0,1.0],[28.014124484041044,33.58786907087302,-733.6842,5.0,0.0,0.0,1.0],[33.58786907087302,37.134797444311545,0.0,5.0,0.0,1.0,1.0],[37.134797444311545,39.668317711053355,1016.5,6.0,0.0,0.0,1.0],[39.668317711053355,56.389551471549275,1860.0,6.0,9.0,3.0,-1.0]]</t>
+          <t>[[6.225850190061506,28.014124484041044,-1860.0,4.0,0.0,0.0,1.0],[28.014124484041044,33.58786907087302,-733.6842,4.0,0.0,0.0,1.0],[33.58786907087302,37.134797444311545,0.0,4.0,0.0,1.0,1.0],[37.134797444311545,39.668317711053355,1016.5,4.0,0.0,0.0,1.0],[39.668317711053355,56.389551471549275,1860.0,6.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>[[10.044765917111793,29.85788793471034,-1860.0,4.0,0.0,0.0,1.0],[29.85788793471034,33.0832798910636,-733.6842,4.0,0.0,0.0,1.0],[33.0832798910636,36.76944212689588,0.0,4.0,0.0,1.0,1.0],[36.76944212689588,40.45560436272817,1016.5,5.0,0.0,0.0,1.0],[40.45560436272817,55.661023585536356,1860.0,5.0,9.0,3.0,-1.0]]</t>
+          <t>[[10.044765917111793,29.85788793471034,-1860.0,3.0,0.0,0.0,1.0],[29.85788793471034,33.0832798910636,-733.6842,3.0,0.0,0.0,1.0],[33.0832798910636,36.76944212689588,0.0,3.0,0.0,1.0,1.0],[36.76944212689588,40.45560436272817,1016.5,4.0,0.0,0.0,1.0],[40.45560436272817,55.661023585536356,1860.0,4.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>[[9.222657630748097,29.500499044187904,-1860.0,3.0,0.0,0.0,1.0],[29.500499044187904,31.70461224130092,-733.6842,3.0,0.0,0.0,1.0],[31.70461224130092,35.23119335668176,0.0,3.0,0.0,1.0,1.0],[35.23119335668176,40.08024239033041,1016.5,4.0,0.0,0.0,1.0],[40.08024239033041,52.864098933585936,1860.0,4.0,9.0,3.0,-1.0]]</t>
+          <t>[[9.222657630748097,29.500499044187904,-1860.0,3.0,0.0,0.0,1.0],[29.500499044187904,31.70461224130092,-733.6842,2.0,0.0,0.0,1.0],[31.70461224130092,35.23119335668176,0.0,2.0,0.0,1.0,1.0],[35.23119335668176,40.08024239033041,1016.5,3.0,0.0,0.0,1.0],[40.08024239033041,52.864098933585936,1860.0,3.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>[[9.953973035437304,23.008611728590267,-1860.0,2.0,0.0,0.0,1.0],[23.008611728590267,31.56165087238014,-733.6842,2.0,0.0,0.0,1.0],[31.56165087238014,35.16293051187061,0.0,2.0,0.0,1.0,1.0],[35.16293051187061,38.764210151361084,1016.5,3.0,0.0,0.0,1.0],[38.764210151361084,54.5198085741319,1860.0,3.0,9.0,3.0,-1.0]]</t>
+          <t>[[9.953973035437304,23.008611728590267,-1860.0,2.0,0.0,0.0,1.0],[23.008611728590267,31.56165087238014,-733.6842,2.0,0.0,0.0,1.0],[31.56165087238014,35.16293051187061,0.0,1.0,0.0,1.0,1.0],[35.16293051187061,38.764210151361084,1016.5,2.0,0.0,0.0,1.0],[38.764210151361084,54.5198085741319,1860.0,2.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>[[9.73102477340215,32.031469719122335,-1860.0,2.0,0.0,0.0,1.0],[32.031469719122335,40.45608225417218,-0.0,2.0,0.0,1.0,1.0],[40.45608225417218,58.79200365398655,1860.0,2.0,8.0,4.0,-1.0]]</t>
+          <t>[[9.73102477340215,32.031469719122335,-1860.0,1.0,0.0,0.0,1.0],[32.031469719122335,40.45608225417218,0.0,2.0,0.0,1.0,1.0],[40.45608225417218,58.79200365398655,1860.0,2.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>[[9.503965080018071,31.57908898205053,-1860.0,1.0,0.0,0.0,1.0],[31.57908898205053,40.77705727456405,-0.0,1.0,0.0,1.0,1.0],[40.77705727456405,41.6968541038154,890.0,1.0,8.0,4.0,-1.0],[41.6968541038154,55.03390812796001,1860.0,1.0,8.0,4.0,-1.0]]</t>
+          <t>[[9.503965080018071,31.57908898205053,-1860.0,1.0,0.0,0.0,1.0],[31.57908898205053,40.77705727456405,0.0,1.0,0.0,1.0,1.0],[40.77705727456405,41.6968541038154,890.0,1.0,8.0,4.0,-1.0],[41.6968541038154,55.03390812796001,1860.0,1.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -1937,11 +1937,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>[[9.515455611933138,40.31012682184718,-0.0,0.0,0.0,1.0,1.0],[40.31012682184718,55.707462426804184,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[9.515455611933138,40.31012682184718,0.0,0.0,0.0,1.0,1.0],[40.31012682184718,55.707462426804184,1860.0,1.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>[[9.58124836654681,39.921888996433026,-0.0,0.0,0.0,1.0,1.0],[39.921888996433026,53.75365163652822,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[9.58124836654681,39.921888996433026,0.0,0.0,0.0,1.0,1.0],[39.921888996433026,53.75365163652822,1860.0,0.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>[[9.718753169976825,33.57171765706868,-1860.0,1.0,4.0,1.0,-1.0],[33.57171765706868,34.471829524506106,-1074.7923,0.0,4.0,2.0,-1.0],[34.471829524506106,38.07227699425582,0.0,0.0,3.0,3.0,-1.0],[38.07227699425582,38.972388861693254,890.0,0.0,3.0,3.0,-1.0],[38.972388861693254,54.27429060812954,1860.0,0.0,3.0,3.0,-1.0]]</t>
+          <t>[[9.718753169976825,33.57171765706868,-1860.0,0.0,4.0,1.0,-1.0],[33.57171765706868,34.471829524506106,-1074.7923,0.0,4.0,2.0,-1.0],[34.471829524506106,38.07227699425582,0.0,0.0,3.0,3.0,-1.0],[38.07227699425582,38.972388861693254,890.0,0.0,3.0,3.0,-1.0],[38.972388861693254,54.27429060812954,1860.0,0.0,3.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>[[9.23685406081708,22.48916018283284,-1860.0,9.0,1.0,0.0,1.0],[22.48916018283284,22.930903720233367,-733.6842,9.0,1.0,0.0,1.0],[22.930903720233367,31.765774468243873,0.0,0.0,1.0,1.0,-1.0],[31.765774468243873,52.96946426346909,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[9.23685406081708,22.48916018283284,-1860.0,8.0,1.0,0.0,1.0],[22.48916018283284,22.930903720233367,-733.6842,9.0,1.0,0.0,1.0],[22.930903720233367,31.765774468243873,0.0,0.0,1.0,1.0,-1.0],[31.765774468243873,52.96946426346909,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>[[9.519828571434266,20.530027531303,-1860.0,9.0,0.0,0.0,1.0],[20.530027531303,21.753382971288413,-532.7423,8.0,0.0,1.0,1.0],[21.753382971288413,24.200093851259243,0.0,8.0,0.0,2.0,1.0],[24.200093851259243,25.42344929124466,1197.85,9.0,0.0,1.0,1.0],[25.42344929124466,49.89055809095296,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[9.519828571434266,20.530027531303,-1860.0,8.0,0.0,0.0,1.0],[20.530027531303,21.753382971288413,-532.7423,8.0,0.0,1.0,1.0],[21.753382971288413,24.200093851259243,0.0,8.0,0.0,2.0,1.0],[24.200093851259243,25.42344929124466,1197.85,9.0,0.0,1.0,1.0],[25.42344929124466,49.89055809095296,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>[[9.52167137946254,22.842992102229722,-1860.0,9.0,0.0,0.0,1.0],[22.842992102229722,35.33173027982396,-733.6842,9.0,0.0,0.0,1.0],[35.33173027982396,50.73450736552351,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[9.52167137946254,22.842992102229722,-1860.0,7.0,0.0,0.0,1.0],[22.842992102229722,35.33173027982396,-733.6842,9.0,0.0,0.0,1.0],[35.33173027982396,50.73450736552351,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>[[9.796336877994353,22.046653992895312,-1860.0,8.0,0.0,0.0,1.0],[22.046653992895312,36.21108315699955,-733.6842,8.0,0.0,0.0,1.0],[36.21108315699955,40.039307255406094,0.0,8.0,8.0,3.0,-1.0],[40.039307255406094,47.695755452219196,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[9.796336877994353,22.046653992895312,-1860.0,6.0,0.0,0.0,1.0],[22.046653992895312,36.21108315699955,-733.6842,7.0,0.0,0.0,1.0],[36.21108315699955,40.039307255406094,0.0,6.0,8.0,3.0,-1.0],[40.039307255406094,47.695755452219196,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>[[9.584146004254329,23.43552812007446,-1860.0,7.0,0.0,0.0,1.0],[23.43552812007446,36.09964891168144,-733.6842,7.0,0.0,0.0,1.0],[36.09964891168144,40.057186659058615,0.0,8.0,9.0,1.0,-1.0],[40.057186659058615,40.452940433796336,46.5,8.0,9.0,1.0,-1.0],[40.452940433796336,40.848694208534056,227.85,7.0,8.0,0.0,-1.0],[40.848694208534056,48.76376970328842,1860.0,7.0,8.0,0.0,-1.0]]</t>
+          <t>[[9.584146004254329,23.43552812007446,-1860.0,6.0,0.0,0.0,1.0],[23.43552812007446,36.09964891168144,-733.6842,7.0,0.0,0.0,1.0],[36.09964891168144,40.057186659058615,0.0,7.0,9.0,1.0,-1.0],[40.057186659058615,40.452940433796336,46.5,8.0,9.0,1.0,-1.0],[40.452940433796336,40.848694208534056,227.85,7.0,8.0,0.0,-1.0],[40.848694208534056,48.76376970328842,1860.0,7.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>[[8.64397061757689,23.05043299389458,-1860.0,6.0,0.0,0.0,1.0],[23.05043299389458,36.25635683885246,-733.6842,6.0,0.0,0.0,1.0],[36.25635683885246,40.25815194338516,0.0,6.0,8.0,3.0,-1.0],[40.25815194338516,41.45869047474496,227.85,6.0,8.0,0.0,-1.0],[41.45869047474496,48.26174215245054,1860.0,6.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.64397061757689,23.05043299389458,-1860.0,5.0,0.0,0.0,1.0],[23.05043299389458,36.25635683885246,-733.6842,5.0,0.0,0.0,1.0],[36.25635683885246,40.25815194338516,0.0,5.0,8.0,3.0,-1.0],[40.25815194338516,41.45869047474496,227.85,5.0,8.0,0.0,-1.0],[41.45869047474496,48.26174215245054,1860.0,5.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>[[5.862221143019794,23.2250913812518,-1860.0,5.0,0.0,0.0,1.0],[23.2250913812518,34.95676046113829,-733.6842,5.0,0.0,0.0,1.0],[34.95676046113829,39.18016132989743,0.0,5.0,8.0,4.0,-1.0],[39.18016132989743,41.05722838267927,227.85,5.0,8.0,0.0,-1.0],[41.05722838267927,52.3196306993703,1860.0,5.0,8.0,0.0,-1.0]]</t>
+          <t>[[5.862221143019794,23.2250913812518,-1860.0,3.0,0.0,0.0,1.0],[23.2250913812518,34.95676046113829,-733.6842,4.0,0.0,0.0,1.0],[34.95676046113829,39.18016132989743,0.0,4.0,8.0,4.0,-1.0],[39.18016132989743,41.05722838267927,227.85,4.0,8.0,0.0,-1.0],[41.05722838267927,52.3196306993703,1860.0,5.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>[[5.627116174204419,23.219334010162427,-1860.0,4.0,0.0,0.0,1.0],[23.219334010162427,35.256114634765275,-733.6842,4.0,0.0,0.0,1.0],[35.256114634765275,38.95973944233538,0.0,4.0,8.0,3.0,-1.0],[38.95973944233538,40.34859874517417,227.85,4.0,8.0,3.0,-1.0],[40.34859874517417,51.4594731678845,1860.0,4.0,9.0,2.0,-1.0]]</t>
+          <t>[[5.627116174204419,23.219334010162427,-1860.0,3.0,0.0,0.0,1.0],[23.219334010162427,35.256114634765275,-733.6842,3.0,0.0,0.0,1.0],[35.256114634765275,38.95973944233538,0.0,3.0,8.0,3.0,-1.0],[38.95973944233538,40.34859874517417,227.85,3.0,8.0,3.0,-1.0],[40.34859874517417,51.4594731678845,1860.0,3.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>[[1.9884784494145846,22.881439909653615,-1860.0,3.0,0.0,0.0,1.0],[22.881439909653615,35.815177956468254,-733.6842,3.0,0.0,0.0,1.0],[35.815177956468254,39.79478966318045,0.0,3.0,8.0,1.0,-1.0],[39.79478966318045,41.78459551653655,227.85,3.0,8.0,0.0,-1.0],[41.78459551653655,51.236173319978015,1860.0,3.0,8.0,0.0,-1.0]]</t>
+          <t>[[1.9884784494145846,22.881439909653615,-1860.0,3.0,0.0,0.0,1.0],[22.881439909653615,35.815177956468254,-733.6842,2.0,0.0,0.0,1.0],[35.815177956468254,39.79478966318045,0.0,2.0,8.0,1.0,-1.0],[39.79478966318045,41.78459551653655,227.85,2.0,8.0,0.0,-1.0],[41.78459551653655,51.236173319978015,1860.0,2.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>[[1.8387703061257163,21.71229952226691,-1860.0,2.0,0.0,0.0,1.0],[21.71229952226691,36.73862649056879,-733.6842,2.0,0.0,0.0,1.0],[36.73862649056879,41.101108513624176,0.0,2.0,8.0,3.0,-1.0],[41.101108513624176,49.82607255973494,1860.0,2.0,8.0,0.0,-1.0]]</t>
+          <t>[[1.8387703061257163,21.71229952226691,-1860.0,1.0,0.0,0.0,1.0],[21.71229952226691,36.73862649056879,-733.6842,2.0,0.0,0.0,1.0],[36.73862649056879,41.101108513624176,0.0,2.0,8.0,3.0,-1.0],[41.101108513624176,49.82607255973494,1860.0,2.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2236,11 +2236,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>[[-4.5925615795403685,36.02884467400938,-733.6842,0.0,0.0,0.0,1.0],[36.02884467400938,39.97814805977116,0.0,0.0,9.0,2.0,-1.0],[39.97814805977116,41.1065204557031,46.5,1.0,9.0,1.0,-1.0],[41.1065204557031,41.670706653669065,227.85,0.0,8.0,0.0,-1.0],[41.670706653669065,51.26187201909054,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-4.5925615795403685,36.02884467400938,-733.6843,0.0,0.0,0.0,1.0],[36.02884467400938,39.97814805977116,0.0,0.0,9.0,2.0,-1.0],[39.97814805977116,41.1065204557031,46.5,1.0,9.0,1.0,-1.0],[41.1065204557031,41.670706653669065,227.85,0.0,8.0,0.0,-1.0],[41.670706653669065,51.26187201909054,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>-733.6842</v>
+        <v>-733.6843</v>
       </c>
     </row>
     <row r="140">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>[[-4.112252481348731,33.34138079507791,-1860.0,1.0,8.0,1.0,-1.0],[33.34138079507791,35.64621976593494,-1074.7922,0.0,8.0,1.0,-1.0],[35.64621976593494,39.103478222220474,0.0,0.0,7.0,2.0,-1.0],[39.103478222220474,39.67968796493473,890.0,0.0,7.0,2.0,-1.0],[39.67968796493473,52.93251204736262,1860.0,0.0,7.0,2.0,-1.0]]</t>
+          <t>[[-4.112252481348731,33.34138079507791,-1860.0,1.0,8.0,1.0,-1.0],[33.34138079507791,35.64621976593494,-1074.7921,0.0,8.0,1.0,-1.0],[35.64621976593494,39.103478222220474,0.0,0.0,7.0,2.0,-1.0],[39.103478222220474,39.67968796493473,890.0001,0.0,7.0,2.0,-1.0],[39.67968796493473,52.93251204736262,1860.0,0.0,7.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>[[-4.895667298450673,33.63212204143139,-1860.0,1.0,7.0,0.0,-1.0],[33.63212204143139,34.17476696171142,-1074.7922,0.0,7.0,1.0,-1.0],[34.17476696171142,37.97328140367162,0.0,0.0,6.0,2.0,-1.0],[37.97328140367162,40.14386108479174,890.0,0.0,6.0,2.0,-1.0],[40.14386108479174,48.826179809272205,1860.0,0.0,6.0,2.0,-1.0]]</t>
+          <t>[[-4.895667298450673,33.63212204143139,-1860.0,1.0,7.0,0.0,-1.0],[33.63212204143139,34.17476696171142,-1074.7921,0.0,7.0,1.0,-1.0],[34.17476696171142,37.97328140367162,0.0,0.0,6.0,2.0,-1.0],[37.97328140367162,40.14386108479174,890.0001,0.0,6.0,2.0,-1.0],[40.14386108479174,48.826179809272205,1860.0,0.0,6.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>[[-4.4881139493366,33.648967563900946,-1860.0,1.0,6.0,1.0,-1.0],[33.648967563900946,34.75439021645856,-1074.7922,0.0,6.0,1.0,-1.0],[34.75439021645856,38.62336950041019,0.0,0.0,5.0,2.0,-1.0],[38.62336950041019,50.23030735226509,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-4.4881139493366,33.648967563900946,-1860.0,1.0,6.0,1.0,-1.0],[33.648967563900946,34.75439021645856,-1074.7921,0.0,6.0,1.0,-1.0],[34.75439021645856,38.62336950041019,0.0,0.0,5.0,2.0,-1.0],[38.62336950041019,50.23030735226509,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>[[-4.548724307462819,33.33541867154124,-1860.0,1.0,5.0,1.0,-1.0],[33.33541867154124,35.00677792061495,-1074.7922,0.0,5.0,1.0,-1.0],[35.00677792061495,38.90661616845361,0.0,0.0,4.0,2.0,-1.0],[38.90661616845361,40.02085566783608,890.0,0.0,4.0,0.0,-1.0],[40.02085566783608,50.60613091196957,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-4.548724307462819,33.33541867154124,-1860.0,1.0,5.0,1.0,-1.0],[33.33541867154124,35.00677792061495,-1074.7921,0.0,5.0,1.0,-1.0],[35.00677792061495,38.90661616845361,0.0,0.0,4.0,2.0,-1.0],[38.90661616845361,40.02085566783608,890.0001,0.0,4.0,0.0,-1.0],[40.02085566783608,50.60613091196957,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>[[-4.436531506642835,32.42116870133077,-1860.0,1.0,5.0,0.0,-1.0],[32.42116870133077,33.978536315752194,-1074.7922,0.0,5.0,0.0,-1.0],[33.978536315752194,37.612394082735506,0.0,0.0,4.0,1.0,-1.0],[37.612394082735506,38.13151662087598,890.0,0.0,4.0,1.0,-1.0],[38.13151662087598,46.956599769264024,1860.0,0.0,4.0,1.0,-1.0]]</t>
+          <t>[[-4.436531506642835,32.42116870133077,-1860.0,1.0,5.0,0.0,-1.0],[32.42116870133077,33.978536315752194,-1074.7921,0.0,5.0,0.0,-1.0],[33.978536315752194,37.612394082735506,0.0,0.0,4.0,1.0,-1.0],[37.612394082735506,38.13151662087598,890.0001,0.0,4.0,1.0,-1.0],[38.13151662087598,46.956599769264024,1860.0,0.0,4.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>[[-4.513958606228754,32.934685247909954,-1860.0,1.0,4.0,0.0,-1.0],[32.934685247909954,34.93194625346402,-1074.7922,0.0,4.0,1.0,-1.0],[34.93194625346402,38.427153013183634,0.0,0.0,3.0,2.0,-1.0],[38.427153013183634,38.92646826457215,890.0,0.0,3.0,2.0,-1.0],[38.92646826457215,44.91825128123434,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[-4.513958606228754,32.934685247909954,-1860.0,1.0,4.0,0.0,-1.0],[32.934685247909954,34.93194625346402,-1074.7921,0.0,4.0,1.0,-1.0],[34.93194625346402,38.427153013183634,0.0,0.0,3.0,2.0,-1.0],[38.427153013183634,38.92646826457215,890.0001,0.0,3.0,2.0,-1.0],[38.92646826457215,44.91825128123434,1860.0,0.0,3.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>[[-4.810640504202817,32.86100263542682,-1860.0,1.0,3.0,0.0,-1.0],[32.86100263542682,36.581658747982836,0.0,0.0,2.0,1.0,-1.0],[36.581658747982836,37.04674076205234,890.0,0.0,2.0,1.0,-1.0],[37.04674076205234,41.23247888867785,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[-4.810640504202817,32.86100263542682,-1860.0,1.0,3.0,0.0,-1.0],[32.86100263542682,36.581658747982836,0.0,0.0,2.0,1.0,-1.0],[36.581658747982836,37.04674076205234,890.0001,0.0,2.0,1.0,-1.0],[37.04674076205234,41.23247888867785,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2353,11 +2353,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>[[-4.701487278192305,32.52958542222231,-1860.0,1.0,2.0,0.0,-1.0],[32.52958542222231,33.56378188612272,-1074.7922,0.0,2.0,1.0,-1.0],[33.56378188612272,37.18346950977414,0.0,0.0,1.0,2.0,-1.0],[37.18346950977414,39.76896066952516,890.0,0.0,1.0,1.0,-1.0],[39.76896066952516,46.49123768487779,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[-4.701487278192305,32.52958542222231,-1860.0,1.0,2.0,0.0,-1.0],[32.52958542222231,33.56378188612272,-1074.7921,0.0,2.0,1.0,-1.0],[33.56378188612272,37.18346950977414,0.0,0.0,1.0,2.0,-1.0],[37.18346950977414,39.76896066952516,890.0001,0.0,1.0,1.0,-1.0],[39.76896066952516,46.49123768487779,1860.0,0.0,1.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>890</v>
+        <v>890.0001</v>
       </c>
     </row>
     <row r="149">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>[[-4.495298292173052,24.796358250910963,-1860.0,9.0,0.0,0.0,1.0],[24.796358250910963,35.718670860196525,0.0,9.0,0.0,1.0,1.0],[35.718670860196525,44.65510844961199,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-4.495298292173052,24.796358250910963,-1860.0,8.0,0.0,0.0,1.0],[24.796358250910963,35.718670860196525,0.0,7.0,0.0,1.0,1.0],[35.718670860196525,44.65510844961199,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>[[-4.3981422541550295,24.77468043619473,-1860.0,8.0,0.0,0.0,1.0],[24.77468043619473,35.714488945075885,0.0,8.0,0.0,1.0,1.0],[35.714488945075885,40.72856784497975,1860.0,9.0,9.0,2.0,-1.0]]</t>
+          <t>[[-4.3981422541550295,24.77468043619473,-1860.0,7.0,0.0,0.0,1.0],[24.77468043619473,35.714488945075885,0.0,6.0,0.0,1.0,1.0],[35.714488945075885,40.72856784497975,1860.0,8.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>[[-4.571120265029684,25.75084319835525,-1860.0,7.0,0.0,0.0,1.0],[25.75084319835525,33.575866027615874,0.0,7.0,0.0,1.0,1.0],[33.575866027615874,43.84620849102045,1860.0,8.0,9.0,1.0,-1.0]]</t>
+          <t>[[-4.571120265029684,25.75084319835525,-1860.0,6.0,0.0,0.0,1.0],[25.75084319835525,33.575866027615874,0.0,6.0,0.0,1.0,1.0],[33.575866027615874,43.84620849102045,1860.0,8.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>[[-4.659987055350011,24.261434604896554,-1860.0,6.0,0.0,0.0,1.0],[24.261434604896554,34.40930185410588,0.0,6.0,0.0,1.0,1.0],[34.40930185410588,45.57195582823613,1860.0,6.0,8.0,3.0,-1.0]]</t>
+          <t>[[-4.659987055350011,24.261434604896554,-1860.0,5.0,0.0,0.0,1.0],[24.261434604896554,34.40930185410588,0.0,3.0,0.0,1.0,1.0],[34.40930185410588,45.57195582823613,1860.0,6.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>[[-4.453921093408683,24.470777928877318,-1860.0,5.0,0.0,0.0,1.0],[24.470777928877318,33.95428580503667,0.0,5.0,0.0,1.0,1.0],[33.95428580503667,34.42846119884463,890.0,5.0,8.0,4.0,-1.0],[34.42846119884463,42.489442893580076,1860.0,5.0,8.0,4.0,-1.0]]</t>
+          <t>[[-4.453921093408683,24.470777928877318,-1860.0,4.0,0.0,0.0,1.0],[24.470777928877318,33.95428580503667,0.0,3.0,0.0,1.0,1.0],[33.95428580503667,34.42846119884463,890.0,4.0,8.0,4.0,-1.0],[34.42846119884463,42.489442893580076,1860.0,5.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>[[-4.5062635054054745,24.70727374859897,-1860.0,4.0,0.0,0.0,1.0],[24.70727374859897,34.76439313112509,0.0,4.0,0.0,1.0,1.0],[34.76439313112509,35.243303577912044,890.0,4.0,8.0,4.0,-1.0],[35.243303577912044,42.90587072650338,1860.0,4.0,8.0,4.0,-1.0]]</t>
+          <t>[[-4.5062635054054745,24.70727374859897,-1860.0,4.0,0.0,0.0,1.0],[24.70727374859897,34.76439313112509,0.0,3.0,0.0,1.0,1.0],[34.76439313112509,35.243303577912044,890.0,4.0,8.0,4.0,-1.0],[35.243303577912044,42.90587072650338,1860.0,4.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>[[-2.618455385771295,32.04932766359303,-1860.0,2.0,0.0,0.0,1.0],[32.04932766359303,35.6049977199381,0.0,1.0,7.0,5.0,-1.0],[35.6049977199381,41.38296156149882,1860.0,1.0,7.0,5.0,-1.0]]</t>
+          <t>[[-2.618455385771295,32.04932766359303,-1860.0,1.0,0.0,0.0,1.0],[32.04932766359303,35.6049977199381,0.0,1.0,7.0,5.0,-1.0],[35.6049977199381,41.38296156149882,1860.0,1.0,7.0,5.0,-1.0]]</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>[[10.935025213554844,30.159331739625436,-1860.0,1.0,0.0,0.0,1.0],[30.159331739625436,30.490785300419756,-873.8504,0.0,8.0,3.0,-1.0],[30.490785300419756,33.80532090836296,0.0,0.0,7.0,4.0,-1.0],[33.80532090836296,35.462588712334565,1071.35,0.0,7.0,3.0,-1.0],[35.462588712334565,43.74892773219258,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[10.935025213554844,30.159331739625436,-1860.0,0.0,0.0,0.0,1.0],[30.159331739625436,30.490785300419756,-873.8504,0.0,8.0,3.0,-1.0],[30.490785300419756,33.80532090836296,0.0,0.0,7.0,4.0,-1.0],[33.80532090836296,35.462588712334565,1071.35,0.0,7.0,3.0,-1.0],[35.462588712334565,43.74892773219258,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>[[10.59862303866299,30.314017397786472,-1860.0,1.0,7.0,0.0,-1.0],[30.314017397786472,34.91427608158195,0.0,0.0,7.0,1.0,-1.0],[34.91427608158195,75.65942442377049,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[10.59862303866299,30.314017397786472,-1860.0,1.0,7.0,0.0,-1.0],[30.314017397786472,34.91427608158195,0.0,0.0,6.0,1.0,-1.0],[34.91427608158195,75.65942442377049,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>[[10.424821564384656,17.328288023122052,-1860.0,8.0,15.0,0.0,0.0],[17.328288023122052,34.97048008433985,0.0,0.0,7.0,1.0,-1.0],[34.97048008433985,86.36295261049602,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[10.424821564384656,17.328288023122052,-1860.0,8.0,15.0,0.0,0.0],[17.328288023122052,34.97048008433985,0.0,0.0,7.0,1.0,-1.0],[34.97048008433985,86.36295261049602,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>[[10.295243394271406,18.528461346656314,-1860.0,9.0,13.0,1.0,0.0],[18.528461346656314,19.276935705964032,-1607.5346,8.0,13.0,2.0,0.0],[19.276935705964032,35.743371610733846,0.0,0.0,5.0,1.0,-1.0],[35.743371610733846,84.39420496573558,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[10.295243394271406,18.528461346656314,-1860.0,9.0,13.0,1.0,0.0],[18.528461346656314,19.276935705964032,-1607.5346,8.0,13.0,2.0,0.0],[19.276935705964032,35.743371610733846,0.0,0.0,5.0,1.0,-1.0],[35.743371610733846,84.39420496573558,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>[[10.904807859266159,18.341452276730262,-1860.0,9.0,3.0,0.0,1.0],[18.341452276730262,19.994039925055617,-733.6842,9.0,3.0,0.0,1.0],[19.994039925055617,36.51991640830918,0.0,0.0,3.0,1.0,-1.0],[36.51991640830918,92.70789645137128,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[10.904807859266159,18.341452276730262,-1860.0,9.0,3.0,0.0,1.0],[18.341452276730262,19.994039925055617,-733.6842,9.0,3.0,0.0,1.0],[19.994039925055617,36.51991640830918,0.0,0.0,3.0,1.0,-1.0],[36.51991640830918,92.70789645137128,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>[[10.723096815150768,19.48061075300562,-1860.0,9.0,1.0,0.0,1.0],[19.48061075300562,20.2767483837197,-733.6842,9.0,1.0,0.0,1.0],[20.2767483837197,31.422675213716786,0.0,0.0,1.0,1.0,-1.0],[31.422675213716786,34.6072257365731,0.0,0.0,0.0,1.0,-1.0],[34.6072257365731,38.58791389014348,1860.0,0.0,0.0,0.0,-1.0],[38.58791389014348,89.54072225584446,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[10.723096815150768,19.48061075300562,-1860.0,7.0,1.0,0.0,1.0],[19.48061075300562,20.2767483837197,-733.6842,9.0,1.0,0.0,1.0],[20.2767483837197,31.422675213716786,0.0,0.0,1.0,1.0,-1.0],[31.422675213716786,34.6072257365731,0.0,0.0,0.0,1.0,-1.0],[34.6072257365731,38.58791389014348,1860.0,0.0,0.0,0.0,-1.0],[38.58791389014348,89.54072225584446,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>[[10.704894523780043,21.105191622045012,-1860.0,8.0,0.0,0.0,1.0],[21.105191622045012,27.17203159603291,-733.6842,8.0,0.0,0.0,1.0],[27.17203159603291,30.638797295454566,0.0,8.0,0.0,1.0,1.0],[30.638797295454566,43.63916866828577,1016.5,9.0,0.0,0.0,1.0],[43.63916866828577,96.50734558446602,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[10.704894523780043,21.105191622045012,-1860.0,6.0,0.0,0.0,1.0],[21.105191622045012,27.17203159603291,-733.6842,8.0,0.0,0.0,1.0],[27.17203159603291,30.638797295454566,0.0,7.0,0.0,1.0,1.0],[30.638797295454566,43.63916866828577,1016.5,9.0,0.0,0.0,1.0],[43.63916866828577,96.50734558446602,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>[[10.693688779388,22.063281640587462,-1860.0,7.0,0.0,0.0,1.0],[22.063281640587462,26.123850519587265,-733.6842,7.0,0.0,0.0,1.0],[26.123850519587265,29.37230562278711,0.0,7.0,0.0,1.0,1.0],[29.37230562278711,48.05092246618622,1016.5,8.0,0.0,0.0,1.0],[48.05092246618622,91.09295258358418,1860.0,8.0,1.0,0.0,1.0]]</t>
+          <t>[[10.693688779388,22.063281640587462,-1860.0,6.0,0.0,0.0,1.0],[22.063281640587462,26.123850519587265,-733.6842,7.0,0.0,0.0,1.0],[26.123850519587265,29.37230562278711,0.0,6.0,0.0,1.0,1.0],[29.37230562278711,48.05092246618622,1016.5,8.0,0.0,0.0,1.0],[48.05092246618622,91.09295258358418,1860.0,8.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>[[12.598372861454413,27.390008247241827,-1860.0,7.0,0.0,0.0,1.0],[27.390008247241827,43.73865788416476,-733.6842,7.0,0.0,0.0,1.0],[43.73865788416476,49.18820776313907,0.0,7.0,0.0,1.0,1.0],[49.18820776313907,53.85925051654562,1016.5,8.0,0.0,0.0,1.0],[53.85925051654562,54.63775764211338,1725.15,9.0,9.0,1.0,-1.0],[54.63775764211338,89.67057829266251,1860.0,9.0,9.0,1.0,-1.0]]</t>
+          <t>[[12.598372861454413,27.390008247241827,-1860.0,6.0,0.0,0.0,1.0],[27.390008247241827,43.73865788416476,-733.6842,7.0,0.0,0.0,1.0],[43.73865788416476,49.18820776313907,0.0,6.0,0.0,1.0,1.0],[49.18820776313907,53.85925051654562,1016.5,8.0,0.0,0.0,1.0],[53.85925051654562,54.63775764211338,1725.15,9.0,9.0,1.0,-1.0],[54.63775764211338,89.67057829266251,1860.0,9.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>[[13.37458633449267,26.413039824104207,-1860.0,6.0,0.0,0.0,1.0],[26.413039824104207,42.711106686118626,-733.6842,6.0,0.0,0.0,1.0],[42.711106686118626,46.78562340162223,0.0,6.0,0.0,1.0,1.0],[46.78562340162223,49.23033343092439,1016.5,7.0,0.0,0.0,1.0],[49.23033343092439,53.304850146427995,1725.15,8.0,9.0,1.0,-1.0],[53.304850146427995,94.05001730146405,1860.0,8.0,10.0,0.0,-1.0]]</t>
+          <t>[[13.37458633449267,26.413039824104207,-1860.0,6.0,0.0,0.0,1.0],[26.413039824104207,42.711106686118626,-733.6842,5.0,0.0,0.0,1.0],[42.711106686118626,46.78562340162223,0.0,6.0,0.0,1.0,1.0],[46.78562340162223,49.23033343092439,1016.5,7.0,0.0,0.0,1.0],[49.23033343092439,53.304850146427995,1725.15,8.0,9.0,1.0,-1.0],[53.304850146427995,94.05001730146405,1860.0,8.0,10.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>[[13.639933032358712,28.222331165931784,-1860.0,5.0,0.0,0.0,1.0],[28.222331165931784,41.18446284021896,-733.6842,5.0,0.0,0.0,1.0],[41.18446284021896,45.2351289884337,0.0,5.0,0.0,1.0,1.0],[45.2351289884337,50.095928366291396,1016.5,6.0,0.0,0.0,1.0],[50.095928366291396,93.84312276701061,1860.0,6.0,9.0,2.0,-1.0]]</t>
+          <t>[[13.639933032358712,28.222331165931784,-1860.0,4.0,0.0,0.0,1.0],[28.222331165931784,41.18446284021896,-733.6842,4.0,0.0,0.0,1.0],[41.18446284021896,45.2351289884337,0.0,4.0,0.0,1.0,1.0],[45.2351289884337,50.095928366291396,1016.5,4.0,0.0,0.0,1.0],[50.095928366291396,93.84312276701061,1860.0,6.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>[[13.491941837436226,26.200707349547443,-1860.0,4.0,0.0,0.0,1.0],[26.200707349547443,41.152196187325345,-733.6842,4.0,0.0,0.0,1.0],[41.152196187325345,45.63764283865872,0.0,4.0,0.0,1.0,1.0],[45.63764283865872,52.36581281565877,1016.5,5.0,0.0,0.0,1.0],[52.36581281565877,53.11338725754767,1725.15,6.0,9.0,1.0,-1.0],[53.11338725754767,87.50181158443685,1860.0,6.0,10.0,0.0,-1.0]]</t>
+          <t>[[13.491941837436226,26.200707349547443,-1860.0,3.0,0.0,0.0,1.0],[26.200707349547443,41.152196187325345,-733.6842,3.0,0.0,0.0,1.0],[41.152196187325345,45.63764283865872,0.0,3.0,0.0,1.0,1.0],[45.63764283865872,52.36581281565877,1016.5,4.0,0.0,0.0,1.0],[52.36581281565877,53.11338725754767,1725.15,5.0,9.0,1.0,-1.0],[53.11338725754767,87.50181158443685,1860.0,5.0,10.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>[[16.84510233064838,26.604269294066462,-1860.0,3.0,0.0,0.0,1.0],[26.604269294066462,40.545936384663726,-733.6842,3.0,0.0,0.0,1.0],[40.545936384663726,44.72843651184291,0.0,3.0,0.0,1.0,1.0],[44.72843651184291,52.3963534116714,1016.5,4.0,0.0,0.0,1.0],[52.3963534116714,85.85635442910484,1860.0,4.0,9.0,2.0,-1.0]]</t>
+          <t>[[16.84510233064838,26.604269294066462,-1860.0,2.0,0.0,0.0,1.0],[26.604269294066462,40.545936384663726,-733.6842,2.0,0.0,0.0,1.0],[40.545936384663726,44.72843651184291,0.0,2.0,0.0,1.0,1.0],[44.72843651184291,52.3963534116714,1016.5,3.0,0.0,0.0,1.0],[52.3963534116714,85.85635442910484,1860.0,3.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>[[16.875250434512846,27.82480811334132,-1860.0,2.0,0.0,0.0,1.0],[27.82480811334132,40.33858831771671,-733.6842,2.0,0.0,0.0,1.0],[40.33858831771671,45.031255894357486,0.0,2.0,0.0,1.0,1.0],[45.031255894357486,52.07025725931865,1016.5,3.0,0.0,0.0,1.0],[52.07025725931865,53.634479784865576,1725.15,4.0,9.0,1.0,-1.0],[53.634479784865576,94.30426544908562,1860.0,4.0,10.0,0.0,-1.0]]</t>
+          <t>[[16.875250434512846,27.82480811334132,-1860.0,2.0,0.0,0.0,1.0],[27.82480811334132,40.33858831771671,-733.6842,2.0,0.0,0.0,1.0],[40.33858831771671,45.031255894357486,0.0,1.0,0.0,1.0,1.0],[45.031255894357486,52.07025725931865,1016.5,2.0,0.0,0.0,1.0],[52.07025725931865,53.634479784865576,1725.15,4.0,9.0,1.0,-1.0],[53.634479784865576,94.30426544908562,1860.0,3.0,10.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>[[19.36322207426412,41.50920932146643,-1860.0,2.0,0.0,0.0,1.0],[41.50920932146643,46.091137717439324,-733.6842,2.0,0.0,0.0,1.0],[46.091137717439324,50.67306611341222,0.0,2.0,9.0,2.0,-1.0],[50.67306611341222,53.727685044060806,46.5,3.0,9.0,1.0,-1.0],[53.727685044060806,94.96504060781683,1860.0,4.0,9.0,0.0,-1.0]]</t>
+          <t>[[19.36322207426412,41.50920932146643,-1860.0,2.0,0.0,0.0,1.0],[41.50920932146643,46.091137717439324,-733.6842,2.0,0.0,0.0,1.0],[46.091137717439324,50.67306611341222,0.0,1.0,9.0,2.0,-1.0],[50.67306611341222,53.727685044060806,46.5,2.0,9.0,1.0,-1.0],[53.727685044060806,94.96504060781683,1860.0,3.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>[[19.40057575206109,41.57412990346195,-1860.0,1.0,0.0,0.0,1.0],[41.57412990346195,46.58106148603635,-733.6842,1.0,0.0,0.0,1.0],[46.58106148603635,51.58799306861073,0.0,1.0,9.0,2.0,-1.0],[51.58799306861073,53.01854494934628,46.5,2.0,9.0,1.0,-1.0],[53.01854494934628,90.2128938484703,1860.0,2.0,9.0,1.0,-1.0]]</t>
+          <t>[[19.40057575206109,41.57412990346195,-1860.0,1.0,0.0,0.0,1.0],[41.57412990346195,46.58106148603635,-733.6842,0.0,0.0,0.0,1.0],[46.58106148603635,51.58799306861073,0.0,1.0,9.0,2.0,-1.0],[51.58799306861073,53.01854494934628,46.5,2.0,9.0,1.0,-1.0],[53.01854494934628,90.2128938484703,1860.0,2.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -2873,11 +2873,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>[[18.29585114683094,48.156297245432384,-733.6842,0.0,0.0,0.0,1.0],[48.156297245432384,53.38187531268764,0.0,0.0,9.0,2.0,-1.0],[53.38187531268764,54.874897617617705,46.5,1.0,9.0,1.0,-1.0],[54.874897617617705,92.20045524086952,1860.0,2.0,9.0,0.0,-1.0]]</t>
+          <t>[[18.29585114683094,48.156297245432384,-733.6843,0.0,0.0,0.0,1.0],[48.156297245432384,53.38187531268764,0.0,0.0,9.0,2.0,-1.0],[53.38187531268764,54.874897617617705,46.5,1.0,9.0,1.0,-1.0],[54.874897617617705,92.20045524086952,1860.0,2.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>-733.6842</v>
+        <v>-733.6843</v>
       </c>
     </row>
     <row r="189">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>[[18.349246050748278,50.16642770056577,-0.0,0.0,0.0,1.0,1.0],[50.16642770056577,50.88954546533435,890.0,0.0,8.0,2.0,-1.0],[50.88954546533435,89.93790476283763,1860.0,0.0,9.0,1.0,-1.0]]</t>
+          <t>[[18.349246050748278,50.16642770056577,0.0,0.0,0.0,1.0,1.0],[50.16642770056577,50.88954546533435,890.0,0.0,8.0,2.0,-1.0],[50.88954546533435,89.93790476283763,1860.0,0.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>[[19.853463846891557,41.59585373794009,-1860.0,1.0,8.0,0.0,-1.0],[41.59585373794009,43.04534639734332,-1074.7923,0.0,8.0,1.0,-1.0],[43.04534639734332,48.11857070525465,0.0,0.0,7.0,2.0,-1.0],[48.11857070525465,51.01755602406112,890.0,0.0,7.0,2.0,-1.0],[51.01755602406112,91.6033504873517,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[19.853463846891557,41.59585373794009,-1860.0,1.0,8.0,0.0,-1.0],[41.59585373794009,43.04534639734332,-1074.7922,0.0,8.0,1.0,-1.0],[43.04534639734332,48.11857070525465,0.0,0.0,7.0,2.0,-1.0],[48.11857070525465,51.01755602406112,890.0001,0.0,7.0,2.0,-1.0],[51.01755602406112,91.6033504873517,1860.0,0.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>[[19.172314516033506,40.32332084343475,-1860.0,1.0,7.0,0.0,-1.0],[40.32332084343475,44.69939111806949,-1074.7923,0.0,7.0,1.0,-1.0],[44.69939111806949,49.80480643847669,0.0,0.0,7.0,1.0,-1.0],[49.80480643847669,91.37747404750672,1860.0,1.0,7.0,0.0,-1.0]]</t>
+          <t>[[19.172314516033506,40.32332084343475,-1860.0,1.0,7.0,0.0,-1.0],[40.32332084343475,44.69939111806949,-1074.7922,0.0,7.0,1.0,-1.0],[44.69939111806949,49.80480643847669,0.0,0.0,7.0,1.0,-1.0],[49.80480643847669,91.37747404750672,1860.0,1.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>[[18.862835997170503,41.85503298893214,-1860.0,1.0,6.0,0.0,-1.0],[41.85503298893214,44.01055145690979,-1074.7923,0.0,6.0,1.0,-1.0],[44.01055145690979,48.321588392865095,0.0,0.0,5.0,2.0,-1.0],[48.321588392865095,51.91411917282785,890.0,0.0,5.0,2.0,-1.0],[51.91411917282785,89.99494544043306,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[18.862835997170503,41.85503298893214,-1860.0,1.0,6.0,0.0,-1.0],[41.85503298893214,44.01055145690979,-1074.7922,0.0,6.0,1.0,-1.0],[44.01055145690979,48.321588392865095,0.0,0.0,5.0,2.0,-1.0],[48.321588392865095,51.91411917282785,890.0001,0.0,5.0,2.0,-1.0],[51.91411917282785,89.99494544043306,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>[[17.99694564525315,39.653137753570505,-1860.0,1.0,6.0,0.0,-1.0],[39.653137753570505,42.15192915068404,-1074.7923,0.0,6.0,0.0,-1.0],[42.15192915068404,46.31658147920661,0.0,0.0,5.0,1.0,-1.0],[46.31658147920661,48.815372876320154,890.0,0.0,5.0,1.0,-1.0],[48.815372876320154,100.45706175,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[17.99694564525315,39.653137753570505,-1860.0,1.0,6.0,0.0,-1.0],[39.653137753570505,42.15192915068404,-1074.7922,0.0,6.0,0.0,-1.0],[42.15192915068404,46.31658147920661,0.0,0.0,5.0,1.0,-1.0],[46.31658147920661,48.815372876320154,890.0001,0.0,5.0,1.0,-1.0],[48.815372876320154,100.45706175,1860.0,0.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>[[19.300369879741282,39.656269192465615,-1860.0,1.0,5.0,0.0,-1.0],[39.656269192465615,40.41019138923318,-1074.7923,0.0,5.0,0.0,-1.0],[40.41019138923318,44.93372456983859,0.0,0.0,4.0,1.0,-1.0],[44.93372456983859,47.949413356908856,890.0,0.0,4.0,1.0,-1.0],[47.949413356908856,93.93866735973049,1860.0,0.0,4.0,1.0,-1.0]]</t>
+          <t>[[19.300369879741282,39.656269192465615,-1860.0,1.0,5.0,0.0,-1.0],[39.656269192465615,40.41019138923318,-1074.7922,0.0,5.0,0.0,-1.0],[40.41019138923318,44.93372456983859,0.0,0.0,4.0,1.0,-1.0],[44.93372456983859,47.949413356908856,890.0001,0.0,4.0,1.0,-1.0],[47.949413356908856,93.93866735973049,1860.0,0.0,4.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>[[17.737711314380388,38.626436171860085,-1860.0,10.0,4.0,0.0,1.0],[38.626436171860085,41.13308315475765,-1808.4765,9.0,4.0,1.0,1.0],[41.13308315475765,41.96863214905684,-1074.7923,0.0,4.0,0.0,-1.0],[41.96863214905684,46.14637712055278,0.0,0.0,3.0,1.0,-1.0],[46.14637712055278,48.65302410345034,890.0,0.0,3.0,1.0,-1.0],[48.65302410345034,100.45706175,1860.0,0.0,3.0,1.0,-1.0]]</t>
+          <t>[[17.737711314380388,38.626436171860085,-1860.0,10.0,4.0,0.0,1.0],[38.626436171860085,41.13308315475765,-1808.4764,9.0,4.0,1.0,1.0],[41.13308315475765,41.96863214905684,-1074.7922,0.0,4.0,0.0,-1.0],[41.96863214905684,46.14637712055278,0.0,0.0,3.0,1.0,-1.0],[46.14637712055278,48.65302410345034,890.0001,0.0,3.0,1.0,-1.0],[48.65302410345034,100.45706175,1860.0,0.0,3.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -2977,11 +2977,11 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>[[18.924053915325917,41.16032877932794,-1860.0,10.0,3.0,0.0,1.0],[41.16032877932794,41.98389451503172,-1808.4765,9.0,3.0,1.0,1.0],[41.98389451503172,46.10172319355061,0.0,9.0,2.0,2.0,1.0],[46.10172319355061,46.92528892925439,227.85,9.0,2.0,2.0,1.0],[46.92528892925439,51.04311760777328,890.0,0.0,2.0,1.0,-1.0],[51.04311760777328,100.45706175,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[18.924053915325917,41.16032877932794,-1860.0,10.0,3.0,0.0,1.0],[41.16032877932794,41.98389451503172,-1808.4764,9.0,3.0,1.0,1.0],[41.98389451503172,46.10172319355061,0.0,9.0,2.0,2.0,1.0],[46.10172319355061,46.92528892925439,227.8501,9.0,2.0,2.0,1.0],[46.92528892925439,51.04311760777328,890.0001,0.0,2.0,1.0,-1.0],[51.04311760777328,100.45706175,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>890</v>
+        <v>890.0001</v>
       </c>
     </row>
     <row r="197">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>[[19.64682174260916,33.52332760246415,-1860.0,9.0,2.0,0.0,1.0],[33.52332760246415,40.869713057681494,-733.6842,9.0,2.0,0.0,1.0],[40.869713057681494,44.951038310580024,0.0,9.0,1.0,1.0,1.0],[44.951038310580024,49.848628614058256,1197.85,9.0,1.0,1.0,1.0],[49.848628614058256,100.45706175,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[19.64682174260916,33.52332760246415,-1860.0,8.0,2.0,0.0,1.0],[33.52332760246415,40.869713057681494,-733.6842,9.0,2.0,0.0,1.0],[40.869713057681494,44.951038310580024,0.0,9.0,1.0,1.0,1.0],[44.951038310580024,49.848628614058256,1197.85,9.0,1.0,1.0,1.0],[49.848628614058256,100.45706175,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>[[19.184450484062637,32.95838988285303,-1860.0,9.0,1.0,0.0,1.0],[32.95838988285303,39.440243717577914,-733.6842,9.0,1.0,0.0,1.0],[39.440243717577914,43.491402364280965,0.0,9.0,0.0,1.0,1.0],[43.491402364280965,48.35279274032463,1197.85,9.0,0.0,1.0,1.0],[48.35279274032463,99.39739168878312,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[19.184450484062637,32.95838988285303,-1860.0,8.0,1.0,0.0,1.0],[32.95838988285303,39.440243717577914,-733.6842,9.0,1.0,0.0,1.0],[39.440243717577914,43.491402364280965,0.0,9.0,0.0,1.0,1.0],[43.491402364280965,48.35279274032463,1197.85,9.0,0.0,1.0,1.0],[48.35279274032463,99.39739168878312,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>[[19.314279809579716,45.89321687238527,-1860.0,9.0,0.0,0.0,1.0],[45.89321687238527,50.72575088380445,0.0,8.0,8.0,2.0,-1.0],[50.72575088380445,99.05109099799635,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[19.314279809579716,45.89321687238527,-1860.0,8.0,0.0,0.0,1.0],[45.89321687238527,50.72575088380445,0.0,7.0,8.0,2.0,-1.0],[50.72575088380445,99.05109099799635,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>[[17.7712642036819,43.66277656667039,-1860.0,8.0,0.0,0.0,1.0],[43.66277656667039,47.83882694779757,-873.8504,7.0,8.0,2.0,-1.0],[47.83882694779757,52.85008740515018,0.0,7.0,8.0,2.0,-1.0],[52.85008740515018,54.52050755760105,890.0,8.0,8.0,1.0,-1.0],[54.52050755760105,100.45706175,1860.0,8.0,9.0,0.0,-1.0]]</t>
+          <t>[[17.7712642036819,43.66277656667039,-1860.0,8.0,0.0,0.0,1.0],[43.66277656667039,47.83882694779757,-873.8505,7.0,8.0,2.0,-1.0],[47.83882694779757,52.85008740515018,0.0,7.0,8.0,2.0,-1.0],[52.85008740515018,54.52050755760105,890.0,8.0,8.0,1.0,-1.0],[54.52050755760105,100.45706175,1860.0,8.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>[[13.316516355357539,44.9441072206282,-1860.0,7.0,0.0,0.0,1.0],[44.9441072206282,50.07290573932073,0.0,7.0,0.0,1.0,1.0],[50.07290573932073,56.056504011128695,890.0,7.0,8.0,1.0,-1.0],[56.056504011128695,97.94169191378442,1860.0,7.0,9.0,0.0,-1.0]]</t>
+          <t>[[13.316516355357539,44.9441072206282,-1860.0,6.0,0.0,0.0,1.0],[44.9441072206282,50.07290573932073,0.0,7.0,0.0,1.0,1.0],[50.07290573932073,56.056504011128695,890.0,7.0,8.0,1.0,-1.0],[56.056504011128695,97.94169191378442,1860.0,5.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>[[15.387718341693397,47.453515135232266,-1860.0,6.0,0.0,0.0,1.0],[47.453515135232266,52.51653568158051,0.0,5.0,8.0,2.0,-1.0],[52.51653568158051,56.735719470204046,890.0,6.0,8.0,1.0,-1.0],[56.735719470204046,98.9275573564394,1860.0,6.0,8.0,1.0,-1.0]]</t>
+          <t>[[15.387718341693397,47.453515135232266,-1860.0,5.0,0.0,0.0,1.0],[47.453515135232266,52.51653568158051,0.0,5.0,8.0,2.0,-1.0],[52.51653568158051,56.735719470204046,890.0,5.0,8.0,1.0,-1.0],[56.735719470204046,98.9275573564394,1860.0,6.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>[[13.557467447436517,43.40177256144821,-1860.0,5.0,0.0,0.0,1.0],[43.40177256144821,46.912867280743704,-873.8504,4.0,8.0,2.0,-1.0],[46.912867280743704,51.30173567986307,0.0,4.0,8.0,2.0,-1.0],[51.30173567986307,53.935056719334696,890.0,5.0,8.0,1.0,-1.0],[53.935056719334696,100.45706175,1860.0,5.0,9.0,0.0,-1.0]]</t>
+          <t>[[13.557467447436517,43.40177256144821,-1860.0,4.0,0.0,0.0,1.0],[43.40177256144821,46.912867280743704,-873.8505,4.0,8.0,2.0,-1.0],[46.912867280743704,51.30173567986307,0.0,3.0,8.0,2.0,-1.0],[51.30173567986307,53.935056719334696,890.0,4.0,8.0,1.0,-1.0],[53.935056719334696,100.45706175,1860.0,5.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>[[14.205980775788843,43.31364776090793,-1860.0,4.0,0.0,0.0,1.0],[43.31364776090793,45.88197131841844,-873.8504,3.0,8.0,2.0,-1.0],[45.88197131841844,51.01861843343946,0.0,3.0,8.0,2.0,-1.0],[51.01861843343946,53.58694199094996,890.0,4.0,8.0,1.0,-1.0],[53.58694199094996,98.9606581736356,1860.0,4.0,9.0,0.0,-1.0]]</t>
+          <t>[[14.205980775788843,43.31364776090793,-1860.0,3.0,0.0,0.0,1.0],[43.31364776090793,45.88197131841844,-873.8505,2.0,8.0,2.0,-1.0],[45.88197131841844,51.01861843343946,0.0,2.0,8.0,2.0,-1.0],[51.01861843343946,53.58694199094996,890.0,3.0,8.0,1.0,-1.0],[53.58694199094996,98.9606581736356,1860.0,3.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>[[12.882699270253498,44.57615845506954,-1860.0,3.0,0.0,0.0,1.0],[44.57615845506954,47.21728005380421,-873.8504,2.0,8.0,2.0,-1.0],[47.21728005380421,52.49952325127355,0.0,2.0,8.0,2.0,-1.0],[52.49952325127355,55.14064485000822,890.0,3.0,8.0,1.0,-1.0],[55.14064485000822,100.03971202849762,1860.0,3.0,9.0,0.0,-1.0]]</t>
+          <t>[[12.882699270253498,44.57615845506954,-1860.0,2.0,0.0,0.0,1.0],[44.57615845506954,47.21728005380421,-873.8505,2.0,8.0,2.0,-1.0],[47.21728005380421,52.49952325127355,0.0,2.0,8.0,2.0,-1.0],[52.49952325127355,55.14064485000822,890.0,2.0,8.0,1.0,-1.0],[55.14064485000822,100.03971202849762,1860.0,2.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>[[13.562888205077785,43.40533164474804,-1860.0,2.0,0.0,0.0,1.0],[43.40533164474804,45.16076949414041,-873.8504,1.0,8.0,2.0,-1.0],[45.16076949414041,50.42708304231751,0.0,1.0,8.0,2.0,-1.0],[50.42708304231751,53.06023981640606,890.0,2.0,8.0,1.0,-1.0],[53.06023981640606,100.45706175,1860.0,2.0,9.0,0.0,-1.0]]</t>
+          <t>[[13.562888205077785,43.40533164474804,-1860.0,2.0,0.0,0.0,1.0],[43.40533164474804,45.16076949414041,-873.8505,1.0,8.0,2.0,-1.0],[45.16076949414041,50.42708304231751,0.0,1.0,8.0,2.0,-1.0],[50.42708304231751,53.06023981640606,890.0,2.0,8.0,1.0,-1.0],[53.06023981640606,100.45706175,1860.0,2.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>[[14.45151079436823,46.03344240870201,-1860.0,1.0,0.0,0.0,1.0],[46.03344240870201,47.6956493357722,-873.8504,0.0,8.0,2.0,-1.0],[47.6956493357722,52.6822701169828,0.0,0.0,8.0,2.0,-1.0],[52.6822701169828,56.837787434658296,890.0,1.0,8.0,1.0,-1.0],[56.837787434658296,96.73075368434307,1860.0,1.0,9.0,0.0,-1.0]]</t>
+          <t>[[14.45151079436823,46.03344240870201,-1860.0,1.0,0.0,0.0,1.0],[46.03344240870201,47.6956493357722,-873.8505,0.0,8.0,2.0,-1.0],[47.6956493357722,52.6822701169828,0.0,0.0,8.0,2.0,-1.0],[52.6822701169828,56.837787434658296,890.0,0.0,8.0,1.0,-1.0],[56.837787434658296,96.73075368434307,1860.0,1.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3159,11 +3159,11 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>[[13.26656992515346,50.256475547815626,-0.0,0.0,0.0,1.0,1.0],[50.256475547815626,55.54074777962451,890.0,0.0,8.0,1.0,-1.0],[55.54074777962451,100.45706175,1860.0,0.0,9.0,0.0,-1.0]]</t>
+          <t>[[13.26656992515346,50.256475547815626,0.0,0.0,0.0,1.0,1.0],[50.256475547815626,55.54074777962451,890.0,0.0,8.0,1.0,-1.0],[55.54074777962451,100.45706175,1860.0,0.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>[[14.224997611241855,40.648856611974345,-0.0,0.0,0.0,1.0,1.0],[40.648856611974345,63.663185419063936,890.0,0.0,8.0,0.0,-1.0],[63.663185419063936,98.61086990390369,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[14.224997611241855,40.648856611974345,0.0,0.0,0.0,1.0,1.0],[40.648856611974345,63.663185419063936,890.0,0.0,8.0,0.0,-1.0],[63.663185419063936,98.61086990390369,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>[[13.0631040652436,35.13228529876794,-986.1496,0.0,0.0,0.0,1.0],[35.13228529876794,43.959957792177676,-0.0,0.0,8.0,1.0,-1.0],[43.959957792177676,100.45706175,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[13.0631040652436,35.13228529876794,-986.1497,0.0,0.0,0.0,1.0],[35.13228529876794,43.959957792177676,0.0,0.0,8.0,1.0,-1.0],[43.959957792177676,100.45706175,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>[[14.093150567174522,35.902219047686,-1860.0,1.0,7.0,0.0,-1.0],[35.902219047686,42.00875822222922,-0.0,0.0,6.0,1.0,-1.0],[42.00875822222922,100.45706175,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[14.093150567174522,35.902219047686,-1860.0,1.0,7.0,0.0,-1.0],[35.902219047686,42.00875822222922,0.0,0.0,6.0,1.0,-1.0],[42.00875822222922,100.45706175,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>[[14.075358982535585,35.70465964650596,-1860.0,1.0,6.0,0.0,-1.0],[35.70465964650596,42.359829081573764,-0.0,0.0,6.0,1.0,-1.0],[42.359829081573764,96.4330807414997,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[14.075358982535585,35.70465964650596,-1860.0,1.0,6.0,0.0,-1.0],[35.70465964650596,42.359829081573764,0.0,0.0,6.0,1.0,-1.0],[42.359829081573764,96.4330807414997,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>[[13.597342608971536,34.783539008924585,-1860.0,1.0,5.0,1.0,-1.0],[34.783539008924585,41.56312185690956,-0.0,0.0,5.0,1.0,-1.0],[41.56312185690956,97.4946803527856,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[13.597342608971536,34.783539008924585,-1860.0,1.0,5.0,1.0,-1.0],[34.783539008924585,41.56312185690956,0.0,0.0,5.0,1.0,-1.0],[41.56312185690956,97.4946803527856,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>[[13.838907630315594,36.11296720663019,-1860.0,1.0,2.0,0.0,-1.0],[36.11296720663019,42.37754646246867,-0.0,0.0,2.0,1.0,-1.0],[42.37754646246867,82.74927944453887,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[13.838907630315594,36.11296720663019,-1860.0,1.0,2.0,0.0,-1.0],[36.11296720663019,42.37754646246867,0.0,0.0,2.0,1.0,-1.0],[42.37754646246867,82.74927944453887,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>[[13.812296661655028,35.755033195775056,-1860.0,1.0,1.0,0.0,-1.0],[35.755033195775056,39.93460205941696,-0.0,0.0,1.0,1.0,-1.0],[39.93460205941696,42.54683259919316,0.0,0.0,0.0,1.0,-1.0],[42.54683259919316,47.2488475707903,1860.0,0.0,0.0,0.0,-1.0],[47.2488475707903,65.53446134922366,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[13.812296661655028,35.755033195775056,-1860.0,1.0,1.0,0.0,-1.0],[35.755033195775056,40.97949427532744,0.0,0.0,1.0,1.0,-1.0],[40.97949427532744,42.54683259919316,0.0,0.0,0.0,1.0,-1.0],[42.54683259919316,47.2488475707903,1860.0,0.0,0.0,0.0,-1.0],[47.2488475707903,65.53446134922366,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3289,11 +3289,11 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>[[13.690500721491528,35.55788734116837,-1860.0,1.0,0.0,0.0,-1.0],[35.55788734116837,62.89212061576441,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[13.690500721491528,35.55788734116837,-1860.0,1.0,0.0,0.0,-1.0],[35.55788734116837,62.89212061576441,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -3302,11 +3302,11 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>[[13.361370108220429,33.697687838089095,-1860.0,1.0,0.0,0.0,-1.0],[33.697687838089095,64.98433049942551,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[13.361370108220429,33.697687838089095,-1860.0,1.0,0.0,0.0,-1.0],[33.697687838089095,64.98433049942551,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -3315,11 +3315,11 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>[[14.156169684915382,34.07776706863876,-1860.0,1.0,0.0,0.0,-1.0],[34.07776706863876,64.72637842821318,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[14.156169684915382,34.07776706863876,-1860.0,1.0,0.0,0.0,-1.0],[34.07776706863876,64.72637842821318,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -3328,11 +3328,11 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>[[13.359833766607641,29.07844754588593,-1860.0,1.0,0.0,0.0,-1.0],[29.07844754588593,61.989295146249844,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[13.359833766607641,29.07844754588593,-1860.0,1.0,0.0,0.0,-1.0],[29.07844754588593,61.989295146249844,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>[[14.32771698013276,29.117100575966113,-1860.0,8.0,0.0,0.0,1.0],[29.117100575966113,35.79617703860053,-733.6842,8.0,0.0,0.0,1.0],[35.79617703860053,39.61279216010591,0.0,8.0,8.0,3.0,-1.0],[39.61279216010591,40.089869050294084,227.85,8.0,8.0,1.0,-1.0],[40.089869050294084,61.55832910876185,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[14.32771698013276,29.117100575966113,-1860.0,7.0,0.0,0.0,1.0],[29.117100575966113,35.79617703860053,-733.6843,8.0,0.0,0.0,1.0],[35.79617703860053,39.61279216010591,0.0,8.0,8.0,3.0,-1.0],[39.61279216010591,40.089869050294084,227.85,8.0,8.0,1.0,-1.0],[40.089869050294084,61.55832910876185,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>[[12.357863091369897,33.57936852334953,-1860.0,8.0,8.0,2.0,-1.0],[33.57936852334953,36.23205670234698,-1607.5346,7.0,8.0,1.0,-1.0],[36.23205670234698,39.94582015294341,0.0,7.0,8.0,1.0,-1.0],[39.94582015294341,43.12904596774036,227.85,8.0,8.0,0.0,-1.0],[43.12904596774036,64.88108903551948,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[12.357863091369897,33.57936852334953,-1860.0,7.0,8.0,2.0,-1.0],[33.57936852334953,36.23205670234698,-1607.5347,7.0,8.0,1.0,-1.0],[36.23205670234698,39.94582015294341,0.0,7.0,8.0,1.0,-1.0],[39.94582015294341,43.12904596774036,227.85,8.0,8.0,0.0,-1.0],[43.12904596774036,64.88108903551948,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>[[11.21110265021379,35.24802977673849,-1860.0,7.0,8.0,1.0,-1.0],[35.24802977673849,35.77057167079338,-1607.5346,6.0,8.0,1.0,-1.0],[35.77057167079338,39.42836492917757,0.0,6.0,8.0,1.0,-1.0],[39.42836492917757,43.60870008161665,227.85,7.0,8.0,0.0,-1.0],[43.60870008161665,62.94275016164738,1860.0,7.0,8.0,0.0,-1.0]]</t>
+          <t>[[11.21110265021379,35.24802977673849,-1860.0,7.0,8.0,1.0,-1.0],[35.24802977673849,35.77057167079338,-1607.5347,6.0,8.0,1.0,-1.0],[35.77057167079338,39.42836492917757,0.0,6.0,8.0,1.0,-1.0],[39.42836492917757,43.60870008161665,227.85,7.0,8.0,0.0,-1.0],[43.60870008161665,62.94275016164738,1860.0,6.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>[[8.484482162591622,35.29868984702014,-1860.0,6.0,8.0,1.0,-1.0],[35.29868984702014,36.94037603178107,-1607.5346,5.0,8.0,1.0,-1.0],[36.94037603178107,41.31820585781023,0.0,5.0,8.0,1.0,-1.0],[41.31820585781023,45.14880695558573,227.85,6.0,8.0,0.0,-1.0],[45.14880695558573,62.66012625970232,1860.0,6.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.484482162591622,35.29868984702014,-1860.0,6.0,8.0,1.0,-1.0],[35.29868984702014,36.94037603178107,-1607.5347,4.0,8.0,1.0,-1.0],[36.94037603178107,41.31820585781023,0.0,5.0,8.0,1.0,-1.0],[41.31820585781023,45.14880695558573,227.85,5.0,8.0,0.0,-1.0],[45.14880695558573,62.66012625970232,1860.0,5.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>[[8.176251301373576,36.24799841734511,-1860.0,5.0,0.0,0.0,1.0],[36.24799841734511,40.178043013581124,0.0,5.0,8.0,1.0,-1.0],[40.178043013581124,41.86234784053942,227.85,5.0,8.0,0.0,-1.0],[41.86234784053942,63.75831059099721,1860.0,5.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.176251301373576,36.24799841734511,-1860.0,4.0,0.0,0.0,1.0],[36.24799841734511,40.178043013581124,0.0,4.0,8.0,1.0,-1.0],[40.178043013581124,41.86234784053942,227.85,4.0,8.0,0.0,-1.0],[41.86234784053942,63.75831059099721,1860.0,4.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>[[8.200410679129284,36.11397131683742,-1860.0,4.0,8.0,1.0,-1.0],[36.11397131683742,36.68363581964779,-1607.5346,3.0,8.0,1.0,-1.0],[36.68363581964779,40.67128733932038,0.0,3.0,8.0,1.0,-1.0],[40.67128733932038,41.81061634494112,227.85,4.0,8.0,0.0,-1.0],[41.81061634494112,64.59719645735592,1860.0,4.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.200410679129284,36.11397131683742,-1860.0,3.0,8.0,1.0,-1.0],[36.11397131683742,36.68363581964779,-1607.5347,2.0,8.0,1.0,-1.0],[36.68363581964779,40.67128733932038,0.0,2.0,8.0,1.0,-1.0],[40.67128733932038,41.81061634494112,227.85,3.0,8.0,0.0,-1.0],[41.81061634494112,64.59719645735592,1860.0,3.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>[[8.911479795307043,35.554552601145645,-1860.0,3.0,0.0,0.0,1.0],[35.554552601145645,37.72949731998961,-733.6842,3.0,0.0,0.0,1.0],[37.72949731998961,42.07938675767755,0.0,3.0,8.0,1.0,-1.0],[42.07938675767755,42.623122937388544,227.85,3.0,8.0,0.0,-1.0],[42.623122937388544,62.74136158669524,1860.0,3.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.911479795307043,35.554552601145645,-1860.0,2.0,0.0,0.0,1.0],[35.554552601145645,37.72949731998961,-733.6843,2.0,0.0,0.0,1.0],[37.72949731998961,42.07938675767755,0.0,2.0,8.0,1.0,-1.0],[42.07938675767755,42.623122937388544,227.85,2.0,8.0,0.0,-1.0],[42.623122937388544,62.74136158669524,1860.0,2.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>[[8.590642544444625,36.4489796238833,-1860.0,2.0,8.0,3.0,-1.0],[36.4489796238833,37.56331310706084,-1607.5346,1.0,8.0,1.0,-1.0],[37.56331310706084,42.020647039771035,0.0,1.0,8.0,1.0,-1.0],[42.020647039771035,43.692147264537354,227.85,2.0,8.0,0.0,-1.0],[43.692147264537354,63.75014996173319,1860.0,2.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.590642544444625,36.4489796238833,-1860.0,2.0,8.0,3.0,-1.0],[36.4489796238833,37.56331310706084,-1607.5347,1.0,8.0,1.0,-1.0],[37.56331310706084,42.020647039771035,0.0,1.0,8.0,1.0,-1.0],[42.020647039771035,43.692147264537354,227.85,2.0,8.0,0.0,-1.0],[43.692147264537354,63.75014996173319,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>[[7.726651746095345,35.40296443649466,-1860.0,1.0,0.0,0.0,1.0],[35.40296443649466,37.03098283004757,-733.6842,1.0,0.0,0.0,1.0],[37.03098283004757,41.3723652128553,0.0,1.0,8.0,3.0,-1.0],[41.3723652128553,44.08572920211014,227.85,1.0,8.0,0.0,-1.0],[44.08572920211014,61.451258733341085,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[7.726651746095345,35.40296443649466,-1860.0,1.0,0.0,0.0,1.0],[35.40296443649466,37.03098283004757,-733.6843,0.0,0.0,0.0,1.0],[37.03098283004757,41.3723652128553,0.0,1.0,8.0,3.0,-1.0],[41.3723652128553,44.08572920211014,227.85,0.0,8.0,0.0,-1.0],[44.08572920211014,61.451258733341085,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>[[8.359104983231369,36.184511379983604,-733.6842,0.0,0.0,0.0,1.0],[36.184511379983604,40.08006827552892,0.0,0.0,8.0,1.0,-1.0],[40.08006827552892,43.41911704313919,227.85,0.0,8.0,0.0,-1.0],[43.41911704313919,63.45340964880081,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.359104983231369,36.184511379983604,-733.6844,0.0,0.0,0.0,1.0],[36.184511379983604,40.08006827552892,0.0,0.0,8.0,1.0,-1.0],[40.08006827552892,43.41911704313919,227.85,0.0,8.0,0.0,-1.0],[43.41911704313919,63.45340964880081,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>[[8.39296009039569,35.209335418135765,-733.6842,0.0,0.0,0.0,1.0],[35.209335418135765,39.04024617924149,0.0,0.0,8.0,2.0,-1.0],[39.04024617924149,42.323883974474974,227.85,0.0,8.0,0.0,-1.0],[42.323883974474974,62.572983711748094,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.39296009039569,35.209335418135765,-733.6844,0.0,0.0,0.0,1.0],[35.209335418135765,39.04024617924149,0.0,0.0,8.0,2.0,-1.0],[39.04024617924149,42.323883974474974,227.85,0.0,8.0,0.0,-1.0],[42.323883974474974,62.572983711748094,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>[[8.381231291361221,34.28626217253296,-1860.0,1.0,2.0,0.0,-1.0],[34.28626217253296,36.67749579233343,-1808.4765,0.0,2.0,1.0,-1.0],[36.67749579233343,40.66288515866755,0.0,0.0,1.0,2.0,-1.0],[40.66288515866755,47.83658601806895,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[8.381231291361221,34.28626217253296,-1860.0,0.0,2.0,0.0,-1.0],[34.28626217253296,36.67749579233343,-1808.4765,0.0,2.0,1.0,-1.0],[36.67749579233343,40.66288515866755,0.0,0.0,1.0,2.0,-1.0],[40.66288515866755,47.83658601806895,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>[[8.15703010922491,34.94278558576943,-1860.0,1.0,1.0,1.0,-1.0],[34.94278558576943,36.043570057408246,-1808.4765,0.0,1.0,1.0,-1.0],[36.043570057408246,39.71285162953763,0.0,0.0,0.0,2.0,-1.0],[39.71285162953763,44.482917673305835,227.85,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[8.15703010922491,34.94278558576943,-1860.0,1.0,1.0,1.0,-1.0],[34.94278558576943,36.043570057408246,-1808.4765,0.0,1.0,1.0,-1.0],[36.043570057408246,39.71285162953763,0.0,0.0,0.0,2.0,-1.0],[39.71285162953763,42.2813487300282,227.85,0.0,0.0,0.0,-1.0],[42.2813487300282,44.482917673305835,227.8501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -3614,11 +3614,11 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>[[8.214199054710384,35.800383175827015,-1860.0,1.0,0.0,0.0,-1.0],[35.800383175827015,44.148833633533364,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[8.214199054710384,35.800383175827015,-1860.0,1.0,0.0,0.0,-1.0],[35.800383175827015,44.148833633533364,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -3627,11 +3627,11 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>[[8.231776226073956,33.37978573773485,-1860.0,1.0,0.0,0.0,-1.0],[33.37978573773485,45.39077535524453,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[8.231776226073956,33.37978573773485,-1860.0,1.0,0.0,0.0,-1.0],[33.37978573773485,45.39077535524453,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -3640,11 +3640,11 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>[[8.484932719365416,27.172711165237473,-1860.0,1.0,0.0,0.0,-1.0],[27.172711165237473,46.241872844698754,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[8.484932719365416,27.172711165237473,-1860.0,1.0,0.0,0.0,-1.0],[27.172711165237473,46.241872844698754,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>[[8.444957811119819,24.641902689125708,-1860.0,8.0,0.0,0.0,1.0],[24.641902689125708,30.81216740455652,-733.6842,8.0,0.0,0.0,1.0],[30.81216740455652,33.89729976227193,0.0,8.0,0.0,1.0,1.0],[33.89729976227193,36.21114903055849,1016.5,9.0,0.0,0.0,1.0],[36.21114903055849,46.62347073784799,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[8.444957811119819,24.641902689125708,-1860.0,7.0,0.0,0.0,1.0],[24.641902689125708,30.81216740455652,-733.6843,8.0,0.0,0.0,1.0],[30.81216740455652,33.89729976227193,0.0,7.0,0.0,1.0,1.0],[33.89729976227193,36.21114903055849,1016.5,9.0,0.0,0.0,1.0],[36.21114903055849,46.62347073784799,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>[[8.456687325990359,25.67480672719658,-1860.0,7.0,0.0,0.0,1.0],[25.67480672719658,30.07092231899391,-733.6842,7.0,0.0,0.0,1.0],[30.07092231899391,33.36800901284191,0.0,7.0,0.0,1.0,1.0],[33.36800901284191,35.56606680874057,1016.5,8.0,0.0,0.0,1.0],[35.56606680874057,44.72464095831835,1860.0,8.0,9.0,2.0,-1.0]]</t>
+          <t>[[8.456687325990359,25.67480672719658,-1860.0,6.0,0.0,0.0,1.0],[25.67480672719658,30.07092231899391,-733.6843,6.0,0.0,0.0,1.0],[30.07092231899391,33.36800901284191,0.0,6.0,0.0,1.0,1.0],[33.36800901284191,35.56606680874057,1016.5,7.0,0.0,0.0,1.0],[35.56606680874057,44.72464095831835,1860.0,7.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>[[8.16146712689788,25.243628411246725,-1860.0,6.0,0.0,0.0,1.0],[25.243628411246725,27.471736404857445,-733.6842,6.0,0.0,0.0,1.0],[27.471736404857445,30.442547063005065,0.0,6.0,0.0,1.0,1.0],[30.442547063005065,36.01281704703187,1016.5,7.0,0.0,0.0,1.0],[36.01281704703187,44.92524902147474,1860.0,7.0,9.0,0.0,-1.0]]</t>
+          <t>[[8.16146712689788,25.243628411246725,-1860.0,6.0,0.0,0.0,1.0],[25.243628411246725,27.471736404857445,-733.6843,5.0,0.0,0.0,1.0],[27.471736404857445,30.442547063005065,0.0,6.0,0.0,1.0,1.0],[30.442547063005065,36.01281704703187,1016.5,7.0,0.0,0.0,1.0],[36.01281704703187,44.92524902147474,1860.0,7.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>[[8.595806879666561,24.820478435008496,-1860.0,5.0,0.0,0.0,1.0],[24.820478435008496,27.642160444633184,-733.6842,5.0,0.0,0.0,1.0],[27.642160444633184,30.46384245425787,0.0,5.0,0.0,1.0,1.0],[30.46384245425787,36.459916724710325,1016.5,6.0,0.0,0.0,1.0],[36.459916724710325,43.514121748772034,1860.0,6.0,9.0,3.0,-1.0]]</t>
+          <t>[[8.595806879666561,24.820478435008496,-1860.0,4.0,0.0,0.0,1.0],[24.820478435008496,27.642160444633184,-733.6843,4.0,0.0,0.0,1.0],[27.642160444633184,30.46384245425787,0.0,4.0,0.0,1.0,1.0],[30.46384245425787,36.459916724710325,1016.5,4.0,0.0,0.0,1.0],[36.459916724710325,43.514121748772034,1860.0,5.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>[[12.76980788055936,25.119448349497155,-1860.0,4.0,0.0,0.0,1.0],[25.119448349497155,29.579040741058023,-733.6842,4.0,0.0,0.0,1.0],[29.579040741058023,32.66645085829247,0.0,4.0,0.0,1.0,1.0],[32.66645085829247,36.78299768127174,1016.5,5.0,0.0,0.0,1.0],[36.78299768127174,46.73131917013829,1860.0,5.0,9.0,1.0,-1.0]]</t>
+          <t>[[12.76980788055936,25.119448349497155,-1860.0,3.0,0.0,0.0,1.0],[25.119448349497155,29.579040741058023,-733.6843,3.0,0.0,0.0,1.0],[29.579040741058023,32.66645085829247,0.0,3.0,0.0,1.0,1.0],[32.66645085829247,36.78299768127174,1016.5,4.0,0.0,0.0,1.0],[36.78299768127174,46.73131917013829,1860.0,4.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>[[15.99501225267529,24.866380518087936,-1860.0,3.0,0.0,0.0,1.0],[24.866380518087936,27.925473023402642,-733.6842,3.0,0.0,0.0,1.0],[27.925473023402642,30.984565528717347,0.0,3.0,0.0,1.0,1.0],[30.984565528717347,34.65547653509499,1016.5,4.0,0.0,0.0,1.0],[34.65547653509499,46.28002805529087,1860.0,4.0,9.0,4.0,-1.0]]</t>
+          <t>[[15.99501225267529,24.866380518087936,-1860.0,2.0,0.0,0.0,1.0],[24.866380518087936,27.925473023402642,-733.6843,2.0,0.0,0.0,1.0],[27.925473023402642,30.984565528717347,0.0,2.0,0.0,1.0,1.0],[30.984565528717347,34.65547653509499,1016.5,3.0,0.0,0.0,1.0],[34.65547653509499,46.28002805529087,1860.0,3.0,9.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>[[15.45241967339454,25.600846042245905,-1860.0,2.0,0.0,0.0,1.0],[25.600846042245905,28.500396433346296,-733.6842,2.0,0.0,0.0,1.0],[28.500396433346296,31.399946824446687,0.0,2.0,0.0,1.0,1.0],[31.399946824446687,36.039227450207306,1016.5,3.0,0.0,0.0,1.0],[36.039227450207306,44.1579685452884,1860.0,3.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.45241967339454,25.600846042245905,-1860.0,2.0,0.0,0.0,1.0],[25.600846042245905,28.500396433346296,-733.6843,2.0,0.0,0.0,1.0],[28.500396433346296,31.399946824446687,0.0,1.0,0.0,1.0,1.0],[31.399946824446687,36.039227450207306,1016.5,2.0,0.0,0.0,1.0],[36.039227450207306,44.1579685452884,1860.0,2.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>[[15.99518482713048,25.395510763969092,-1860.0,1.0,0.0,0.0,1.0],[25.395510763969092,28.33311261923116,-733.6842,1.0,0.0,0.0,1.0],[28.33311261923116,31.564474660019435,0.0,1.0,0.0,1.0,1.0],[31.564474660019435,36.26463762843874,1016.5,2.0,0.0,0.0,1.0],[36.26463762843874,45.07744319422494,1860.0,2.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.99518482713048,25.395510763969092,-1860.0,1.0,0.0,0.0,1.0],[25.395510763969092,28.33311261923116,-733.6843,0.0,0.0,0.0,1.0],[28.33311261923116,31.564474660019435,0.0,1.0,0.0,1.0,1.0],[31.564474660019435,36.26463762843874,1016.5,2.0,0.0,0.0,1.0],[36.26463762843874,45.07744319422494,1860.0,2.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -3783,11 +3783,11 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>[[15.336249492833469,28.71106901098448,-733.6842,0.0,0.0,0.0,1.0],[28.71106901098448,31.750800719655167,0.0,0.0,0.0,1.0,1.0],[31.750800719655167,36.00642511179412,1016.5,1.0,0.0,0.0,1.0],[36.00642511179412,45.42959340867324,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.336249492833469,25.975310473180862,-733.6844,0.0,0.0,0.0,1.0],[25.975310473180862,28.71106901098448,-733.6843,0.0,0.0,0.0,1.0],[28.71106901098448,31.750800719655167,0.0,0.0,0.0,1.0,1.0],[31.750800719655167,36.00642511179412,1016.5,1.0,0.0,0.0,1.0],[36.00642511179412,45.42959340867324,1860.0,0.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>-733.6842</v>
+        <v>-733.6844</v>
       </c>
     </row>
     <row r="259">
@@ -3796,11 +3796,11 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>[[16.06438042500798,36.96599093567612,-0.0,0.0,0.0,1.0,1.0],[36.96599093567612,37.25629108165762,890.0,0.0,8.0,3.0,-1.0],[37.25629108165762,44.804094877176674,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[16.06438042500798,36.96599093567612,0.0,0.0,0.0,1.0,1.0],[36.96599093567612,37.25629108165762,890.0,0.0,8.0,3.0,-1.0],[37.25629108165762,44.804094877176674,1860.0,0.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>[[15.719847462416912,35.42905634531299,-0.0,0.0,0.0,1.0,1.0],[35.42905634531299,36.555296852907055,890.0,0.0,8.0,2.0,-1.0],[36.555296852907055,43.59430002536994,1860.0,0.0,9.0,1.0,-1.0]]</t>
+          <t>[[15.719847462416912,35.42905634531299,0.0,0.0,0.0,1.0,1.0],[35.42905634531299,36.555296852907055,890.0,0.0,8.0,2.0,-1.0],[36.555296852907055,43.59430002536994,1860.0,0.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>[[15.467816108780807,31.68783998259861,-1860.0,1.0,8.0,2.0,-1.0],[31.68783998259861,32.27765903255562,-1074.7923,0.0,8.0,1.0,-1.0],[32.27765903255562,35.816573332297686,0.0,0.0,7.0,2.0,-1.0],[35.816573332297686,36.7013019072332,890.0,0.0,7.0,0.0,-1.0],[36.7013019072332,44.66385908165285,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[15.467816108780807,31.68783998259861,-1860.0,1.0,8.0,2.0,-1.0],[31.68783998259861,32.27765903255562,-1074.7921,0.0,8.0,1.0,-1.0],[32.27765903255562,35.816573332297686,0.0,0.0,7.0,2.0,-1.0],[35.816573332297686,36.7013019072332,890.0001,0.0,7.0,0.0,-1.0],[36.7013019072332,44.66385908165285,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>[[15.052156947622725,31.152124706297208,-1860.0,1.0,7.0,1.0,-1.0],[31.152124706297208,34.431747768249416,0.0,0.0,6.0,1.0,-1.0],[34.431747768249416,35.326190421509104,890.0,0.0,6.0,0.0,-1.0],[35.326190421509104,44.568764505192604,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[15.052156947622725,31.152124706297208,-1860.0,1.0,7.0,1.0,-1.0],[31.152124706297208,34.431747768249416,0.0,0.0,6.0,1.0,-1.0],[34.431747768249416,35.326190421509104,890.0001,0.0,6.0,0.0,-1.0],[35.326190421509104,44.568764505192604,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>[[15.640541201465409,30.235122709197704,-1860.0,1.0,7.0,1.0,-1.0],[30.235122709197704,30.515787738192554,-1074.7923,0.0,7.0,0.0,-1.0],[30.515787738192554,33.603103057135925,0.0,0.0,6.0,1.0,-1.0],[33.603103057135925,35.28709323110503,890.0,0.0,6.0,1.0,-1.0],[35.28709323110503,43.426379071955736,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[15.640541201465409,30.235122709197704,-1860.0,1.0,7.0,1.0,-1.0],[30.235122709197704,30.515787738192554,-1074.7921,0.0,7.0,0.0,-1.0],[30.515787738192554,33.603103057135925,0.0,0.0,6.0,1.0,-1.0],[33.603103057135925,35.28709323110503,890.0001,0.0,6.0,1.0,-1.0],[35.28709323110503,43.426379071955736,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>[[14.901878560461185,30.476758797770316,-1860.0,1.0,7.0,0.0,-1.0],[30.476758797770316,30.776275725410876,-1074.7923,0.0,7.0,0.0,-1.0],[30.776275725410876,34.07096192945704,0.0,0.0,6.0,1.0,-1.0],[34.07096192945704,34.370478857097595,890.0,0.0,6.0,0.0,-1.0],[34.370478857097595,44.554054396876644,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[14.901878560461185,30.476758797770316,-1860.0,1.0,7.0,0.0,-1.0],[30.476758797770316,30.776275725410876,-1074.7921,0.0,7.0,0.0,-1.0],[30.776275725410876,34.07096192945704,0.0,0.0,6.0,1.0,-1.0],[34.07096192945704,34.370478857097595,890.0001,0.0,6.0,0.0,-1.0],[34.370478857097595,44.554054396876644,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>[[15.912450500068951,30.96146709076174,-1860.0,1.0,6.0,0.0,-1.0],[30.96146709076174,31.2081722807731,-1074.7923,0.0,6.0,1.0,-1.0],[31.2081722807731,34.41533975092074,0.0,0.0,5.0,2.0,-1.0],[34.41533975092074,35.40216051096617,890.0,0.0,5.0,0.0,-1.0],[35.40216051096617,40.33626431119331,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[15.912450500068951,30.96146709076174,-1860.0,1.0,6.0,0.0,-1.0],[30.96146709076174,31.2081722807731,-1074.7921,0.0,6.0,1.0,-1.0],[31.2081722807731,34.41533975092074,0.0,0.0,5.0,2.0,-1.0],[34.41533975092074,35.40216051096617,890.0001,0.0,5.0,0.0,-1.0],[35.40216051096617,40.33626431119331,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>[[16.135123603165802,20.210664734416042,-1860.0,9.0,13.0,1.0,0.0],[20.210664734416042,30.17309861080552,-1074.7923,0.0,6.0,0.0,-1.0],[30.17309861080552,33.56938288684739,0.0,0.0,5.0,1.0,-1.0],[33.56938288684739,34.022220790319636,890.0,0.0,5.0,1.0,-1.0],[34.022220790319636,38.55059982504213,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[16.135123603165802,20.210664734416042,-1860.0,9.0,13.0,1.0,0.0],[20.210664734416042,30.17309861080552,-1074.7921,0.0,6.0,0.0,-1.0],[30.17309861080552,33.56938288684739,0.0,0.0,5.0,1.0,-1.0],[33.56938288684739,34.022220790319636,890.0001,0.0,5.0,1.0,-1.0],[34.022220790319636,38.55059982504213,1860.0,0.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>[[15.675729073966822,20.3956468169795,-1860.0,9.0,5.0,0.0,1.0],[20.3956468169795,21.74419474355455,-1808.4765,9.0,5.0,0.0,1.0],[21.74419474355455,30.284998278529876,-1074.7923,0.0,5.0,0.0,-1.0],[30.284998278529876,33.656368094967505,0.0,0.0,4.0,1.0,-1.0],[33.656368094967505,34.78015803378005,890.0,0.0,4.0,1.0,-1.0],[34.78015803378005,37.92676986245517,1860.0,0.0,4.0,1.0,-1.0]]</t>
+          <t>[[15.675729073966822,20.3956468169795,-1860.0,9.0,5.0,0.0,1.0],[20.3956468169795,21.74419474355455,-1808.4763,9.0,5.0,0.0,1.0],[21.74419474355455,30.284998278529876,-1074.7921,0.0,5.0,0.0,-1.0],[30.284998278529876,33.656368094967505,0.0,0.0,4.0,1.0,-1.0],[33.656368094967505,34.78015803378005,890.0001,0.0,4.0,1.0,-1.0],[34.78015803378005,37.92676986245517,1860.0,0.0,4.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -3913,11 +3913,11 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>[[15.870474893686131,21.02302767466669,-1860.0,9.0,4.0,0.0,1.0],[21.02302767466669,21.435231897145133,-1808.4765,9.0,4.0,0.0,1.0],[21.435231897145133,29.26711212423558,-1074.7923,0.0,4.0,0.0,-1.0],[29.26711212423558,32.56474590406314,0.0,0.0,3.0,1.0,-1.0],[32.56474590406314,35.03797123893381,890.0,0.0,3.0,1.0,-1.0],[35.03797123893381,36.27458390636914,1860.0,0.0,3.0,1.0,-1.0]]</t>
+          <t>[[15.870474893686131,21.02302767466669,-1860.0,9.0,4.0,0.0,1.0],[21.02302767466669,21.435231897145133,-1808.4763,9.0,4.0,0.0,1.0],[21.435231897145133,29.26711212423558,-1074.7921,0.0,4.0,0.0,-1.0],[29.26711212423558,32.56474590406314,0.0,0.0,3.0,1.0,-1.0],[32.56474590406314,35.03797123893381,890.0001,0.0,3.0,1.0,-1.0],[35.03797123893381,36.27458390636914,1860.0,0.0,3.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>890</v>
+        <v>890.0001</v>
       </c>
     </row>
     <row r="269">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>[[15.724542238620721,19.698849272077297,-1860.0,9.0,3.0,0.0,1.0],[19.698849272077297,20.535545489647102,-733.6842,9.0,3.0,0.0,1.0],[20.535545489647102,33.922684970763996,0.0,0.0,3.0,1.0,-1.0],[33.922684970763996,36.43277362347341,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[15.724542238620721,19.698849272077297,-1860.0,9.0,3.0,0.0,1.0],[19.698849272077297,20.535545489647102,-733.6842,9.0,3.0,0.0,1.0],[20.535545489647102,33.922684970763996,0.0,0.0,3.0,1.0,-1.0],[33.922684970763996,36.43277362347341,1860.0,0.0,3.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>[[15.360268596773755,20.37500219047014,-1860.0,9.0,2.0,0.0,1.0],[20.37500219047014,20.976770221713707,-733.6842,9.0,2.0,0.0,1.0],[20.976770221713707,32.61095215908933,0.0,0.0,2.0,1.0,-1.0],[32.61095215908933,35.21861362781145,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[15.360268596773755,20.37500219047014,-1860.0,8.0,2.0,0.0,1.0],[20.37500219047014,20.976770221713707,-733.6842,9.0,2.0,0.0,1.0],[20.976770221713707,32.61095215908933,0.0,0.0,2.0,1.0,-1.0],[32.61095215908933,35.21861362781145,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>[[15.952667004090516,18.318021832612608,-1860.0,9.0,1.0,0.0,1.0],[18.318021832612608,20.28915085638102,-532.7424,8.0,1.0,1.0,1.0],[20.28915085638102,22.45739278252627,0.0,8.0,1.0,1.0,1.0],[22.45739278252627,24.42852180629468,1197.85,9.0,1.0,0.0,1.0],[24.42852180629468,35.466844339397774,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[15.952667004090516,18.318021832612608,-1860.0,8.0,1.0,0.0,1.0],[18.318021832612608,20.28915085638102,-532.7423,8.0,1.0,1.0,1.0],[20.28915085638102,22.45739278252627,0.0,8.0,1.0,1.0,1.0],[22.45739278252627,24.42852180629468,1197.85,9.0,1.0,0.0,1.0],[24.42852180629468,35.466844339397774,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>[[15.976639529397236,18.698189764717316,-1860.0,8.0,0.0,1.0,1.0],[18.698189764717316,19.670171991617345,-532.7424,8.0,0.0,1.0,1.0],[19.670171991617345,21.80853289079741,0.0,8.0,0.0,1.0,1.0],[21.80853289079741,23.55810089921746,1197.85,9.0,0.0,0.0,1.0],[23.55810089921746,35.22188762201781,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[15.976639529397236,18.698189764717316,-1860.0,8.0,0.0,1.0,1.0],[18.698189764717316,19.670171991617345,-532.7423,8.0,0.0,1.0,1.0],[19.670171991617345,21.80853289079741,0.0,8.0,0.0,1.0,1.0],[21.80853289079741,23.55810089921746,1197.85,9.0,0.0,0.0,1.0],[23.55810089921746,35.22188762201781,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>[[15.832286293910919,21.978467773638812,-1860.0,9.0,8.0,3.0,-1.0],[21.978467773638812,22.13212231063201,-1607.5347,8.0,8.0,4.0,-1.0],[22.13212231063201,31.044085456237454,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[15.832286293910919,21.978467773638812,-1860.0,8.0,8.0,3.0,-1.0],[21.978467773638812,22.13212231063201,-1607.5346,7.0,8.0,4.0,-1.0],[22.13212231063201,31.044085456237454,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>[[12.091956485902598,21.76498431541698,-1860.0,8.0,8.0,3.0,-1.0],[21.76498431541698,21.958444872007266,-1607.5347,7.0,8.0,1.0,-1.0],[21.958444872007266,24.473432107681006,0.0,7.0,7.0,2.0,-1.0],[24.473432107681006,31.244551588341075,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[12.091956485902598,21.76498431541698,-1860.0,7.0,8.0,3.0,-1.0],[21.76498431541698,21.958444872007266,-1607.5346,7.0,8.0,1.0,-1.0],[21.958444872007266,24.473432107681006,0.0,6.0,7.0,2.0,-1.0],[24.473432107681006,31.244551588341075,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>[[10.945183828414104,22.071508761142717,-1860.0,7.0,8.0,3.0,-1.0],[22.071508761142717,22.29403525979729,-1607.5347,6.0,8.0,4.0,-1.0],[22.29403525979729,24.741826744997585,0.0,6.0,7.0,5.0,-1.0],[24.741826744997585,25.18687974230673,409.2,6.0,7.0,4.0,-1.0],[25.18687974230673,32.97530719521676,1860.0,6.0,7.0,4.0,-1.0]]</t>
+          <t>[[10.945183828414104,22.071508761142717,-1860.0,7.0,8.0,3.0,-1.0],[22.071508761142717,22.29403525979729,-1607.5346,6.0,8.0,4.0,-1.0],[22.29403525979729,24.741826744997585,0.0,6.0,7.0,5.0,-1.0],[24.741826744997585,25.18687974230673,409.2,6.0,7.0,4.0,-1.0],[25.18687974230673,32.97530719521676,1860.0,4.0,7.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>[[9.65376696164116,21.75944995118528,-1860.0,6.0,8.0,3.0,-1.0],[21.75944995118528,24.370479615596757,0.0,5.0,7.0,5.0,-1.0],[24.370479615596757,24.845212281853392,409.2,5.0,7.0,4.0,-1.0],[24.845212281853392,33.153033941344454,1860.0,5.0,8.0,3.0,-1.0]]</t>
+          <t>[[9.65376696164116,21.75944995118528,-1860.0,5.0,8.0,3.0,-1.0],[21.75944995118528,24.370479615596757,0.0,5.0,7.0,5.0,-1.0],[24.370479615596757,24.845212281853392,409.2,5.0,7.0,4.0,-1.0],[24.845212281853392,33.153033941344454,1860.0,5.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>[[9.850265458890377,22.098639673055978,-1860.0,5.0,8.0,4.0,-1.0],[22.098639673055978,22.544035099025635,-1607.5347,4.0,8.0,4.0,-1.0],[22.544035099025635,24.993709941858754,0.0,4.0,8.0,4.0,-1.0],[24.993709941858754,25.439105367828414,227.85,5.0,8.0,3.0,-1.0],[25.439105367828414,31.897339044388456,1860.0,5.0,8.0,3.0,-1.0]]</t>
+          <t>[[9.850265458890377,22.098639673055978,-1860.0,5.0,8.0,4.0,-1.0],[22.098639673055978,22.544035099025635,-1607.5346,3.0,8.0,4.0,-1.0],[22.544035099025635,24.993709941858754,0.0,3.0,8.0,4.0,-1.0],[24.993709941858754,25.439105367828414,227.85,4.0,8.0,3.0,-1.0],[25.439105367828414,31.897339044388456,1860.0,5.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>[[7.630236145808632,21.91668362163247,-1860.0,4.0,8.0,3.0,-1.0],[21.91668362163247,22.147110193823174,-1607.5347,3.0,8.0,4.0,-1.0],[22.147110193823174,24.68180248792095,0.0,3.0,7.0,5.0,-1.0],[24.68180248792095,30.442466792688627,1860.0,3.0,8.0,4.0,-1.0]]</t>
+          <t>[[7.630236145808632,21.91668362163247,-1860.0,3.0,8.0,3.0,-1.0],[21.91668362163247,22.147110193823174,-1607.5346,2.0,8.0,4.0,-1.0],[22.147110193823174,24.68180248792095,0.0,3.0,7.0,5.0,-1.0],[24.68180248792095,30.442466792688627,1860.0,2.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>[[-0.6336587098386811,21.454726636478632,-1860.0,3.0,8.0,3.0,-1.0],[21.454726636478632,22.114081422935865,-1607.5347,2.0,8.0,4.0,-1.0],[22.114081422935865,24.421823175536183,0.0,2.0,7.0,5.0,-1.0],[24.421823175536183,25.410855355222033,409.2,2.0,7.0,5.0,-1.0],[25.410855355222033,32.00440321979436,1860.0,2.0,7.0,5.0,-1.0]]</t>
+          <t>[[-0.6336587098386811,21.454726636478632,-1860.0,2.0,8.0,3.0,-1.0],[21.454726636478632,22.114081422935865,-1607.5346,2.0,8.0,4.0,-1.0],[22.114081422935865,24.421823175536183,0.0,2.0,7.0,5.0,-1.0],[24.421823175536183,25.410855355222033,409.2,2.0,7.0,5.0,-1.0],[25.410855355222033,32.00440321979436,1860.0,1.0,7.0,5.0,-1.0]]</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>[[-2.539888137032523,22.05875559180121,-1860.0,2.0,8.0,3.0,-1.0],[22.05875559180121,22.40521536262985,-1607.5347,1.0,8.0,4.0,-1.0],[22.40521536262985,24.83043375843036,0.0,1.0,7.0,5.0,-1.0],[24.83043375843036,31.759629175003248,1860.0,1.0,7.0,5.0,-1.0]]</t>
+          <t>[[-2.539888137032523,22.05875559180121,-1860.0,2.0,8.0,3.0,-1.0],[22.05875559180121,22.40521536262985,-1607.5346,1.0,8.0,4.0,-1.0],[22.40521536262985,24.83043375843036,0.0,1.0,7.0,5.0,-1.0],[24.83043375843036,31.759629175003248,1860.0,0.0,7.0,5.0,-1.0]]</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>[[-8.332828864608409,22.198992470804722,-733.6842,0.0,0.0,0.0,1.0],[22.198992470804722,24.64153817763777,0.0,0.0,8.0,2.0,-1.0],[24.64153817763777,31.969175298136925,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-8.332828864608409,22.198992470804722,-733.6843,0.0,0.0,0.0,1.0],[22.198992470804722,24.64153817763777,0.0,0.0,8.0,2.0,-1.0],[24.64153817763777,31.969175298136925,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>[[-9.702933227245694,20.81253118026722,-733.6842,0.0,0.0,0.0,1.0],[20.81253118026722,23.28675802411962,0.0,0.0,8.0,2.0,-1.0],[23.28675802411962,23.699129164761686,227.85,0.0,8.0,1.0,-1.0],[23.699129164761686,31.121809696318884,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[-9.702933227245694,20.81253118026722,-733.6843,0.0,0.0,0.0,1.0],[20.81253118026722,23.28675802411962,0.0,0.0,8.0,2.0,-1.0],[23.28675802411962,23.699129164761686,227.85,0.0,8.0,1.0,-1.0],[23.699129164761686,31.121809696318884,1860.0,0.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>[[-8.60600868042424,20.667100587490488,-1860.0,1.0,7.0,0.0,-1.0],[20.667100587490488,21.792989405487205,-1808.4765,0.0,7.0,1.0,-1.0],[21.792989405487205,24.044767041480647,0.0,0.0,6.0,2.0,-1.0],[24.044767041480647,24.7953595868118,227.85,0.0,6.0,1.0,-1.0],[24.7953595868118,28.548322313467526,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[-8.60600868042424,20.667100587490488,-1860.0,1.0,7.0,0.0,-1.0],[20.667100587490488,21.792989405487205,-1808.4764,0.0,7.0,1.0,-1.0],[21.792989405487205,24.044767041480647,0.0,0.0,6.0,2.0,-1.0],[24.044767041480647,24.7953595868118,227.85,0.0,6.0,1.0,-1.0],[24.7953595868118,28.548322313467526,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>[[-8.495658764577326,21.080942629242358,-1860.0,1.0,6.0,0.0,-1.0],[21.080942629242358,21.811229083410744,-1808.4765,0.0,6.0,1.0,-1.0],[21.811229083410744,24.3672316730001,0.0,0.0,5.0,2.0,-1.0],[24.3672316730001,25.097518127168485,227.85,0.0,5.0,2.0,-1.0],[25.097518127168485,27.653520716757843,1860.0,0.0,5.0,2.0,-1.0]]</t>
+          <t>[[-8.495658764577326,21.080942629242358,-1860.0,1.0,6.0,0.0,-1.0],[21.080942629242358,21.811229083410744,-1808.4764,0.0,6.0,1.0,-1.0],[21.811229083410744,24.3672316730001,0.0,0.0,5.0,2.0,-1.0],[24.3672316730001,25.097518127168485,227.85,0.0,5.0,2.0,-1.0],[25.097518127168485,27.653520716757843,1860.0,0.0,5.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>[[-8.695105961896813,20.759385942072143,-1860.0,1.0,6.0,0.0,-1.0],[20.759385942072143,21.52443767983757,-1808.4765,0.0,6.0,0.0,-1.0],[21.52443767983757,23.81959289313385,0.0,0.0,5.0,1.0,-1.0],[23.81959289313385,24.202118762016568,227.85,0.0,5.0,1.0,-1.0],[24.202118762016568,29.174955057491847,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[-8.695105961896813,20.759385942072143,-1860.0,1.0,6.0,0.0,-1.0],[20.759385942072143,21.52443767983757,-1808.4764,0.0,6.0,0.0,-1.0],[21.52443767983757,23.81959289313385,0.0,0.0,5.0,1.0,-1.0],[23.81959289313385,24.202118762016568,227.85,0.0,5.0,1.0,-1.0],[24.202118762016568,29.174955057491847,1860.0,0.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>[[-8.786559521560193,20.538598603604882,-1860.0,1.0,4.0,0.0,-1.0],[20.538598603604882,21.35318632930391,-1808.4765,0.0,4.0,0.0,-1.0],[21.35318632930391,23.796949506401,0.0,0.0,3.0,1.0,-1.0],[23.796949506401,31.53553290054178,1860.0,0.0,3.0,1.0,-1.0]]</t>
+          <t>[[-8.786559521560193,20.538598603604882,-1860.0,1.0,4.0,0.0,-1.0],[20.538598603604882,21.35318632930391,-1808.4764,0.0,4.0,0.0,-1.0],[21.35318632930391,23.796949506401,0.0,0.0,3.0,1.0,-1.0],[23.796949506401,31.53553290054178,1860.0,0.0,3.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>[[-8.551771677351692,20.026235174745132,-1860.0,2.0,3.0,1.0,-1.0],[20.026235174745132,21.28702959469058,-1808.4765,0.0,3.0,0.0,-1.0],[21.28702959469058,23.80861843458148,0.0,0.0,2.0,1.0,-1.0],[23.80861843458148,33.054444180848094,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[-8.551771677351692,20.026235174745132,-1860.0,2.0,3.0,1.0,-1.0],[20.026235174745132,21.28702959469058,-1808.4764,0.0,3.0,0.0,-1.0],[21.28702959469058,23.80861843458148,0.0,0.0,2.0,1.0,-1.0],[23.80861843458148,33.054444180848094,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>[[-8.500875855240508,19.82590059591878,-1860.0,2.0,2.0,1.0,-1.0],[19.82590059591878,21.174794712640654,-1808.4765,0.0,2.0,0.0,-1.0],[21.174794712640654,23.872582946084393,0.0,0.0,1.0,1.0,-1.0],[23.872582946084393,24.322214318325017,227.85,0.0,1.0,1.0,-1.0],[24.322214318325017,36.01262999658123,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[-8.500875855240508,19.82590059591878,-1860.0,2.0,2.0,1.0,-1.0],[19.82590059591878,21.174794712640654,-1808.4764,0.0,2.0,0.0,-1.0],[21.174794712640654,23.872582946084393,0.0,0.0,1.0,1.0,-1.0],[23.872582946084393,24.322214318325017,227.85,0.0,1.0,1.0,-1.0],[24.322214318325017,36.01262999658123,1860.0,0.0,1.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>[[-9.24631650423712,19.229036167347445,-1860.0,2.0,2.0,0.0,-1.0],[19.229036167347445,20.543283213728273,-1808.4765,0.0,2.0,0.0,-1.0],[20.543283213728273,22.733694957696315,0.0,0.0,1.0,1.0,-1.0],[22.733694957696315,24.924106701664364,227.85,0.0,1.0,0.0,-1.0],[24.924106701664364,34.123836026330146,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-9.24631650423712,19.229036167347445,-1860.0,2.0,2.0,0.0,-1.0],[19.229036167347445,20.543283213728273,-1808.4764,0.0,2.0,0.0,-1.0],[20.543283213728273,22.733694957696315,0.0,0.0,1.0,1.0,-1.0],[22.733694957696315,24.924106701664364,227.85,0.0,1.0,0.0,-1.0],[24.924106701664364,34.123836026330146,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>[[-9.123393332121417,18.442901135502527,-1860.0,1.0,2.0,0.0,-1.0],[18.442901135502527,20.221371746316972,-200.9419,1.0,2.0,0.0,-1.0],[20.221371746316972,22.444460009835034,0.0,1.0,1.0,1.0,-1.0],[22.444460009835034,34.89375428553617,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-9.123393332121417,18.442901135502527,-1860.0,1.0,2.0,0.0,-1.0],[18.442901135502527,20.221371746316972,-200.9418,1.0,2.0,0.0,-1.0],[20.221371746316972,22.444460009835034,0.0,1.0,1.0,1.0,-1.0],[22.444460009835034,34.89375428553617,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -4264,11 +4264,11 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>[[-9.027359949009863,19.00989194162133,-1860.0,1.0,0.0,0.0,-1.0],[19.00989194162133,34.34276406931026,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-9.027359949009863,19.00989194162133,-1860.0,1.0,0.0,0.0,-1.0],[19.00989194162133,34.34276406931026,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>[[-8.813884177572477,16.992815391043088,-1860.0,9.0,0.0,0.0,1.0],[16.992815391043088,26.072950424444862,-0.0,9.0,0.0,1.0,1.0],[26.072950424444862,38.49839836488939,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-8.813884177572477,16.992815391043088,-1860.0,9.0,0.0,0.0,1.0],[16.992815391043088,26.072950424444862,0.0,8.0,0.0,1.0,1.0],[26.072950424444862,38.49839836488939,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>[[-8.73173788014999,17.539251582855375,-1860.0,8.0,0.0,0.0,1.0],[17.539251582855375,27.755747485135235,-0.0,8.0,0.0,1.0,1.0],[27.755747485135235,28.242247290005704,890.0,8.0,8.0,4.0,-1.0],[28.242247290005704,39.43174280202651,1860.0,8.0,9.0,3.0,-1.0]]</t>
+          <t>[[-8.73173788014999,17.539251582855375,-1860.0,7.0,0.0,0.0,1.0],[17.539251582855375,27.755747485135235,0.0,7.0,0.0,1.0,1.0],[27.755747485135235,28.242247290005704,890.0,7.0,8.0,4.0,-1.0],[28.242247290005704,39.43174280202651,1860.0,7.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>[[-8.971465657761424,16.835160399350027,-1860.0,7.0,0.0,0.0,1.0],[16.835160399350027,27.753348346589487,-0.0,7.0,0.0,1.0,1.0],[27.753348346589487,28.249629616918558,708.65,8.0,9.0,2.0,-1.0],[28.249629616918558,40.16038010481614,1860.0,8.0,10.0,1.0,-1.0]]</t>
+          <t>[[-8.971465657761424,16.835160399350027,-1860.0,6.0,0.0,0.0,1.0],[16.835160399350027,27.753348346589487,0.0,6.0,0.0,1.0,1.0],[27.753348346589487,28.249629616918558,708.65,8.0,9.0,2.0,-1.0],[28.249629616918558,40.16038010481614,1860.0,8.0,10.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>[[-10.4561744993561,17.453105873594986,-1860.0,6.0,0.0,0.0,1.0],[17.453105873594986,27.735472326787487,-0.0,6.0,0.0,1.0,1.0],[27.735472326787487,38.01783877997999,1860.0,6.0,8.0,4.0,-1.0]]</t>
+          <t>[[-10.4561744993561,17.453105873594986,-1860.0,6.0,0.0,0.0,1.0],[17.453105873594986,27.735472326787487,0.0,6.0,0.0,1.0,1.0],[27.735472326787487,38.01783877997999,1860.0,6.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>[[-9.581443882848344,17.434684435901232,-1860.0,5.0,0.0,0.0,1.0],[17.434684435901232,27.258731097264718,-0.0,5.0,0.0,1.0,1.0],[27.258731097264718,39.04758709090089,1860.0,5.0,9.0,3.0,-1.0]]</t>
+          <t>[[-9.581443882848344,17.434684435901232,-1860.0,5.0,0.0,0.0,1.0],[17.434684435901232,27.258731097264718,0.0,4.0,0.0,1.0,1.0],[27.258731097264718,39.04758709090089,1860.0,5.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>[[-18.963746012354907,17.642961813739145,-1860.0,4.0,0.0,0.0,1.0],[17.642961813739145,28.270715698734197,-0.0,4.0,0.0,1.0,1.0],[28.270715698734197,39.488900355117856,1860.0,5.0,9.0,2.0,-1.0]]</t>
+          <t>[[-18.963746012354907,17.642961813739145,-1860.0,4.0,0.0,0.0,1.0],[17.642961813739145,28.270715698734197,0.0,4.0,0.0,1.0,1.0],[28.270715698734197,39.488900355117856,1860.0,5.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>[[-18.869506492868076,16.90228595607352,-1860.0,3.0,0.0,0.0,1.0],[16.90228595607352,27.209412593904148,-0.0,3.0,0.0,1.0,1.0],[27.209412593904148,27.815714160835363,890.0,3.0,8.0,4.0,-1.0],[27.815714160835363,41.154348633322066,1860.0,3.0,9.0,3.0,-1.0]]</t>
+          <t>[[-18.869506492868076,16.90228595607352,-1860.0,3.0,0.0,0.0,1.0],[16.90228595607352,27.209412593904148,0.0,3.0,0.0,1.0,1.0],[27.209412593904148,27.815714160835363,890.0,3.0,8.0,4.0,-1.0],[27.815714160835363,41.154348633322066,1860.0,3.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>[[-19.730185648214132,17.107605273967906,-1860.0,2.0,0.0,0.0,1.0],[17.107605273967906,27.208289881662985,-0.0,2.0,0.0,1.0,1.0],[27.208289881662985,28.3966057178624,890.0,2.0,8.0,4.0,-1.0],[28.3966057178624,39.09144824365719,1860.0,2.0,8.0,4.0,-1.0]]</t>
+          <t>[[-19.730185648214132,17.107605273967906,-1860.0,2.0,0.0,0.0,1.0],[17.107605273967906,27.208289881662985,0.0,2.0,0.0,1.0,1.0],[27.208289881662985,28.3966057178624,890.0,2.0,8.0,4.0,-1.0],[28.3966057178624,39.09144824365719,1860.0,2.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>[[-18.322836839503953,17.345431669463654,-1860.0,1.0,0.0,0.0,1.0],[17.345431669463654,28.227276299318174,-0.0,1.0,0.0,1.0,1.0],[28.227276299318174,41.52730862469593,1860.0,2.0,9.0,2.0,-1.0]]</t>
+          <t>[[-18.322836839503953,-0.18642912307974768,-1860.0,1.0,0.0,0.0,1.0],[-0.18642912307974768,17.345431669463654,-1860.0,0.0,0.0,0.0,1.0],[17.345431669463654,19.159072441106073,0.0,0.0,0.0,1.0,1.0],[19.159072441106073,22.786353984390917,0.0,1.0,0.0,1.0,1.0],[22.786353984390917,25.20454167991414,0.0,0.0,0.0,1.0,1.0],[25.20454167991414,28.227276299318174,0.0,1.0,0.0,1.0,1.0],[28.227276299318174,41.52730862469593,1860.0,2.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -4433,11 +4433,11 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>[[-18.36657183730695,27.688618808674747,-0.0,0.0,0.0,1.0,1.0],[27.688618808674747,28.279069970802716,1678.65,1.0,0.0,0.0,1.0],[28.279069970802716,40.08809321336213,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[-18.36657183730695,27.688618808674747,0.0,0.0,0.0,1.0,1.0],[27.688618808674747,28.279069970802716,1678.65,1.0,0.0,0.0,1.0],[28.279069970802716,40.08809321336213,1860.0,1.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309">
@@ -4446,11 +4446,11 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>[[-18.547634592004425,28.32207412992179,-0.0,0.0,0.0,1.0,1.0],[28.32207412992179,28.915361582098075,890.0,0.0,8.0,3.0,-1.0],[28.915361582098075,40.18782317344742,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[-18.547634592004425,28.32207412992179,0.0,0.0,0.0,1.0,1.0],[28.32207412992179,28.915361582098075,890.0,0.0,8.0,3.0,-1.0],[28.915361582098075,40.18782317344742,1860.0,0.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>[[-19.59274793037786,26.421433390683582,-0.0,0.0,0.0,1.0,1.0],[26.421433390683582,27.616606931490374,890.0,0.0,8.0,2.0,-1.0],[27.616606931490374,39.568342339558285,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-19.59274793037786,26.421433390683582,0.0,0.0,0.0,1.0,1.0],[26.421433390683582,27.616606931490374,890.0,0.0,8.0,2.0,-1.0],[27.616606931490374,39.568342339558285,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>[[-19.0848640230873,22.318948420012546,-1860.0,1.0,8.0,0.0,-1.0],[22.318948420012546,24.719169431206737,-1074.7923,0.0,8.0,1.0,-1.0],[24.719169431206737,27.719445695199482,0.0,0.0,8.0,1.0,-1.0],[27.719445695199482,28.31950094799803,708.65,1.0,8.0,0.0,-1.0],[28.31950094799803,40.320606003969,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[-19.0848640230873,22.318948420012546,-1860.0,1.0,8.0,0.0,-1.0],[22.318948420012546,24.719169431206737,-1074.7922,0.0,8.0,1.0,-1.0],[24.719169431206737,27.719445695199482,0.0,0.0,8.0,1.0,-1.0],[27.719445695199482,28.31950094799803,708.65,1.0,8.0,0.0,-1.0],[28.31950094799803,40.320606003969,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>[[-18.083173204444062,12.989496696720064,-1860.0,1.0,8.0,0.0,-1.0],[12.989496696720064,23.745420893276876,-1074.7923,0.0,8.0,0.0,-1.0],[23.745420893276876,26.733177614542658,0.0,0.0,7.0,1.0,-1.0],[26.733177614542658,27.330728958795813,890.0,0.0,7.0,1.0,-1.0],[27.330728958795813,41.074409876618404,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[-18.083173204444062,12.989496696720064,-1860.0,1.0,8.0,0.0,-1.0],[12.989496696720064,23.745420893276876,-1074.7922,0.0,8.0,0.0,-1.0],[23.745420893276876,26.733177614542658,0.0,0.0,7.0,1.0,-1.0],[26.733177614542658,27.330728958795813,890.0,0.0,7.0,1.0,-1.0],[27.330728958795813,41.074409876618404,1860.0,0.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>[[-19.997741224992556,12.385340527165038,-1860.0,1.0,7.0,0.0,-1.0],[12.385340527165038,22.58001441210354,-1074.7923,0.0,7.0,0.0,-1.0],[22.58001441210354,25.578447907673688,0.0,0.0,6.0,1.0,-1.0],[25.578447907673688,27.977194704129804,890.0,0.0,6.0,1.0,-1.0],[27.977194704129804,39.37124198729637,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-19.997741224992556,12.385340527165038,-1860.0,1.0,7.0,0.0,-1.0],[12.385340527165038,22.58001441210354,-1074.7922,0.0,7.0,0.0,-1.0],[22.58001441210354,25.578447907673688,0.0,0.0,6.0,1.0,-1.0],[25.578447907673688,27.977194704129804,890.0,0.0,6.0,1.0,-1.0],[27.977194704129804,39.37124198729637,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>[[-18.84860564699721,13.070559642789203,-1860.0,1.0,6.0,0.0,-1.0],[13.070559642789203,22.35613499981798,-1074.7923,0.0,6.0,0.0,-1.0],[22.35613499981798,25.257877298889465,0.0,0.0,5.0,1.0,-1.0],[25.257877298889465,27.579271138146662,890.0,0.0,5.0,1.0,-1.0],[27.579271138146662,38.60589187461833,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[-18.84860564699721,13.070559642789203,-1860.0,1.0,6.0,0.0,-1.0],[13.070559642789203,22.35613499981798,-1074.7922,0.0,6.0,0.0,-1.0],[22.35613499981798,25.257877298889465,0.0,0.0,5.0,1.0,-1.0],[25.257877298889465,27.579271138146662,890.0,0.0,5.0,1.0,-1.0],[27.579271138146662,38.60589187461833,1860.0,0.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>[[-18.72920294444079,12.41922387052568,-1860.0,1.0,5.0,0.0,-1.0],[12.41922387052568,22.410228697967757,-1074.7923,0.0,5.0,0.0,-1.0],[22.410228697967757,24.76105336324824,0.0,0.0,4.0,1.0,-1.0],[24.76105336324824,27.699584194848857,890.0,0.0,4.0,1.0,-1.0],[27.699584194848857,39.4537075212513,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-18.72920294444079,12.41922387052568,-1860.0,1.0,5.0,0.0,-1.0],[12.41922387052568,22.410228697967757,-1074.7922,0.0,5.0,0.0,-1.0],[22.410228697967757,24.76105336324824,0.0,0.0,4.0,1.0,-1.0],[24.76105336324824,27.699584194848857,890.0,0.0,4.0,1.0,-1.0],[27.699584194848857,39.4537075212513,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>[[-18.202335393321956,13.1065339757218,-1860.0,1.0,4.0,0.0,-1.0],[13.1065339757218,21.967534740545506,-1074.7923,0.0,4.0,0.0,-1.0],[21.967534740545506,24.330468277831823,0.0,0.0,3.0,1.0,-1.0],[24.330468277831823,27.284135199439728,890.0,0.0,3.0,1.0,-1.0],[27.284135199439728,40.280269654514484,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-18.202335393321956,13.1065339757218,-1860.0,1.0,4.0,0.0,-1.0],[13.1065339757218,21.967534740545506,-1074.7922,0.0,4.0,0.0,-1.0],[21.967534740545506,24.330468277831823,0.0,0.0,3.0,1.0,-1.0],[24.330468277831823,27.284135199439728,890.0,0.0,3.0,1.0,-1.0],[27.284135199439728,40.280269654514484,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>[[-18.161635208595573,13.240998055117121,-1860.0,1.0,3.0,0.0,-1.0],[13.240998055117121,24.49854582890092,-1074.7923,0.0,3.0,0.0,-1.0],[24.49854582890092,27.461058400949288,0.0,0.0,2.0,1.0,-1.0],[27.461058400949288,30.423570972997656,890.0,0.0,2.0,1.0,-1.0],[30.423570972997656,40.496113717962096,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-18.161635208595573,13.240998055117121,-1860.0,1.0,3.0,0.0,-1.0],[13.240998055117121,24.49854582890092,-1074.7922,0.0,3.0,0.0,-1.0],[24.49854582890092,27.461058400949288,0.0,0.0,2.0,1.0,-1.0],[27.461058400949288,30.423570972997656,890.0,0.0,2.0,1.0,-1.0],[30.423570972997656,40.496113717962096,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>[[-18.717597789029234,5.099322627965442,-1860.0,10.0,3.0,0.0,1.0],[5.099322627965442,5.680223125940923,-1808.4765,9.0,3.0,1.0,1.0],[5.680223125940923,13.231929599622163,-1074.7923,0.0,3.0,0.0,-1.0],[13.231929599622163,14.974631093548602,0.0,0.0,2.0,1.0,-1.0],[14.974631093548602,31.239845036862043,890.0,0.0,2.0,0.0,-1.0],[31.239845036862043,38.79155151054328,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-18.717597789029234,5.099322627965442,-1860.0,10.0,3.0,0.0,1.0],[5.099322627965442,5.680223125940923,-1808.4764,9.0,3.0,1.0,1.0],[5.680223125940923,13.231929599622163,-1074.7922,0.0,3.0,0.0,-1.0],[13.231929599622163,14.974631093548602,0.0,0.0,2.0,1.0,-1.0],[14.974631093548602,31.239845036862043,890.0,0.0,2.0,0.0,-1.0],[31.239845036862043,38.79155151054328,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>[[-18.858695035645415,4.193525130370194,-1860.0,10.0,2.0,0.0,1.0],[4.193525130370194,4.78460769872957,-733.6843,9.0,2.0,1.0,1.0],[4.78460769872957,14.833011360838935,0.0,0.0,2.0,1.0,-1.0],[14.833011360838935,39.658479231932674,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-18.858695035645415,4.193525130370194,-1860.0,10.0,2.0,0.0,1.0],[4.193525130370194,4.78460769872957,-733.6842,9.0,2.0,1.0,1.0],[4.78460769872957,14.833011360838935,0.0,0.0,2.0,1.0,-1.0],[14.833011360838935,39.658479231932674,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>[[-17.846349505466844,5.12504090123748,-1860.0,10.0,1.0,0.0,1.0],[5.12504090123748,5.714050911665797,-733.6843,9.0,1.0,1.0,1.0],[5.714050911665797,13.371181047233907,0.0,0.0,1.0,1.0,-1.0],[13.371181047233907,14.549201068090536,0.0,0.0,0.0,1.0,-1.0],[14.549201068090536,16.31623109937549,1860.0,0.0,0.0,0.0,-1.0],[16.31623109937549,40.46564152693644,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-17.846349505466844,5.12504090123748,-1860.0,10.0,1.0,0.0,1.0],[5.12504090123748,5.714050911665797,-733.6842,9.0,1.0,1.0,1.0],[5.714050911665797,14.549201068090536,0.0,0.0,1.0,1.0,-1.0],[14.549201068090536,40.46564152693644,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>[[-18.44467554567356,4.854090473381191,-1860.0,10.0,0.0,0.0,1.0],[4.854090473381191,5.383607882905164,-733.6843,9.0,0.0,1.0,1.0],[5.383607882905164,33.97754799719963,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-18.44467554567356,4.854090473381191,-1860.0,10.0,0.0,0.0,1.0],[4.854090473381191,5.383607882905164,-733.6842,9.0,0.0,1.0,1.0],[5.383607882905164,33.97754799719963,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -4615,11 +4615,11 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>[[-19.196582680214775,1.30248995448569,-1860.0,9.0,0.0,0.0,1.0],[1.30248995448569,26.233794510202465,-733.6843,9.0,0.0,0.0,1.0],[26.233794510202465,35.652287342362136,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-19.196582680214775,1.30248995448569,-1860.0,9.0,0.0,0.0,1.0],[1.30248995448569,26.233794510202465,-733.6842,9.0,0.0,0.0,1.0],[26.233794510202465,35.652287342362136,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>-733.6843</v>
+        <v>-733.6842</v>
       </c>
     </row>
     <row r="323">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>[[-18.44566975749752,26.326646903304486,-1860.0,9.0,0.0,0.0,1.0],[26.326646903304486,29.09037015397127,0.0,8.0,7.0,1.0,-1.0],[29.09037015397127,36.27605060570493,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-18.44566975749752,26.326646903304486,-1860.0,8.0,0.0,0.0,1.0],[26.326646903304486,29.09037015397127,0.0,8.0,7.0,1.0,-1.0],[29.09037015397127,36.27605060570493,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>[[-18.87824952192215,26.336957040724037,-1860.0,8.0,0.0,0.0,1.0],[26.336957040724037,27.99117191496719,-873.8504,7.0,8.0,0.0,-1.0],[27.99117191496719,30.748196705372443,0.0,7.0,7.0,1.0,-1.0],[30.748196705372443,35.71084132810191,1860.0,7.0,7.0,1.0,-1.0]]</t>
+          <t>[[-18.87824952192215,26.336957040724037,-1860.0,6.0,0.0,0.0,1.0],[26.336957040724037,27.99117191496719,-873.8504,7.0,8.0,0.0,-1.0],[27.99117191496719,30.748196705372443,0.0,7.0,7.0,1.0,-1.0],[30.748196705372443,35.71084132810191,1860.0,7.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>[[-18.795445222113045,25.140693754248474,-1860.0,7.0,0.0,0.0,1.0],[25.140693754248474,26.239097228657513,-1074.7922,7.0,9.0,1.0,-1.0],[26.239097228657513,28.985105914680112,0.0,7.0,8.0,2.0,-1.0],[28.985105914680112,29.53430765188463,890.0,7.0,8.0,1.0,-1.0],[29.53430765188463,35.57552676113434,1860.0,7.0,8.0,1.0,-1.0]]</t>
+          <t>[[-18.795445222113045,25.140693754248474,-1860.0,6.0,0.0,0.0,1.0],[25.140693754248474,26.239097228657513,-1074.7922,7.0,9.0,1.0,-1.0],[26.239097228657513,28.985105914680112,0.0,7.0,8.0,2.0,-1.0],[28.985105914680112,29.53430765188463,890.0,7.0,8.0,1.0,-1.0],[29.53430765188463,35.57552676113434,1860.0,7.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>[[-18.371446659018705,25.32383887525282,-1860.0,6.0,0.0,0.0,1.0],[25.32383887525282,25.87002994443122,-873.8504,5.0,8.0,0.0,-1.0],[25.87002994443122,28.60098529032319,0.0,5.0,7.0,1.0,-1.0],[28.60098529032319,30.239558497858372,1071.35,5.0,7.0,1.0,-1.0],[30.239558497858372,35.70146918964231,1860.0,5.0,7.0,1.0,-1.0]]</t>
+          <t>[[-18.371446659018705,25.32383887525282,-1860.0,5.0,0.0,0.0,1.0],[25.32383887525282,25.87002994443122,-873.8504,5.0,8.0,0.0,-1.0],[25.87002994443122,28.60098529032319,0.0,5.0,7.0,1.0,-1.0],[28.60098529032319,30.239558497858372,1071.35,5.0,7.0,1.0,-1.0],[30.239558497858372,35.70146918964231,1860.0,5.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>[[-18.460136581089603,25.77642098180738,-1860.0,5.0,0.0,0.0,1.0],[25.77642098180738,26.32255132209006,-873.8504,4.0,8.0,2.0,-1.0],[26.32255132209006,29.053203023503453,0.0,4.0,7.0,3.0,-1.0],[29.053203023503453,31.237724384634166,1071.35,4.0,7.0,1.0,-1.0],[31.237724384634166,35.6067671068956,1860.0,4.0,8.0,0.0,-1.0]]</t>
+          <t>[[-18.460136581089603,25.77642098180738,-1860.0,4.0,0.0,0.0,1.0],[25.77642098180738,26.32255132209006,-873.8504,4.0,8.0,2.0,-1.0],[26.32255132209006,29.053203023503453,0.0,4.0,7.0,3.0,-1.0],[29.053203023503453,31.237724384634166,1071.35,4.0,7.0,1.0,-1.0],[31.237724384634166,35.6067671068956,1860.0,4.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>[[-11.457705885176512,26.050139092890394,-1860.0,4.0,7.0,0.0,-1.0],[26.050139092890394,27.474487636361292,-672.9085,3.0,7.0,1.0,-1.0],[27.474487636361292,30.79796757112671,0.0,3.0,6.0,2.0,-1.0],[30.79796757112671,31.27275041895034,1252.7,3.0,6.0,1.0,-1.0],[31.27275041895034,35.545796049363034,1860.0,3.0,6.0,1.0,-1.0]]</t>
+          <t>[[-11.457705885176512,26.050139092890394,-1860.0,4.0,7.0,0.0,-1.0],[26.050139092890394,27.474487636361292,-672.9086,3.0,7.0,1.0,-1.0],[27.474487636361292,30.79796757112671,0.0,3.0,6.0,2.0,-1.0],[30.79796757112671,31.27275041895034,1252.7,3.0,6.0,1.0,-1.0],[31.27275041895034,35.545796049363034,1860.0,3.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>[[-8.751260776202853,25.749859251972516,-1860.0,3.0,7.0,2.0,-1.0],[25.749859251972516,26.623305328635183,-672.9085,2.0,7.0,3.0,-1.0],[26.623305328635183,29.68036659695452,0.0,2.0,6.0,4.0,-1.0],[29.68036659695452,30.553812673617188,1252.7,2.0,6.0,4.0,-1.0],[30.553812673617188,34.48432001859919,1860.0,2.0,7.0,3.0,-1.0]]</t>
+          <t>[[-8.751260776202853,25.749859251972516,-1860.0,3.0,7.0,2.0,-1.0],[25.749859251972516,26.623305328635183,-672.9086,2.0,7.0,3.0,-1.0],[26.623305328635183,29.68036659695452,0.0,2.0,6.0,4.0,-1.0],[29.68036659695452,30.553812673617188,1252.7,2.0,6.0,4.0,-1.0],[30.553812673617188,34.48432001859919,1860.0,2.0,7.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>[[-8.720600197365597,27.85785470548778,-1860.0,2.0,6.0,1.0,-1.0],[27.85785470548778,30.906059280725565,0.0,1.0,5.0,3.0,-1.0],[30.906059280725565,31.3415170771881,1434.05,1.0,5.0,3.0,-1.0],[31.3415170771881,34.389721652425884,1860.0,1.0,5.0,3.0,-1.0]]</t>
+          <t>[[-8.720600197365597,27.85785470548778,-1860.0,2.0,6.0,1.0,-1.0],[27.85785470548778,30.906059280725565,0.0,1.0,5.0,3.0,-1.0],[30.906059280725565,31.3415170771881,1434.05,0.0,5.0,3.0,-1.0],[31.3415170771881,34.389721652425884,1860.0,1.0,5.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>[[-9.0369809601662,25.38427064912653,-1860.0,1.0,7.0,2.0,-1.0],[25.38427064912653,28.473357332011776,-672.9085,0.0,7.0,0.0,-1.0],[28.473357332011776,31.121145917341988,0.0,0.0,6.0,1.0,-1.0],[31.121145917341988,31.56244401489702,1252.7,0.0,6.0,1.0,-1.0],[31.56244401489702,34.65153069778226,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[-9.0369809601662,25.38427064912653,-1860.0,1.0,7.0,2.0,-1.0],[25.38427064912653,28.473357332011776,-672.9086,0.0,7.0,0.0,-1.0],[28.473357332011776,31.121145917341988,0.0,0.0,6.0,1.0,-1.0],[31.121145917341988,31.56244401489702,1252.7,0.0,6.0,1.0,-1.0],[31.56244401489702,34.65153069778226,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>[[-8.731740297598687,24.82649491496002,-1860.0,1.0,7.0,0.0,-1.0],[24.82649491496002,25.72138118729492,-672.9085,0.0,7.0,1.0,-1.0],[25.72138118729492,28.406040004299616,0.0,0.0,6.0,2.0,-1.0],[28.406040004299616,30.195812548969418,1252.7,0.0,6.0,0.0,-1.0],[30.195812548969418,35.56513018297881,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-8.731740297598687,24.82649491496002,-1860.0,1.0,7.0,0.0,-1.0],[24.82649491496002,25.72138118729492,-672.9086,0.0,7.0,1.0,-1.0],[25.72138118729492,28.406040004299616,0.0,0.0,6.0,2.0,-1.0],[28.406040004299616,30.195812548969418,1252.7,0.0,6.0,0.0,-1.0],[30.195812548969418,35.56513018297881,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>[[-8.808865035697247,24.339139950345356,-1860.0,1.0,6.0,1.0,-1.0],[24.339139950345356,26.15546899067646,-672.9085,0.0,6.0,1.0,-1.0],[26.15546899067646,28.879962551173108,0.0,0.0,5.0,2.0,-1.0],[28.879962551173108,31.150373851586984,1252.7,0.0,5.0,0.0,-1.0],[31.150373851586984,36.145278712497515,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-8.808865035697247,24.339139950345356,-1860.0,1.0,6.0,1.0,-1.0],[24.339139950345356,26.15546899067646,-672.9086,0.0,6.0,1.0,-1.0],[26.15546899067646,28.879962551173108,0.0,0.0,5.0,2.0,-1.0],[28.879962551173108,31.150373851586984,1252.7,0.0,5.0,0.0,-1.0],[31.150373851586984,36.145278712497515,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>[[-8.966725062329564,0.5538491698966137,-1860.0,8.0,0.0,0.0,1.0],[0.5538491698966137,23.675243733874474,-733.6842,8.0,0.0,0.0,1.0],[23.675243733874474,26.39540780022481,0.0,8.0,0.0,1.0,1.0],[26.39540780022481,27.755489833399977,1016.5,9.0,0.0,0.0,1.0],[27.755489833399977,35.91598203245099,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-8.966725062329564,0.5538491698966137,-1860.0,8.0,0.0,0.0,1.0],[0.5538491698966137,23.675243733874474,-733.6842,8.0,0.0,0.0,1.0],[23.675243733874474,26.39540780022481,0.0,8.0,0.0,1.0,1.0],[26.39540780022481,27.755489833399977,1016.5,9.0,0.0,0.0,1.0],[27.755489833399977,35.91598203245099,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>[[-8.189371790192736,0.8107482806395137,-1860.0,1.0,0.0,0.0,1.0],[0.8107482806395137,24.382491323295405,-733.6842,1.0,0.0,0.0,1.0],[24.382491323295405,26.953954200676044,0.0,1.0,0.0,1.0,1.0],[26.953954200676044,34.239765686587866,1860.0,2.0,9.0,1.0,-1.0]]</t>
+          <t>[[-8.189371790192736,0.8107482806395137,-1860.0,1.0,0.0,0.0,1.0],[0.8107482806395137,24.382491323295405,-733.6842,0.0,0.0,0.0,1.0],[24.382491323295405,26.953954200676044,0.0,1.0,0.0,1.0,1.0],[26.953954200676044,34.239765686587866,1860.0,2.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>[[-0.8285544780504653,25.031884576340058,-1860.0,1.0,8.0,3.0,-1.0],[25.031884576340058,27.511652704843257,0.0,0.0,8.0,4.0,-1.0],[27.511652704843257,27.865905294629428,227.85,1.0,8.0,3.0,-1.0],[27.865905294629428,34.24245191078052,1860.0,1.0,8.0,3.0,-1.0]]</t>
+          <t>[[-0.8285544780504653,25.031884576340058,-1860.0,1.0,8.0,3.0,-1.0],[25.031884576340058,27.511652704843257,0.0,0.0,8.0,4.0,-1.0],[27.511652704843257,27.865905294629428,227.85,0.0,8.0,3.0,-1.0],[27.865905294629428,34.24245191078052,1860.0,1.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>[[-0.8045334098895883,22.896049447989117,-733.6842,0.0,0.0,0.0,1.0],[22.896049447989117,25.409747629885345,0.0,0.0,8.0,2.0,-1.0],[25.409747629885345,27.205246331239795,227.85,0.0,8.0,2.0,-1.0],[27.205246331239795,34.74634087692848,1860.0,0.0,9.0,1.0,-1.0]]</t>
+          <t>[[-0.8045334098895883,22.896049447989117,-733.6843,0.0,0.0,0.0,1.0],[22.896049447989117,25.409747629885345,0.0,0.0,8.0,2.0,-1.0],[25.409747629885345,27.205246331239795,227.85,0.0,8.0,2.0,-1.0],[27.205246331239795,34.74634087692848,1860.0,0.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>[[-0.8086767806605984,23.28119775225262,-986.1495,0.0,0.0,0.0,1.0],[23.28119775225262,26.42335530002391,0.0,0.0,8.0,2.0,-1.0],[26.42335530002391,33.755056244823585,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-0.8086767806605984,23.28119775225262,-986.1497,0.0,0.0,0.0,1.0],[23.28119775225262,26.42335530002391,0.0,0.0,8.0,2.0,-1.0],[26.42335530002391,33.755056244823585,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C357" t="n">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>[[-0.8226825328544912,22.666785807354938,-986.1495,0.0,0.0,0.0,1.0],[22.666785807354938,26.076547340611146,0.0,0.0,8.0,3.0,-1.0],[26.076547340611146,36.68469433296379,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[-0.8226825328544912,22.666785807354938,-986.1497,0.0,0.0,0.0,1.0],[22.666785807354938,26.076547340611146,0.0,0.0,8.0,3.0,-1.0],[26.076547340611146,36.68469433296379,1860.0,0.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>[[-0.792115077659882,12.814010090091632,-1860.0,9.0,0.0,0.0,1.0],[12.814010090091632,17.91630702799845,-733.6842,9.0,0.0,0.0,1.0],[17.91630702799845,41.30183466007137,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-0.792115077659882,12.814010090091632,-1860.0,8.0,0.0,0.0,1.0],[12.814010090091632,17.91630702799845,-733.6842,9.0,0.0,0.0,1.0],[17.91630702799845,41.30183466007137,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C369" t="n">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>[[-0.7901573278879391,18.16278630648099,-1860.0,9.0,0.0,0.0,1.0],[18.16278630648099,28.93150428055424,0.0,9.0,0.0,1.0,1.0],[28.93150428055424,41.85396584944215,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-0.7901573278879391,18.16278630648099,-1860.0,8.0,0.0,0.0,1.0],[18.16278630648099,28.93150428055424,0.0,9.0,0.0,1.0,1.0],[28.93150428055424,41.85396584944215,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>[[-0.7626232794666812,18.13348796244254,-1860.0,8.0,0.0,0.0,1.0],[18.13348796244254,29.11959914959907,0.0,8.0,0.0,1.0,1.0],[29.11959914959907,29.559043597085328,890.0,8.0,8.0,0.0,-1.0],[29.559043597085328,42.74237702167316,1860.0,8.0,8.0,0.0,-1.0]]</t>
+          <t>[[-0.7626232794666812,18.13348796244254,-1860.0,5.0,0.0,0.0,1.0],[18.13348796244254,29.11959914959907,0.0,7.0,0.0,1.0,1.0],[29.11959914959907,29.559043597085328,890.0,7.0,8.0,0.0,-1.0],[29.559043597085328,42.74237702167316,1860.0,6.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>[[-0.7843419030361622,17.71378017751417,-1860.0,7.0,0.0,0.0,1.0],[17.71378017751417,29.759068974151592,0.0,7.0,0.0,1.0,1.0],[29.759068974151592,30.189257859745787,890.0,7.0,8.0,1.0,-1.0],[30.189257859745787,41.80435777078901,1860.0,7.0,8.0,1.0,-1.0]]</t>
+          <t>[[-0.7843419030361622,17.71378017751417,-1860.0,4.0,0.0,0.0,1.0],[17.71378017751417,29.759068974151592,0.0,7.0,0.0,1.0,1.0],[29.759068974151592,30.189257859745787,890.0,7.0,8.0,1.0,-1.0],[30.189257859745787,41.80435777078901,1860.0,5.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>[[-0.7838041493776018,17.488555091540736,-1860.0,6.0,0.0,0.0,1.0],[17.488555091540736,29.23507174641681,0.0,6.0,0.0,1.0,1.0],[29.23507174641681,30.540240263625265,890.0,6.0,8.0,1.0,-1.0],[30.540240263625265,42.28675691850134,1860.0,6.0,8.0,1.0,-1.0]]</t>
+          <t>[[-0.7838041493776018,17.488555091540736,-1860.0,4.0,0.0,0.0,1.0],[17.488555091540736,29.23507174641681,0.0,4.0,0.0,1.0,1.0],[29.23507174641681,30.540240263625265,890.0,4.0,8.0,1.0,-1.0],[30.540240263625265,42.28675691850134,1860.0,5.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C373" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>[[0.4373098028181701,26.72693793185583,-1860.0,6.0,0.0,0.0,1.0],[26.72693793185583,28.06369868417978,-873.8504,5.0,8.0,0.0,-1.0],[28.06369868417978,31.182807106268996,0.0,5.0,7.0,1.0,-1.0],[31.182807106268996,44.55041462950848,1860.0,5.0,7.0,1.0,-1.0]]</t>
+          <t>[[0.4373098028181701,26.72693793185583,-1860.0,3.0,0.0,0.0,1.0],[26.72693793185583,28.06369868417978,-873.8504,4.0,8.0,0.0,-1.0],[28.06369868417978,31.182807106268996,0.0,3.0,7.0,1.0,-1.0],[31.182807106268996,44.55041462950848,1860.0,4.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>[[-0.9883996611836087,25.258160411523082,-1860.0,5.0,0.0,0.0,1.0],[25.258160411523082,27.007931083036862,-873.8504,4.0,8.0,0.0,-1.0],[27.007931083036862,29.63258709030753,0.0,4.0,7.0,1.0,-1.0],[29.63258709030753,31.382357761821307,1071.35,4.0,7.0,1.0,-1.0],[31.382357761821307,42.31842445878244,1860.0,4.0,7.0,1.0,-1.0]]</t>
+          <t>[[-0.9883996611836087,25.258160411523082,-1860.0,3.0,0.0,0.0,1.0],[25.258160411523082,27.007931083036862,-873.8504,3.0,8.0,0.0,-1.0],[27.007931083036862,29.63258709030753,0.0,3.0,7.0,1.0,-1.0],[29.63258709030753,31.382357761821307,1071.35,3.0,7.0,1.0,-1.0],[31.382357761821307,42.31842445878244,1860.0,3.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C375" t="n">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>[[-3.238786972373251,27.35248498107974,-1860.0,4.0,0.0,0.0,1.0],[27.35248498107974,27.80907112963874,-873.8504,3.0,8.0,1.0,-1.0],[27.80907112963874,31.00517416955174,0.0,3.0,7.0,2.0,-1.0],[31.00517416955174,31.918346466669735,1071.35,3.0,7.0,1.0,-1.0],[31.918346466669735,41.96324173496774,1860.0,3.0,7.0,1.0,-1.0]]</t>
+          <t>[[-3.238786972373251,27.35248498107974,-1860.0,2.0,0.0,0.0,1.0],[27.35248498107974,27.80907112963874,-873.8504,2.0,8.0,1.0,-1.0],[27.80907112963874,31.00517416955174,0.0,2.0,7.0,2.0,-1.0],[31.00517416955174,31.918346466669735,1071.35,2.0,7.0,1.0,-1.0],[31.918346466669735,41.96324173496774,1860.0,2.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>[[-2.9947433807787847,25.510747135571663,-1860.0,3.0,0.0,0.0,1.0],[25.510747135571663,26.460930152783344,-873.8504,2.0,8.0,0.0,-1.0],[26.460930152783344,29.31147920441839,0.0,2.0,7.0,1.0,-1.0],[29.31147920441839,30.73675373023591,1071.35,2.0,7.0,1.0,-1.0],[30.73675373023591,44.03931597119946,1860.0,2.0,7.0,1.0,-1.0]]</t>
+          <t>[[-2.9947433807787847,25.510747135571663,-1860.0,2.0,0.0,0.0,1.0],[25.510747135571663,26.460930152783344,-873.8504,2.0,8.0,0.0,-1.0],[26.460930152783344,29.31147920441839,0.0,1.0,7.0,1.0,-1.0],[29.31147920441839,30.73675373023591,1071.35,2.0,7.0,1.0,-1.0],[30.73675373023591,44.03931597119946,1860.0,1.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>[[-2.940369776150578,25.958161273224494,-1860.0,2.0,0.0,0.0,1.0],[25.958161273224494,26.890371952236592,-873.8504,1.0,8.0,1.0,-1.0],[26.890371952236592,29.687003989272892,0.0,1.0,7.0,2.0,-1.0],[29.687003989272892,32.01753068680314,1071.35,1.0,7.0,1.0,-1.0],[32.01753068680314,43.20405883494833,1860.0,1.0,7.0,1.0,-1.0]]</t>
+          <t>[[-2.940369776150578,25.958161273224494,-1860.0,1.0,0.0,0.0,1.0],[25.958161273224494,26.890371952236592,-873.8504,0.0,8.0,1.0,-1.0],[26.890371952236592,29.687003989272892,0.0,1.0,7.0,2.0,-1.0],[29.687003989272892,32.01753068680314,1071.35,0.0,7.0,1.0,-1.0],[32.01753068680314,43.20405883494833,1860.0,1.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>[[-3.317736787693387,26.322060943358295,-1860.0,1.0,0.0,0.0,1.0],[26.322060943358295,26.77805783152832,-873.8504,0.0,8.0,1.0,-1.0],[26.77805783152832,29.514039160548474,0.0,0.0,7.0,2.0,-1.0],[29.514039160548474,30.882029825058556,1071.35,0.0,7.0,1.0,-1.0],[30.882029825058556,41.825955141139175,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[-3.317736787693387,-0.12575857050320582,-1860.0,1.0,0.0,0.0,1.0],[-0.12575857050320582,26.322060943358295,-1860.0,0.0,0.0,0.0,1.0],[26.322060943358295,26.77805783152832,-873.8504,0.0,8.0,1.0,-1.0],[26.77805783152832,29.514039160548474,0.0,0.0,7.0,2.0,-1.0],[29.514039160548474,30.882029825058556,1071.35,0.0,7.0,1.0,-1.0],[30.882029825058556,41.825955141139175,1860.0,0.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C379" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>[[-3.1675207668873657,23.958319871765298,-1860.0,2.0,7.0,0.0,-1.0],[23.958319871765298,24.41041721574284,-401.8836,2.0,7.0,0.0,-1.0],[24.41041721574284,27.123001279608104,0.0,2.0,6.0,1.0,-1.0],[27.123001279608104,28.931390655518285,1497.3,2.0,6.0,1.0,-1.0],[28.931390655518285,41.590116286889526,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-3.1675207668873657,23.958319871765298,-1860.0,2.0,7.0,0.0,-1.0],[23.958319871765298,24.41041721574284,-401.8837,2.0,7.0,0.0,-1.0],[24.41041721574284,27.123001279608104,0.0,2.0,6.0,1.0,-1.0],[27.123001279608104,28.931390655518285,1497.3,2.0,6.0,1.0,-1.0],[28.931390655518285,41.590116286889526,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C384" t="n">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>[[-3.2429692379502564,22.87532269503339,-1860.0,2.0,5.0,1.0,-1.0],[22.87532269503339,25.207313046192645,-200.9418,1.0,5.0,2.0,-1.0],[25.207313046192645,28.005701467583748,0.0,1.0,5.0,2.0,-1.0],[28.005701467583748,28.4720995378156,1497.3,2.0,5.0,1.0,-1.0],[28.4720995378156,42.930439715002976,1860.0,1.0,4.0,0.0,-1.0]]</t>
+          <t>[[-3.2429692379502564,22.87532269503339,-1860.0,1.0,5.0,1.0,-1.0],[22.87532269503339,25.207313046192645,-200.9418,1.0,5.0,2.0,-1.0],[25.207313046192645,28.005701467583748,0.0,1.0,5.0,2.0,-1.0],[28.005701467583748,28.4720995378156,1497.3,2.0,5.0,1.0,-1.0],[28.4720995378156,42.930439715002976,1860.0,1.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>[[-3.132943569688188,24.27451152586689,-1860.0,2.0,5.0,0.0,-1.0],[24.27451152586689,24.7470538551006,-401.8836,2.0,5.0,0.0,-1.0],[24.7470538551006,27.10976550126914,0.0,2.0,4.0,1.0,-1.0],[27.10976550126914,28.054850159736556,1497.3,2.0,4.0,1.0,-1.0],[28.054850159736556,43.64874702444893,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-3.132943569688188,24.27451152586689,-1860.0,2.0,5.0,0.0,-1.0],[24.27451152586689,24.7470538551006,-401.8837,2.0,5.0,0.0,-1.0],[24.7470538551006,27.10976550126914,0.0,2.0,4.0,1.0,-1.0],[27.10976550126914,28.054850159736556,1497.3,2.0,4.0,1.0,-1.0],[28.054850159736556,43.64874702444893,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>[[-2.949744650801829,23.86187624182115,-1860.0,2.0,2.0,2.0,-1.0],[23.86187624182115,24.650453326898294,-200.9418,1.0,2.0,2.0,-1.0],[24.650453326898294,27.410473124668307,0.0,1.0,2.0,2.0,-1.0],[27.410473124668307,27.80476166720688,1497.3,2.0,2.0,1.0,-1.0],[27.80476166720688,36.08482106051692,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-2.949744650801829,23.86187624182115,-1860.0,1.0,2.0,2.0,-1.0],[23.86187624182115,24.650453326898294,-200.9418,1.0,2.0,2.0,-1.0],[24.650453326898294,27.410473124668307,0.0,1.0,2.0,2.0,-1.0],[27.410473124668307,27.80476166720688,1497.3,2.0,2.0,1.0,-1.0],[27.80476166720688,36.08482106051692,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>[[-3.0940505631117587,22.816301005505593,-1860.0,2.0,2.0,0.0,-1.0],[22.816301005505593,24.749909331521813,-401.8836,1.0,2.0,0.0,-1.0],[24.749909331521813,27.45696098794452,0.0,1.0,1.0,1.0,-1.0],[27.45696098794452,30.164012644367226,1497.3,1.0,1.0,1.0,-1.0],[30.164012644367226,35.1913942920094,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-3.0940505631117587,22.816301005505593,-1860.0,2.0,2.0,0.0,-1.0],[22.816301005505593,24.749909331521813,-401.8837,1.0,2.0,0.0,-1.0],[24.749909331521813,27.45696098794452,0.0,1.0,1.0,1.0,-1.0],[27.45696098794452,30.164012644367226,1497.3,1.0,1.0,1.0,-1.0],[30.164012644367226,35.1913942920094,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>[[-3.133647285768385,22.892994648448287,-1860.0,2.0,1.0,0.0,-1.0],[22.892994648448287,36.106520553512134,0.0,1.0,1.0,1.0,-1.0],[36.106520553512134,36.50693042942316,181.35,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-3.133647285768385,7.277009487918283,-1860.0,1.0,1.0,0.0,-1.0],[7.277009487918283,20.0901255170711,-1860.0,2.0,1.0,0.0,-1.0],[20.0901255170711,22.892994648448287,-1860.0,1.0,1.0,0.0,-1.0],[22.892994648448287,36.106520553512134,0.0,1.0,1.0,1.0,-1.0],[36.106520553512134,36.50693042942316,181.3501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>[[-6.519053499862936,10.160326180227317,-1860.0,9.0,0.0,0.0,1.0],[10.160326180227317,11.468512821803023,-532.7423,8.0,0.0,1.0,1.0],[11.468512821803023,12.449652802984803,0.0,8.0,0.0,1.0,1.0],[12.449652802984803,18.663539350469406,1197.85,9.0,0.0,0.0,1.0],[18.663539350469406,25.858565879135792,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-6.519053499862936,10.160326180227317,-1860.0,9.0,0.0,0.0,1.0],[10.160326180227317,11.468512821803023,-532.7424,8.0,0.0,1.0,1.0],[11.468512821803023,12.449652802984803,0.0,8.0,0.0,1.0,1.0],[12.449652802984803,18.663539350469406,1197.85,9.0,0.0,0.0,1.0],[18.663539350469406,25.858565879135792,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>[[-23.157544165598864,16.90843076475364,-1860.0,8.0,9.0,2.0,-1.0],[16.90843076475364,17.403072430560456,-1808.4764,8.0,9.0,2.0,-1.0],[17.403072430560456,18.886997427980923,0.0,8.0,9.0,2.0,-1.0],[18.886997427980923,19.38163909378774,46.5,9.0,9.0,1.0,-1.0],[19.38163909378774,25.811980749276415,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-23.157544165598864,16.90843076475364,-1860.0,8.0,9.0,2.0,-1.0],[16.90843076475364,17.403072430560456,-1808.4764,7.0,9.0,2.0,-1.0],[17.403072430560456,18.886997427980923,0.0,7.0,9.0,2.0,-1.0],[18.886997427980923,19.38163909378774,46.5,8.0,9.0,1.0,-1.0],[19.38163909378774,25.811980749276415,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>[[-23.95174992965749,17.10621284315048,-1860.0,7.0,9.0,3.0,-1.0],[17.10621284315048,19.239094026153488,0.0,7.0,8.0,4.0,-1.0],[19.239094026153488,28.837059349667033,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[-23.95174992965749,17.10621284315048,-1860.0,7.0,9.0,3.0,-1.0],[17.10621284315048,19.239094026153488,0.0,7.0,8.0,4.0,-1.0],[19.239094026153488,28.837059349667033,1860.0,6.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C397" t="n">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>[[-27.589920189762932,15.94679725448454,-1860.0,6.0,0.0,0.0,1.0],[15.94679725448454,17.092500345122634,-733.6842,6.0,0.0,0.0,1.0],[17.092500345122634,19.383906526398814,0.0,6.0,8.0,3.0,-1.0],[19.383906526398814,29.1223827968226,1860.0,6.0,9.0,2.0,-1.0]]</t>
+          <t>[[-27.589920189762932,15.94679725448454,-1860.0,6.0,0.0,0.0,1.0],[15.94679725448454,17.092500345122634,-733.6842,5.0,0.0,0.0,1.0],[17.092500345122634,19.383906526398814,0.0,5.0,8.0,3.0,-1.0],[19.383906526398814,29.1223827968226,1860.0,6.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>[[-28.266459330222244,16.8154451342167,-1860.0,5.0,0.0,0.0,1.0],[16.8154451342167,18.506016551633156,0.0,5.0,8.0,3.0,-1.0],[18.506016551633156,19.633064163244132,227.85,5.0,8.0,3.0,-1.0],[19.633064163244132,27.522397444520944,1860.0,5.0,9.0,2.0,-1.0]]</t>
+          <t>[[-28.266459330222244,16.8154451342167,-1860.0,5.0,0.0,0.0,1.0],[16.8154451342167,18.506016551633156,0.0,4.0,8.0,3.0,-1.0],[18.506016551633156,19.633064163244132,227.85,4.0,8.0,3.0,-1.0],[19.633064163244132,27.522397444520944,1860.0,5.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>[[-28.51583558333333,16.458330178919848,-1860.0,4.0,0.0,0.0,1.0],[16.458330178919848,17.582684322976174,-733.6842,4.0,0.0,0.0,1.0],[17.582684322976174,19.26921553906067,0.0,4.0,8.0,4.0,-1.0],[19.26921553906067,19.831392611088834,227.85,4.0,8.0,3.0,-1.0],[19.831392611088834,27.139694547454976,1860.0,4.0,9.0,2.0,-1.0]]</t>
+          <t>[[-28.51583558333333,16.458330178919848,-1860.0,3.0,0.0,0.0,1.0],[16.458330178919848,17.582684322976174,-733.6842,3.0,0.0,0.0,1.0],[17.582684322976174,19.26921553906067,0.0,3.0,8.0,4.0,-1.0],[19.26921553906067,19.831392611088834,227.85,3.0,8.0,3.0,-1.0],[19.831392611088834,27.139694547454976,1860.0,3.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>[[-28.51583558333333,16.659021744360256,-1860.0,3.0,0.0,0.0,1.0],[16.659021744360256,18.39651625696386,0.0,3.0,9.0,2.0,-1.0],[18.39651625696386,28.821483332585455,1860.0,4.0,9.0,1.0,-1.0]]</t>
+          <t>[[-28.51583558333333,16.659021744360256,-1860.0,3.0,0.0,0.0,1.0],[16.659021744360256,18.39651625696386,0.0,2.0,9.0,2.0,-1.0],[18.39651625696386,28.821483332585455,1860.0,3.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>[[-28.51583558333333,16.856873397231563,-1860.0,2.0,8.0,3.0,-1.0],[16.856873397231563,18.558349984002742,0.0,1.0,8.0,4.0,-1.0],[18.558349984002742,19.1255088462598,227.85,2.0,8.0,3.0,-1.0],[19.1255088462598,27.632891780115717,1860.0,2.0,8.0,3.0,-1.0]]</t>
+          <t>[[-28.51583558333333,16.856873397231563,-1860.0,1.0,8.0,3.0,-1.0],[16.856873397231563,18.558349984002742,0.0,1.0,8.0,4.0,-1.0],[18.558349984002742,19.1255088462598,227.85,2.0,8.0,3.0,-1.0],[19.1255088462598,27.632891780115717,1860.0,2.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>[[-28.352162380837775,16.97681646261686,-733.6842,0.0,0.0,0.0,1.0],[16.97681646261686,18.720238725826647,0.0,0.0,9.0,2.0,-1.0],[18.720238725826647,19.30137948022991,46.5,1.0,9.0,1.0,-1.0],[19.30137948022991,29.180772305085412,1860.0,1.0,9.0,1.0,-1.0]]</t>
+          <t>[[-28.352162380837775,16.97681646261686,-733.6843,0.0,0.0,0.0,1.0],[16.97681646261686,18.720238725826647,0.0,0.0,9.0,2.0,-1.0],[18.720238725826647,19.30137948022991,46.5,1.0,9.0,1.0,-1.0],[19.30137948022991,29.180772305085412,1860.0,1.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>[[-28.51583558333333,16.3082887319805,-733.6842,0.0,0.0,0.0,1.0],[16.3082887319805,17.989193393804772,0.0,0.0,8.0,2.0,-1.0],[17.989193393804772,18.549494947746194,227.85,0.0,8.0,2.0,-1.0],[18.549494947746194,26.954018256867542,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-28.51583558333333,16.3082887319805,-733.6843,0.0,0.0,0.0,1.0],[16.3082887319805,17.989193393804772,0.0,0.0,8.0,2.0,-1.0],[17.989193393804772,18.549494947746194,227.85,0.0,8.0,2.0,-1.0],[18.549494947746194,26.954018256867542,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>[[-28.292333007671303,-7.798825774169366,-1860.0,1.0,2.0,0.0,-1.0],[-7.798825774169366,-7.196075561419306,-200.9418,0.0,2.0,0.0,-1.0],[-7.196075561419306,18.119433374083087,0.0,0.0,2.0,1.0,-1.0],[18.119433374083087,31.379938054584343,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-28.292333007671303,-6.59332534866925,-1860.0,1.0,2.0,0.0,-1.0],[-6.59332534866925,18.119433374083087,0.0,0.0,2.0,1.0,-1.0],[18.119433374083087,31.379938054584343,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>[[-28.251498498182293,-8.062514982872095,-1860.0,1.0,1.0,0.0,-1.0],[-8.062514982872095,-6.874927717265614,-200.9418,0.0,1.0,0.0,-1.0],[-6.874927717265614,18.064404860470518,0.0,0.0,1.0,1.0,-1.0],[18.064404860470518,30.534071149338583,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-28.251498498182293,-6.281134084462369,-1860.0,1.0,1.0,0.0,-1.0],[-6.281134084462369,18.064404860470518,0.0,0.0,1.0,1.0,-1.0],[18.064404860470518,30.534071149338583,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>[[-28.51583558333333,-8.08576385353344,-1860.0,1.0,0.0,0.0,-1.0],[-8.08576385353344,-7.466670770812229,-200.9418,0.0,0.0,0.0,-1.0],[-7.466670770812229,32.77437960606635,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-28.51583558333333,-6.847577688091018,-1860.0,1.0,0.0,0.0,-1.0],[-6.847577688091018,32.77437960606635,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>[[-28.51583558333333,-8.161336289602811,-1860.0,8.0,0.0,0.0,1.0],[-8.161336289602811,14.587809979860712,-733.6842,8.0,0.0,0.0,1.0],[14.587809979860712,16.38379521166046,0.0,8.0,0.0,1.0,1.0],[16.38379521166046,22.370412650992964,1016.5,9.0,0.0,0.0,1.0],[22.370412650992964,30.751677066058473,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-28.51583558333333,-8.161336289602811,-1860.0,8.0,0.0,0.0,1.0],[-8.161336289602811,14.587809979860712,-733.6842,8.0,0.0,0.0,1.0],[14.587809979860712,16.38379521166046,0.0,8.0,0.0,1.0,1.0],[16.38379521166046,22.370412650992964,1016.5,9.0,0.0,0.0,1.0],[22.370412650992964,30.751677066058473,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>[[-11.908724046901925,20.73534036402382,-1860.0,4.0,9.0,0.0,-1.0],[20.73534036402382,21.176476369576875,-1808.4764,3.0,9.0,1.0,-1.0],[21.176476369576875,23.382156397342122,0.0,3.0,8.0,2.0,-1.0],[23.382156397342122,23.823292402895177,227.85,3.0,8.0,1.0,-1.0],[23.823292402895177,25.146700419554328,590.55,1.0,6.0,0.0,-1.0],[25.146700419554328,31.763740502850084,1860.0,1.0,6.0,0.0,-1.0]]</t>
+          <t>[[-11.908724046901925,20.73534036402382,-1860.0,4.0,9.0,0.0,-1.0],[20.73534036402382,21.176476369576875,-1808.4764,3.0,9.0,1.0,-1.0],[21.176476369576875,23.382156397342122,0.0,1.0,8.0,2.0,-1.0],[23.382156397342122,23.823292402895177,227.85,3.0,8.0,1.0,-1.0],[23.823292402895177,25.146700419554328,590.55,1.0,6.0,0.0,-1.0],[25.146700419554328,31.763740502850084,1860.0,1.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>[[-13.035674578375192,19.366164276537077,-1860.0,1.0,3.0,1.0,-1.0],[19.366164276537077,19.924816670587283,-1808.4764,1.0,3.0,1.0,-1.0],[19.924816670587283,22.15942624678813,0.0,1.0,3.0,1.0,-1.0],[22.15942624678813,22.718078640838343,46.5,2.0,3.0,0.0,-1.0],[22.718078640838343,42.27091243259575,1860.0,2.0,3.0,0.0,-1.0]]</t>
+          <t>[[-13.035674578375192,19.366164276537077,-1860.0,1.0,3.0,1.0,-1.0],[19.366164276537077,19.924816670587283,-1808.4764,1.0,3.0,1.0,-1.0],[19.924816670587283,22.15942624678813,0.0,0.0,3.0,1.0,-1.0],[22.15942624678813,22.718078640838343,46.5,1.0,3.0,0.0,-1.0],[22.718078640838343,42.27091243259575,1860.0,1.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>[[-12.446742943472662,20.89588487044766,-1860.0,2.0,2.0,0.0,-1.0],[20.89588487044766,21.49128893855338,-1808.4764,1.0,2.0,1.0,-1.0],[21.49128893855338,23.872905210976263,0.0,1.0,1.0,2.0,-1.0],[23.872905210976263,24.468309279081986,227.85,1.0,1.0,2.0,-1.0],[24.468309279081986,46.49825979899363,409.2,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-12.446742943472662,20.89588487044766,-1860.0,2.0,2.0,0.0,-1.0],[20.89588487044766,21.49128893855338,-1808.4764,1.0,2.0,1.0,-1.0],[21.49128893855338,23.872905210976263,0.0,1.0,1.0,2.0,-1.0],[23.872905210976263,24.468309279081986,227.85,1.0,1.0,2.0,-1.0],[24.468309279081986,26.254521483399145,409.2,0.0,0.0,0.0,-1.0],[26.254521483399145,46.49825979899363,409.2001,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>[[-13.362752798384967,18.067167782712055,-1860.0,1.0,2.0,0.0,-1.0],[18.067167782712055,19.8804324316215,-1808.4764,0.0,2.0,1.0,-1.0],[19.8804324316215,22.298118630167423,0.0,0.0,2.0,1.0,-1.0],[22.298118630167423,22.902540179803907,46.5,1.0,2.0,0.0,-1.0],[22.902540179803907,46.47498061562668,1860.0,1.0,2.0,0.0,-1.0]]</t>
+          <t>[[-13.362752798384967,18.067167782712055,-1860.0,0.0,2.0,0.0,-1.0],[18.067167782712055,19.8804324316215,-1808.4764,0.0,2.0,1.0,-1.0],[19.8804324316215,22.298118630167423,0.0,0.0,2.0,1.0,-1.0],[22.298118630167423,22.902540179803907,46.5,1.0,2.0,0.0,-1.0],[22.902540179803907,46.47498061562668,1860.0,1.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C437" t="n">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>[[-12.510026571708218,20.517998799094805,-1860.0,1.0,1.0,0.0,-1.0],[20.517998799094805,21.153153133148713,-1808.4764,0.0,1.0,1.0,-1.0],[21.153153133148713,23.058616135310423,0.0,0.0,0.0,2.0,-1.0],[23.058616135310423,50.37025249962831,227.85,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-12.510026571708218,20.517998799094805,-1860.0,1.0,1.0,0.0,-1.0],[20.517998799094805,21.153153133148713,-1808.4764,0.0,1.0,1.0,-1.0],[21.153153133148713,23.058616135310423,0.0,0.0,0.0,2.0,-1.0],[23.058616135310423,24.96407913747214,227.85,0.0,0.0,0.0,-1.0],[24.96407913747214,50.37025249962831,227.8501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>[[-13.468146016474295,6.028954467555527,-1860.0,1.0,1.0,0.0,-1.0],[6.028954467555527,21.12348387454636,-0.0,0.0,1.0,1.0,-1.0],[21.12348387454636,23.010300050420213,0.0,0.0,0.0,1.0,-1.0],[23.010300050420213,25.52605495158535,1860.0,0.0,0.0,0.0,-1.0],[25.52605495158535,48.79678778736288,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-13.468146016474295,6.028954467555527,-1860.0,1.0,1.0,0.0,-1.0],[6.028954467555527,21.12348387454636,0.0,0.0,1.0,1.0,-1.0],[21.12348387454636,23.010300050420213,0.0,0.0,0.0,1.0,-1.0],[23.010300050420213,25.52605495158535,1860.0,0.0,0.0,0.0,-1.0],[25.52605495158535,48.79678778736288,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -6149,11 +6149,11 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>[[-13.037180856471332,6.060877343205567,-1860.0,1.0,0.0,0.0,-1.0],[6.060877343205567,49.98641120246244,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-13.037180856471332,6.060877343205567,-1860.0,1.0,0.0,0.0,-1.0],[6.060877343205567,49.98641120246244,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C440" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="441">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>[[-12.888065504034058,18.190362976117605,-1860.0,9.0,0.0,0.0,1.0],[18.190362976117605,32.143943110063255,-0.0,9.0,0.0,1.0,1.0],[32.143943110063255,49.90304509872135,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-12.888065504034058,18.190362976117605,-1860.0,9.0,0.0,0.0,1.0],[18.190362976117605,32.143943110063255,0.0,9.0,0.0,1.0,1.0],[32.143943110063255,49.90304509872135,662.15,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>[[-12.761608216582523,18.15128723523793,-1860.0,8.0,0.0,0.0,1.0],[18.15128723523793,32.31969765065564,-0.0,8.0,0.0,1.0,1.0],[32.31969765065564,33.60773496114816,1678.65,9.0,0.0,2.0,1.0],[33.60773496114816,50.99623865279717,1860.0,9.0,1.0,1.0,1.0]]</t>
+          <t>[[-12.761608216582523,18.15128723523793,-1860.0,7.0,0.0,0.0,1.0],[18.15128723523793,32.31969765065564,0.0,8.0,0.0,1.0,1.0],[32.31969765065564,33.60773496114816,1678.6499,9.0,0.0,2.0,1.0],[33.60773496114816,50.99623865279717,1860.0,9.0,1.0,1.0,1.0]]</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>[[-12.73523555927291,17.54656383104959,-1860.0,7.0,0.0,0.0,1.0],[17.54656383104959,34.298197536334385,-0.0,7.0,0.0,1.0,1.0],[34.298197536334385,51.04983124161917,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[-12.73523555927291,17.54656383104959,-1860.0,7.0,0.0,0.0,1.0],[17.54656383104959,34.298197536334385,0.0,7.0,0.0,1.0,1.0],[34.298197536334385,51.04983124161917,1860.0,7.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>[[-12.630442718895095,18.12591559759094,-1860.0,6.0,0.0,0.0,1.0],[18.12591559759094,32.27384042317452,-0.0,6.0,0.0,1.0,1.0],[32.27384042317452,48.267146747747255,1860.0,6.0,9.0,2.0,-1.0]]</t>
+          <t>[[-12.630442718895095,18.12591559759094,-1860.0,6.0,0.0,0.0,1.0],[18.12591559759094,32.27384042317452,0.0,6.0,0.0,1.0,1.0],[32.27384042317452,48.267146747747255,1860.0,6.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>[[-12.931053183247252,17.377753250520712,-1860.0,5.0,0.0,0.0,1.0],[17.377753250520712,32.5321564674047,-0.0,5.0,0.0,1.0,1.0],[32.5321564674047,34.42645686951519,1678.65,6.0,0.0,0.0,1.0],[34.42645686951519,49.58086008639918,1860.0,6.0,1.0,0.0,1.0]]</t>
+          <t>[[-12.931053183247252,17.377753250520712,-1860.0,5.0,0.0,0.0,1.0],[17.377753250520712,32.5321564674047,0.0,5.0,0.0,1.0,1.0],[32.5321564674047,34.42645686951519,1678.6499,6.0,0.0,0.0,1.0],[34.42645686951519,49.58086008639918,1860.0,5.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>[[-12.789751678456406,17.524917111374926,-1860.0,4.0,0.0,0.0,1.0],[17.524917111374926,33.64974093575329,-0.0,4.0,0.0,1.0,1.0],[33.64974093575329,51.064550666081935,1860.0,4.0,9.0,2.0,-1.0]]</t>
+          <t>[[-12.789751678456406,17.524917111374926,-1860.0,4.0,0.0,0.0,1.0],[17.524917111374926,33.64974093575329,0.0,4.0,0.0,1.0,1.0],[33.64974093575329,51.064550666081935,1860.0,4.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C448" t="n">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>[[-12.387430091420587,17.799611991275615,-1860.0,3.0,0.0,0.0,1.0],[17.799611991275615,33.52202974267989,-0.0,3.0,0.0,1.0,1.0],[33.52202974267989,49.87334420414034,1860.0,3.0,9.0,2.0,-1.0]]</t>
+          <t>[[-12.387430091420587,17.799611991275615,-1860.0,3.0,0.0,0.0,1.0],[17.799611991275615,33.52202974267989,0.0,3.0,0.0,1.0,1.0],[33.52202974267989,49.87334420414034,1860.0,3.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>[[-11.166545990068537,28.404275155559752,-1860.0,3.0,0.0,0.0,1.0],[28.404275155559752,30.91670824417107,-873.8504,2.0,8.0,3.0,-1.0],[30.91670824417107,34.05724960493522,0.0,2.0,8.0,3.0,-1.0],[34.05724960493522,51.01617295306163,1860.0,3.0,9.0,1.0,-1.0]]</t>
+          <t>[[-11.166545990068537,28.404275155559752,-1860.0,3.0,0.0,0.0,1.0],[28.404275155559752,30.91670824417107,-873.8505,2.0,8.0,3.0,-1.0],[30.91670824417107,34.05724960493522,0.0,2.0,8.0,3.0,-1.0],[34.05724960493522,51.01617295306163,1860.0,3.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>[[-7.640204688437672,30.186354010912417,-1860.0,2.0,8.0,2.0,-1.0],[30.186354010912417,30.768301067825497,-873.8504,2.0,8.0,2.0,-1.0],[30.768301067825497,34.25998340930396,0.0,2.0,8.0,2.0,-1.0],[34.25998340930396,34.84193046621704,890.0,3.0,8.0,1.0,-1.0],[34.84193046621704,49.97255394595708,1860.0,3.0,9.0,0.0,-1.0]]</t>
+          <t>[[-7.640204688437672,30.186354010912417,-1860.0,2.0,8.0,2.0,-1.0],[30.186354010912417,30.768301067825497,-873.8505,2.0,8.0,2.0,-1.0],[30.768301067825497,34.25998340930396,0.0,1.0,8.0,2.0,-1.0],[34.25998340930396,34.84193046621704,889.9999,2.0,8.0,1.0,-1.0],[34.84193046621704,49.97255394595708,1860.0,3.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>[[-7.4856277310705694,30.797224793110733,-1860.0,1.0,8.0,2.0,-1.0],[30.797224793110733,34.22553994452995,0.0,1.0,8.0,2.0,-1.0],[34.22553994452995,35.368311661669686,890.0,2.0,8.0,1.0,-1.0],[35.368311661669686,49.08157226734657,1860.0,2.0,9.0,0.0,-1.0]]</t>
+          <t>[[-7.4856277310705694,30.797224793110733,-1860.0,1.0,8.0,2.0,-1.0],[30.797224793110733,34.22553994452995,0.0,1.0,8.0,2.0,-1.0],[34.22553994452995,35.368311661669686,889.9999,2.0,8.0,1.0,-1.0],[35.368311661669686,49.08157226734657,1860.0,1.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C452" t="n">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>[[-7.9743499847910035,30.436236141724955,-1860.0,1.0,0.0,0.0,1.0],[30.436236141724955,31.018214719399438,-873.8504,0.0,8.0,2.0,-1.0],[31.018214719399438,33.928107607771864,0.0,0.0,8.0,2.0,-1.0],[33.928107607771864,34.51008618544635,890.0,1.0,8.0,1.0,-1.0],[34.51008618544635,49.64152920498293,1860.0,1.0,9.0,0.0,-1.0]]</t>
+          <t>[[-7.9743499847910035,30.436236141724955,-1860.0,1.0,0.0,0.0,1.0],[30.436236141724955,31.018214719399438,-873.8505,0.0,8.0,2.0,-1.0],[31.018214719399438,33.928107607771864,0.0,0.0,8.0,2.0,-1.0],[33.928107607771864,34.51008618544635,889.9999,1.0,8.0,1.0,-1.0],[34.51008618544635,49.64152920498293,1860.0,1.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -6331,11 +6331,11 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>[[-7.847153200307435,30.646372336029042,-1860.0,1.0,0.0,0.0,1.0],[30.646372336029042,34.66808395922837,-0.0,1.0,0.0,1.0,1.0],[34.66808395922837,37.54073511865647,890.0,1.0,8.0,0.0,-1.0],[37.54073511865647,49.03133975636885,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[-7.847153200307435,30.646372336029042,-1860.0,1.0,0.0,0.0,1.0],[30.646372336029042,34.66808395922837,0.0,1.0,0.0,1.0,1.0],[34.66808395922837,37.54073511865647,889.9999,1.0,8.0,0.0,-1.0],[37.54073511865647,49.03133975636885,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C454" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="455">
@@ -6344,11 +6344,11 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>[[-7.981039677926239,29.75385873808272,-1860.0,1.0,0.0,0.0,1.0],[29.75385873808272,34.89952670390212,-873.8504,0.0,8.0,0.0,-1.0],[34.89952670390212,38.90171289953943,0.0,0.0,7.0,1.0,-1.0],[38.90171289953943,40.61693555481257,1071.35,0.0,7.0,1.0,-1.0],[40.61693555481257,48.6213079460872,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[-7.981039677926239,29.75385873808272,-1860.0,1.0,0.0,0.0,1.0],[29.75385873808272,34.89952670390212,-873.8505,0.0,8.0,0.0,-1.0],[34.89952670390212,38.90171289953943,0.0,0.0,7.0,1.0,-1.0],[38.90171289953943,40.61693555481257,1071.3499,0.0,7.0,1.0,-1.0],[40.61693555481257,48.6213079460872,1860.0,0.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C455" t="n">
-        <v>-873.8504</v>
+        <v>-873.8505</v>
       </c>
     </row>
     <row r="456">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>[[-7.391476067821784,8.815961861520975,-986.1496,0.0,0.0,0.0,1.0],[8.815961861520975,33.40655734052378,-0.0,0.0,8.0,1.0,-1.0],[33.40655734052378,47.93736375993453,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-7.391476067821784,8.815961861520975,-986.1497,0.0,0.0,0.0,1.0],[8.815961861520975,33.40655734052378,0.0,0.0,8.0,1.0,-1.0],[33.40655734052378,47.93736375993453,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>[[-7.50252825896867,8.725470877811897,-1860.0,1.0,7.0,0.0,-1.0],[8.725470877811897,33.36798808551572,-0.0,0.0,7.0,1.0,-1.0],[33.36798808551572,52.00013524256007,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-7.50252825896867,8.725470877811897,-1860.0,1.0,7.0,0.0,-1.0],[8.725470877811897,33.36798808551572,0.0,0.0,7.0,1.0,-1.0],[33.36798808551572,52.00013524256007,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>[[-7.88717335140371,9.044753456036549,-1860.0,1.0,6.0,0.0,-1.0],[9.044753456036549,32.874872666508026,-0.0,0.0,6.0,1.0,-1.0],[32.874872666508026,54.19655827587724,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-7.88717335140371,9.044753456036549,-1860.0,1.0,6.0,0.0,-1.0],[9.044753456036549,32.874872666508026,0.0,0.0,6.0,1.0,-1.0],[32.874872666508026,54.19655827587724,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>[[-7.871601879230988,9.1470993319877,-1860.0,1.0,5.0,0.0,-1.0],[9.1470993319877,34.35999001527465,-0.0,0.0,5.0,1.0,-1.0],[34.35999001527465,54.5303025619042,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-7.871601879230988,9.1470993319877,-1860.0,1.0,5.0,0.0,-1.0],[9.1470993319877,34.35999001527465,0.0,0.0,5.0,1.0,-1.0],[34.35999001527465,54.5303025619042,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>[[-8.06501593357726,9.678007584631597,-1860.0,1.0,4.0,0.0,-1.0],[9.678007584631597,34.151143471816226,-0.0,0.0,4.0,1.0,-1.0],[34.151143471816226,52.5059953872047,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-8.06501593357726,9.678007584631597,-1860.0,1.0,4.0,0.0,-1.0],[9.678007584631597,34.151143471816226,0.0,0.0,4.0,1.0,-1.0],[34.151143471816226,52.5059953872047,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>[[-7.452173238962049,9.01199110040751,-1860.0,1.0,3.0,0.0,-1.0],[9.01199110040751,34.88424934798826,-0.0,0.0,3.0,1.0,-1.0],[34.88424934798826,50.76040781809462,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-7.452173238962049,9.01199110040751,-1860.0,1.0,3.0,0.0,-1.0],[9.01199110040751,34.88424934798826,0.0,0.0,3.0,1.0,-1.0],[34.88424934798826,50.76040781809462,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>[[-8.132259430011528,9.377048097731977,-1860.0,1.0,2.0,0.0,-1.0],[9.377048097731977,33.52781710151612,-0.0,0.0,2.0,1.0,-1.0],[33.52781710151612,51.640893854354225,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-8.132259430011528,9.377048097731977,-1860.0,1.0,2.0,0.0,-1.0],[9.377048097731977,33.52781710151612,0.0,0.0,2.0,1.0,-1.0],[33.52781710151612,51.640893854354225,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>[[-7.811071104687318,8.991548733924635,-1860.0,1.0,1.0,0.0,-1.0],[8.991548733924635,30.317950836778262,-0.0,0.0,1.0,1.0,-1.0],[30.317950836778262,33.54922388266518,0.0,0.0,0.0,1.0,-1.0],[33.54922388266518,36.7804969285521,1860.0,0.0,0.0,0.0,-1.0],[36.7804969285521,56.16813520387358,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-7.811071104687318,8.991548733924635,-1860.0,1.0,1.0,0.0,-1.0],[8.991548733924635,33.54922388266518,0.0,0.0,1.0,1.0,-1.0],[33.54922388266518,56.16813520387358,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -6461,11 +6461,11 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>[[-7.509250764453817,9.287177164359285,-1860.0,1.0,0.0,0.0,-1.0],[9.287177164359285,54.07765164119422,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-7.509250764453817,9.287177164359285,-1860.0,1.0,0.0,0.0,-1.0],[9.287177164359285,54.07765164119422,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C464" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="465">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>[[-7.998756354782032,3.2823498029561913,-1860.0,9.0,0.0,0.0,1.0],[3.2823498029561913,9.219774096502626,-733.6843,9.0,0.0,0.0,1.0],[9.219774096502626,50.781744151327665,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-7.998756354782032,3.2823498029561913,-1860.0,9.0,0.0,0.0,1.0],[3.2823498029561913,9.219774096502626,-733.6842,9.0,0.0,0.0,1.0],[9.219774096502626,50.781744151327665,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>[[-7.5259422466292625,8.88714186218196,-1860.0,9.0,0.0,0.0,1.0],[8.88714186218196,29.555469999203503,-733.6843,9.0,0.0,0.0,1.0],[29.555469999203503,52.65536615234522,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-7.5259422466292625,8.88714186218196,-1860.0,9.0,0.0,0.0,1.0],[8.88714186218196,29.555469999203503,-733.6842,9.0,0.0,0.0,1.0],[29.555469999203503,52.65536615234522,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>[[-7.83124313551667,9.15363989450027,-1860.0,8.0,0.0,0.0,1.0],[9.15363989450027,29.778140716663696,-733.6843,8.0,0.0,0.0,1.0],[29.778140716663696,32.81115554345243,0.0,8.0,8.0,2.0,-1.0],[32.81115554345243,35.23756740488342,227.85,8.0,8.0,1.0,-1.0],[35.23756740488342,52.22245043490036,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-7.83124313551667,9.15363989450027,-1860.0,8.0,0.0,0.0,1.0],[9.15363989450027,29.778140716663696,-733.6842,8.0,0.0,0.0,1.0],[29.778140716663696,32.81115554345243,0.0,8.0,8.0,2.0,-1.0],[32.81115554345243,35.23756740488342,227.85,8.0,8.0,1.0,-1.0],[35.23756740488342,52.22245043490036,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>[[-7.948929564089551,8.896219842097295,-1860.0,7.0,0.0,0.0,1.0],[8.896219842097295,29.22657257370211,-733.6843,7.0,0.0,0.0,1.0],[29.22657257370211,32.13090867821708,0.0,7.0,8.0,1.0,-1.0],[32.13090867821708,35.616112003635045,227.85,7.0,8.0,1.0,-1.0],[35.616112003635045,49.556925305306926,1860.0,7.0,8.0,1.0,-1.0]]</t>
+          <t>[[-7.948929564089551,8.896219842097295,-1860.0,7.0,0.0,0.0,1.0],[8.896219842097295,29.22657257370211,-733.6842,7.0,0.0,0.0,1.0],[29.22657257370211,32.13090867821708,0.0,7.0,8.0,1.0,-1.0],[32.13090867821708,35.616112003635045,227.85,7.0,8.0,1.0,-1.0],[35.616112003635045,49.556925305306926,1860.0,7.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>[[-7.779917561568604,9.173138445962588,-1860.0,6.0,0.0,0.0,1.0],[9.173138445962588,30.364458455376578,-733.6843,6.0,0.0,0.0,1.0],[30.364458455376578,33.39178988529286,0.0,6.0,8.0,2.0,-1.0],[33.39178988529286,34.602722457259375,227.85,6.0,8.0,2.0,-1.0],[34.602722457259375,52.161244750773825,1860.0,6.0,8.0,2.0,-1.0]]</t>
+          <t>[[-7.779917561568604,9.173138445962588,-1860.0,6.0,0.0,0.0,1.0],[9.173138445962588,30.364458455376578,-733.6842,6.0,0.0,0.0,1.0],[30.364458455376578,33.39178988529286,0.0,6.0,8.0,2.0,-1.0],[33.39178988529286,34.602722457259375,227.85,6.0,8.0,2.0,-1.0],[34.602722457259375,52.161244750773825,1860.0,6.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>[[-7.778354666204955,9.193166131691363,-1860.0,5.0,0.0,0.0,1.0],[9.193166131691363,29.80144138627975,-733.6843,5.0,0.0,0.0,1.0],[29.80144138627975,33.438195842971815,0.0,5.0,8.0,3.0,-1.0],[33.438195842971815,34.65044732853584,227.85,5.0,8.0,1.0,-1.0],[34.65044732853584,52.22809386921417,1860.0,5.0,8.0,1.0,-1.0]]</t>
+          <t>[[-7.778354666204955,9.193166131691363,-1860.0,5.0,0.0,0.0,1.0],[9.193166131691363,29.80144138627975,-733.6842,5.0,0.0,0.0,1.0],[29.80144138627975,33.438195842971815,0.0,5.0,8.0,3.0,-1.0],[33.438195842971815,34.65044732853584,227.85,5.0,8.0,1.0,-1.0],[34.65044732853584,52.22809386921417,1860.0,5.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>[[-7.795372522931508,8.664729823290738,-1860.0,4.0,0.0,0.0,1.0],[8.664729823290738,32.08872162368394,-733.6843,4.0,0.0,0.0,1.0],[32.08872162368394,35.254125921034365,0.0,4.0,8.0,2.0,-1.0],[35.254125921034365,54.87963256460705,1860.0,4.0,9.0,0.0,-1.0]]</t>
+          <t>[[-7.795372522931508,8.664729823290738,-1860.0,4.0,0.0,0.0,1.0],[8.664729823290738,32.08872162368394,-733.6842,4.0,0.0,0.0,1.0],[32.08872162368394,35.254125921034365,0.0,4.0,8.0,2.0,-1.0],[35.254125921034365,54.87963256460705,1860.0,4.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>[[-8.127396585498271,8.772950009571108,-1860.0,3.0,0.0,0.0,1.0],[8.772950009571108,31.70913467430812,-733.6843,3.0,0.0,0.0,1.0],[31.70913467430812,35.330637516108695,0.0,3.0,8.0,2.0,-1.0],[35.330637516108695,51.627400304211314,1860.0,3.0,8.0,1.0,-1.0]]</t>
+          <t>[[-8.127396585498271,8.772950009571108,-1860.0,3.0,0.0,0.0,1.0],[8.772950009571108,31.70913467430812,-733.6842,3.0,0.0,0.0,1.0],[31.70913467430812,35.330637516108695,0.0,3.0,8.0,2.0,-1.0],[35.330637516108695,51.627400304211314,1860.0,3.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>[[-2.2953996911123196,9.064560437938052,-1860.0,2.0,0.0,0.0,1.0],[9.064560437938052,30.161629249031595,-733.6843,2.0,0.0,0.0,1.0],[30.161629249031595,33.407332143045984,0.0,2.0,8.0,2.0,-1.0],[33.407332143045984,34.48923310771745,227.85,2.0,8.0,2.0,-1.0],[34.48923310771745,51.25869806012514,1860.0,2.0,8.0,2.0,-1.0]]</t>
+          <t>[[-2.2953996911123196,9.064560437938052,-1860.0,2.0,0.0,0.0,1.0],[9.064560437938052,30.161629249031595,-733.6842,2.0,0.0,0.0,1.0],[30.161629249031595,33.407332143045984,0.0,1.0,8.0,2.0,-1.0],[33.407332143045984,34.48923310771745,227.85,2.0,8.0,2.0,-1.0],[34.48923310771745,51.25869806012514,1860.0,1.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>[[1.1803474957605447,30.770960056018414,-1860.0,2.0,8.0,1.0,-1.0],[30.770960056018414,32.77710328044268,-1607.5347,1.0,8.0,1.0,-1.0],[32.77710328044268,36.28785392318514,0.0,1.0,8.0,1.0,-1.0],[36.28785392318514,37.79246134150333,227.85,2.0,8.0,0.0,-1.0],[37.79246134150333,50.83239230026104,1860.0,2.0,8.0,0.0,-1.0]]</t>
+          <t>[[1.1803474957605447,30.770960056018414,-1860.0,2.0,8.0,1.0,-1.0],[30.770960056018414,32.77710328044268,-1607.5346,1.0,8.0,1.0,-1.0],[32.77710328044268,36.28785392318514,0.0,1.0,8.0,1.0,-1.0],[36.28785392318514,37.79246134150333,227.85,2.0,8.0,0.0,-1.0],[37.79246134150333,50.83239230026104,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>[[8.84718636594401,30.1015725931777,-1860.0,1.0,8.0,0.0,-1.0],[30.1015725931777,30.553793576735863,-1607.5347,0.0,8.0,1.0,-1.0],[30.553793576735863,33.71934046164301,0.0,0.0,7.0,2.0,-1.0],[33.71934046164301,37.337108330108315,409.2,0.0,7.0,1.0,-1.0],[37.337108330108315,53.617063738202205,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.84718636594401,30.1015725931777,-1860.0,1.0,8.0,0.0,-1.0],[30.1015725931777,30.553793576735863,-1607.5346,0.0,8.0,1.0,-1.0],[30.553793576735863,33.71934046164301,0.0,0.0,7.0,2.0,-1.0],[33.71934046164301,37.337108330108315,409.2,0.0,7.0,1.0,-1.0],[37.337108330108315,53.617063738202205,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>[[8.629600166848725,24.505992982956336,-1860.0,1.0,8.0,0.0,-1.0],[24.505992982956336,26.9485149546652,-1808.4765,0.0,8.0,0.0,-1.0],[26.9485149546652,29.79812392165887,0.0,0.0,7.0,1.0,-1.0],[29.79812392165887,33.86899387450698,227.85,0.0,7.0,0.0,-1.0],[33.86899387450698,48.931212700044966,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[8.629600166848725,24.505992982956336,-1860.0,1.0,8.0,0.0,-1.0],[24.505992982956336,26.9485149546652,-1808.4764,0.0,8.0,0.0,-1.0],[26.9485149546652,29.79812392165887,0.0,0.0,7.0,1.0,-1.0],[29.79812392165887,33.86899387450698,227.85,0.0,7.0,0.0,-1.0],[33.86899387450698,48.931212700044966,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>[[8.578850941358132,25.691822073148877,-1860.0,1.0,7.0,0.0,-1.0],[25.691822073148877,29.11441629950702,-1808.4765,0.0,7.0,0.0,-1.0],[29.11441629950702,32.53701052586517,0.0,0.0,6.0,1.0,-1.0],[32.53701052586517,33.392659082454706,227.85,0.0,6.0,0.0,-1.0],[33.392659082454706,50.93345449254022,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[8.578850941358132,25.691822073148877,-1860.0,1.0,7.0,0.0,-1.0],[25.691822073148877,29.11441629950702,-1808.4764,0.0,7.0,0.0,-1.0],[29.11441629950702,32.53701052586517,0.0,0.0,6.0,1.0,-1.0],[32.53701052586517,33.392659082454706,227.85,0.0,6.0,0.0,-1.0],[33.392659082454706,50.93345449254022,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>[[8.58402710487467,24.645981237977466,-1860.0,1.0,6.0,1.0,-1.0],[24.645981237977466,27.684729317213126,-1808.4765,0.0,6.0,0.0,-1.0],[27.684729317213126,30.723477396448793,0.0,0.0,5.0,1.0,-1.0],[30.723477396448793,33.328118607222216,227.85,0.0,5.0,0.0,-1.0],[33.328118607222216,51.5606070826362,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[8.58402710487467,24.645981237977466,-1860.0,1.0,6.0,1.0,-1.0],[24.645981237977466,27.684729317213126,-1808.4764,0.0,6.0,0.0,-1.0],[27.684729317213126,30.723477396448793,0.0,0.0,5.0,1.0,-1.0],[30.723477396448793,33.328118607222216,227.85,0.0,5.0,0.0,-1.0],[33.328118607222216,51.5606070826362,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>[[8.712982875655083,24.97042591158625,-1860.0,1.0,6.0,0.0,-1.0],[24.97042591158625,25.692978935405414,-1808.4765,0.0,6.0,1.0,-1.0],[25.692978935405414,28.221914518772483,0.0,0.0,5.0,2.0,-1.0],[28.221914518772483,32.19595614977788,227.85,0.0,5.0,0.0,-1.0],[32.19595614977788,44.479357554703654,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[8.712982875655083,24.97042591158625,-1860.0,1.0,6.0,0.0,-1.0],[24.97042591158625,25.692978935405414,-1808.4764,0.0,6.0,1.0,-1.0],[25.692978935405414,28.221914518772483,0.0,0.0,5.0,2.0,-1.0],[28.221914518772483,32.19595614977788,227.85,0.0,5.0,0.0,-1.0],[32.19595614977788,44.479357554703654,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>[[8.82649513126567,14.423283006946393,-1860.0,8.0,13.0,2.0,0.0],[14.423283006946393,24.497501183171693,-1808.4765,0.0,6.0,0.0,-1.0],[24.497501183171693,27.48245471686808,0.0,0.0,5.0,1.0,-1.0],[27.48245471686808,45.765295110758444,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[8.82649513126567,14.423283006946393,-1860.0,8.0,13.0,2.0,0.0],[14.423283006946393,24.497501183171693,-1808.4764,0.0,6.0,0.0,-1.0],[24.497501183171693,27.48245471686808,0.0,0.0,5.0,1.0,-1.0],[27.48245471686808,45.765295110758444,1860.0,0.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>[[8.660443620862267,15.446325744617937,-1860.0,9.0,13.0,1.0,0.0],[15.446325744617937,24.171031332303798,-1808.4765,0.0,5.0,0.0,-1.0],[24.171031332303798,26.756129284210722,0.0,0.0,4.0,1.0,-1.0],[26.756129284210722,28.04867826016418,227.85,0.0,4.0,0.0,-1.0],[28.04867826016418,40.651030775710424,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[8.660443620862267,15.446325744617937,-1860.0,9.0,13.0,1.0,0.0],[15.446325744617937,24.171031332303798,-1808.4764,0.0,5.0,0.0,-1.0],[24.171031332303798,26.756129284210722,0.0,0.0,4.0,1.0,-1.0],[26.756129284210722,28.04867826016418,227.85,0.0,4.0,0.0,-1.0],[28.04867826016418,40.651030775710424,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>[[8.548162273718686,15.656809220158557,-1860.0,10.0,4.0,0.0,1.0],[15.656809220158557,24.310814198433185,-1808.4765,0.0,4.0,0.0,-1.0],[24.310814198433185,27.09245865573574,0.0,0.0,3.0,1.0,-1.0],[27.09245865573574,39.14625130404683,1860.0,0.0,3.0,1.0,-1.0]]</t>
+          <t>[[8.548162273718686,15.656809220158557,-1860.0,10.0,4.0,0.0,1.0],[15.656809220158557,24.310814198433185,-1808.4764,0.0,4.0,0.0,-1.0],[24.310814198433185,27.09245865573574,0.0,0.0,3.0,1.0,-1.0],[27.09245865573574,39.14625130404683,1860.0,0.0,3.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C484" t="n">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>[[8.632676841069298,15.006814361456225,-1860.0,10.0,3.0,0.0,1.0],[15.006814361456225,24.416255462979787,-1808.4765,0.0,3.0,0.0,-1.0],[24.416255462979787,27.148028686002757,0.0,0.0,2.0,1.0,-1.0],[27.148028686002757,28.058619760343745,227.85,0.0,2.0,1.0,-1.0],[28.058619760343745,38.68218229432196,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[8.632676841069298,15.006814361456225,-1860.0,9.0,3.0,0.0,1.0],[15.006814361456225,24.416255462979787,-1808.4764,0.0,3.0,0.0,-1.0],[24.416255462979787,27.148028686002757,0.0,0.0,2.0,1.0,-1.0],[27.148028686002757,28.058619760343745,227.85,0.0,2.0,1.0,-1.0],[28.058619760343745,38.68218229432196,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>[[8.616079852194712,15.022587019903547,-1860.0,10.0,2.0,0.0,1.0],[15.022587019903547,24.952673129852236,-1808.4765,0.0,2.0,0.0,-1.0],[24.952673129852236,27.51527599693577,0.0,0.0,1.0,1.0,-1.0],[27.51527599693577,40.32829033235344,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[8.616079852194712,15.022587019903547,-1860.0,10.0,2.0,0.0,1.0],[15.022587019903547,24.952673129852236,-1808.4764,0.0,2.0,0.0,-1.0],[24.952673129852236,27.51527599693577,0.0,0.0,1.0,1.0,-1.0],[27.51527599693577,40.32829033235344,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>[[8.08920529025552,15.947533603561325,-1860.0,10.0,1.0,0.0,1.0],[15.947533603561325,24.788152956030356,-1808.4765,0.0,1.0,0.0,-1.0],[24.788152956030356,27.407595727132293,0.0,0.0,0.0,1.0,-1.0],[27.407595727132293,40.50480958264197,227.85,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[8.08920529025552,15.947533603561325,-1860.0,10.0,1.0,0.0,1.0],[15.947533603561325,24.788152956030356,-1808.4764,0.0,1.0,0.0,-1.0],[24.788152956030356,27.407595727132293,0.0,0.0,0.0,1.0,-1.0],[27.407595727132293,30.35446884462197,227.85,0.0,0.0,0.0,-1.0],[30.35446884462197,40.50480958264197,227.8501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C487" t="n">
@@ -6773,11 +6773,11 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>[[8.842562569053646,15.41074883013695,-1860.0,9.0,0.0,1.0,1.0],[15.41074883013695,16.306410593011947,-481.2189,9.0,0.0,1.0,1.0],[16.306410593011947,18.097734118761938,0.0,9.0,0.0,1.0,1.0],[18.097734118761938,38.39940074392852,227.85,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[8.842562569053646,15.41074883013695,-1860.0,8.0,0.0,1.0,1.0],[15.41074883013695,16.306410593011947,-481.2188,9.0,0.0,1.0,1.0],[16.306410593011947,18.097734118761938,0.0,8.0,0.0,1.0,1.0],[18.097734118761938,38.39940074392852,227.8501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>227.85</v>
+        <v>227.8501</v>
       </c>
     </row>
     <row r="489">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>[[8.919905311090957,15.155385387502504,-1860.0,9.0,0.0,0.0,1.0],[15.155385387502504,18.273125425708276,-733.6843,9.0,0.0,0.0,1.0],[18.273125425708276,36.97956565494292,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[8.919905311090957,15.155385387502504,-1860.0,9.0,0.0,0.0,1.0],[15.155385387502504,18.273125425708276,-733.6842,9.0,0.0,0.0,1.0],[18.273125425708276,36.97956565494292,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>[[8.550657227158867,15.978622018906291,-1860.0,8.0,0.0,0.0,1.0],[15.978622018906291,17.464214977255775,-733.6843,8.0,0.0,0.0,1.0],[17.464214977255775,19.544045118945057,0.0,8.0,0.0,1.0,1.0],[19.544045118945057,30.83455160240114,1016.5,9.0,0.0,0.0,1.0],[30.83455160240114,37.96539780247866,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[8.550657227158867,15.978622018906291,-1860.0,7.0,0.0,0.0,1.0],[15.978622018906291,17.464214977255775,-733.6843,8.0,0.0,0.0,1.0],[17.464214977255775,19.544045118945057,0.0,7.0,0.0,1.0,1.0],[19.544045118945057,30.83455160240114,1016.4999,9.0,0.0,0.0,1.0],[30.83455160240114,37.96539780247866,1678.65,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>[[6.6348014116466745,15.477132553586404,-1860.0,7.0,0.0,0.0,1.0],[15.477132553586404,18.424576267566312,-733.6843,7.0,0.0,0.0,1.0],[18.424576267566312,20.38953874355292,0.0,7.0,0.0,1.0,1.0],[20.38953874355292,29.23186988549265,1016.5,8.0,0.0,0.0,1.0],[29.23186988549265,39.056682265425685,1860.0,8.0,9.0,2.0,-1.0]]</t>
+          <t>[[6.6348014116466745,15.477132553586404,-1860.0,6.0,0.0,0.0,1.0],[15.477132553586404,18.424576267566312,-733.6843,7.0,0.0,0.0,1.0],[18.424576267566312,20.38953874355292,0.0,6.0,0.0,1.0,1.0],[20.38953874355292,29.23186988549265,1016.4999,8.0,0.0,0.0,1.0],[29.23186988549265,39.056682265425685,1860.0,8.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>[[5.014245738012112,15.464234063745074,-1860.0,6.0,0.0,0.0,1.0],[15.464234063745074,17.48681244937081,-733.6843,6.0,0.0,0.0,1.0],[17.48681244937081,19.509390834996545,0.0,6.0,0.0,1.0,1.0],[19.509390834996545,29.285186365520925,1016.5,7.0,0.0,0.0,1.0],[29.285186365520925,38.38678910083674,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[5.014245738012112,15.464234063745074,-1860.0,5.0,0.0,0.0,1.0],[15.464234063745074,17.48681244937081,-733.6843,5.0,0.0,0.0,1.0],[17.48681244937081,19.509390834996545,0.0,5.0,0.0,1.0,1.0],[19.509390834996545,29.285186365520925,1016.4999,6.0,0.0,0.0,1.0],[29.285186365520925,38.38678910083674,1860.0,6.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>[[4.80593404755855,15.80707791294227,-1860.0,5.0,0.0,0.0,1.0],[15.80707791294227,17.226580347185333,-733.6843,5.0,0.0,0.0,1.0],[17.226580347185333,19.355833998549926,0.0,5.0,0.0,1.0,1.0],[19.355833998549926,29.292351038251347,1016.5,6.0,0.0,0.0,1.0],[29.292351038251347,39.93861929507431,1860.0,6.0,9.0,2.0,-1.0]]</t>
+          <t>[[4.80593404755855,15.80707791294227,-1860.0,3.0,0.0,0.0,1.0],[15.80707791294227,17.226580347185333,-733.6843,4.0,0.0,0.0,1.0],[17.226580347185333,19.355833998549926,0.0,4.0,0.0,1.0,1.0],[19.355833998549926,29.292351038251347,1016.4999,4.0,0.0,0.0,1.0],[29.292351038251347,39.93861929507431,1860.0,6.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>[[5.136988153927689,15.74779109715457,-1860.0,4.0,0.0,0.0,1.0],[15.74779109715457,18.82834679034947,-733.6843,4.0,0.0,0.0,1.0],[18.82834679034947,20.88205058581274,0.0,4.0,0.0,1.0,1.0],[20.88205058581274,30.123717665397443,1016.5,5.0,0.0,0.0,1.0],[30.123717665397443,39.0231007790716,1860.0,5.0,9.0,1.0,-1.0]]</t>
+          <t>[[5.136988153927689,15.74779109715457,-1860.0,4.0,0.0,0.0,1.0],[15.74779109715457,18.82834679034947,-733.6843,3.0,0.0,0.0,1.0],[18.82834679034947,20.88205058581274,0.0,3.0,0.0,1.0,1.0],[20.88205058581274,30.123717665397443,1016.4999,4.0,0.0,0.0,1.0],[30.123717665397443,39.0231007790716,1860.0,4.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>[[5.36313052343956,14.794150075647046,-1860.0,3.0,0.0,0.0,1.0],[14.794150075647046,18.162371344292577,-733.6843,3.0,0.0,0.0,1.0],[18.162371344292577,19.846481978615344,0.0,3.0,0.0,1.0,1.0],[19.846481978615344,30.287967911416487,1016.5,4.0,0.0,0.0,1.0],[30.287967911416487,38.70852108303031,1860.0,4.0,9.0,1.0,-1.0]]</t>
+          <t>[[5.36313052343956,14.794150075647046,-1860.0,3.0,0.0,0.0,1.0],[14.794150075647046,18.162371344292577,-733.6843,2.0,0.0,0.0,1.0],[18.162371344292577,19.846481978615344,0.0,2.0,0.0,1.0,1.0],[19.846481978615344,30.287967911416487,1016.4999,4.0,0.0,0.0,1.0],[30.287967911416487,38.70852108303031,1860.0,3.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C495" t="n">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>[[3.5918526248606204,18.159338784552713,-1860.0,3.0,0.0,0.0,1.0],[18.159338784552713,29.88438862040245,0.0,3.0,0.0,1.0,1.0],[29.88438862040245,30.239693160882744,890.0,3.0,8.0,3.0,-1.0],[30.239693160882744,38.76700213240982,1860.0,3.0,8.0,3.0,-1.0]]</t>
+          <t>[[3.5918526248606204,18.159338784552713,-1860.0,2.0,0.0,0.0,1.0],[18.159338784552713,29.88438862040245,0.0,2.0,0.0,1.0,1.0],[29.88438862040245,30.239693160882744,890.0,2.0,8.0,3.0,-1.0],[30.239693160882744,38.76700213240982,1860.0,2.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>[[3.3390809357406224,17.87989495737115,-1860.0,2.0,0.0,0.0,1.0],[17.87989495737115,29.938130975308656,0.0,2.0,0.0,1.0,1.0],[29.938130975308656,30.647438976363805,890.0,2.0,8.0,1.0,-1.0],[30.647438976363805,38.44982698797043,1860.0,2.0,8.0,1.0,-1.0]]</t>
+          <t>[[3.3390809357406224,17.87989495737115,-1860.0,1.0,0.0,0.0,1.0],[17.87989495737115,27.100898971088064,0.0,2.0,0.0,1.0,1.0],[27.100898971088064,29.938130975308656,0.0,0.0,0.0,1.0,1.0],[29.938130975308656,30.647438976363805,890.0,2.0,8.0,1.0,-1.0],[30.647438976363805,38.44982698797043,1860.0,2.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>[[3.7020015909171002,17.18838567738531,-1860.0,1.0,0.0,0.0,1.0],[17.18838567738531,18.96290989928902,-1860.0,0.0,0.0,0.0,1.0],[18.96290989928902,21.09233896557347,0.0,0.0,0.0,1.0,1.0],[21.09233896557347,29.61005523071129,0.0,1.0,0.0,1.0,1.0],[29.61005523071129,30.319864919472774,890.0,1.0,8.0,3.0,-1.0],[30.319864919472774,38.83758118461059,1860.0,1.0,8.0,3.0,-1.0]]</t>
+          <t>[[3.7020015909171002,18.96290989928902,-1860.0,0.0,0.0,0.0,1.0],[18.96290989928902,26.77081647566535,0.0,1.0,0.0,1.0,1.0],[26.77081647566535,28.545340697569063,0.0,0.0,0.0,1.0,1.0],[28.545340697569063,29.61005523071129,0.0,1.0,0.0,1.0,1.0],[29.61005523071129,30.319864919472774,890.0,1.0,8.0,3.0,-1.0],[30.319864919472774,38.83758118461059,1860.0,1.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>[[3.5676443893777567,24.40867347535547,-1860.0,1.0,3.0,0.0,-1.0],[24.40867347535547,26.49277638395324,-1074.7922,0.0,3.0,0.0,-1.0],[26.49277638395324,29.271580262083603,0.0,0.0,2.0,1.0,-1.0],[29.271580262083603,37.95534238124098,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[3.5676443893777567,24.40867347535547,-1860.0,0.0,3.0,0.0,-1.0],[24.40867347535547,26.49277638395324,-1074.7922,0.0,3.0,0.0,-1.0],[26.49277638395324,29.271580262083603,0.0,0.0,2.0,1.0,-1.0],[29.271580262083603,37.95534238124098,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>[[3.8386374432748696,18.05559317772364,-1860.0,8.0,0.0,0.0,1.0],[18.05559317772364,19.909978708303917,-733.6842,8.0,0.0,0.0,1.0],[19.909978708303917,22.073428493980902,0.0,8.0,0.0,1.0,1.0],[22.073428493980902,30.418163381592137,1016.5,9.0,0.0,0.0,1.0],[30.418163381592137,34.4359986978494,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[3.8386374432748696,18.05559317772364,-1860.0,8.0,0.0,0.0,1.0],[18.05559317772364,19.909978708303917,-733.6842,8.0,0.0,0.0,1.0],[19.909978708303917,22.073428493980902,0.0,8.0,0.0,1.0,1.0],[22.073428493980902,30.418163381592137,1016.5,9.0,0.0,0.0,1.0],[30.418163381592137,34.4359986978494,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C514" t="n">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>[[3.852624596638034,17.856215668709932,-1860.0,7.0,0.0,0.0,1.0],[17.856215668709932,20.65693388312431,-733.6842,7.0,0.0,0.0,1.0],[20.65693388312431,22.835270272113274,0.0,7.0,0.0,1.0,1.0],[22.835270272113274,29.681470351792864,1016.5,8.0,0.0,0.0,1.0],[29.681470351792864,34.66052495519621,1860.0,8.0,9.0,2.0,-1.0]]</t>
+          <t>[[3.852624596638034,17.856215668709932,-1860.0,6.0,0.0,0.0,1.0],[17.856215668709932,20.65693388312431,-733.6842,6.0,0.0,0.0,1.0],[20.65693388312431,22.835270272113274,0.0,6.0,0.0,1.0,1.0],[22.835270272113274,29.681470351792864,1016.5,7.0,0.0,0.0,1.0],[29.681470351792864,34.66052495519621,1860.0,7.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C515" t="n">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>[[3.7308772600832674,17.193471352098303,-1860.0,6.0,0.0,0.0,1.0],[17.193471352098303,20.63739077098587,-733.6842,6.0,0.0,0.0,1.0],[20.63739077098587,22.8289758557325,0.0,6.0,0.0,1.0,1.0],[22.8289758557325,29.716814693507636,1016.5,7.0,0.0,0.0,1.0],[29.716814693507636,34.72615203007137,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[3.7308772600832674,17.193471352098303,-1860.0,5.0,0.0,0.0,1.0],[17.193471352098303,20.63739077098587,-733.6842,5.0,0.0,0.0,1.0],[20.63739077098587,22.8289758557325,0.0,5.0,0.0,1.0,1.0],[22.8289758557325,29.716814693507636,1016.5,7.0,0.0,0.0,1.0],[29.716814693507636,34.72615203007137,1860.0,7.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C516" t="n">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>[[3.7331082354585186,17.71248440328762,-1860.0,5.0,0.0,0.0,1.0],[17.71248440328762,20.197706833123902,-733.6842,5.0,0.0,0.0,1.0],[20.197706833123902,22.37227645923065,0.0,5.0,0.0,1.0,1.0],[22.37227645923065,30.75990215992811,1016.5,6.0,0.0,0.0,1.0],[30.75990215992811,34.487735804682536,1860.0,6.0,9.0,0.0,-1.0]]</t>
+          <t>[[3.7331082354585186,17.71248440328762,-1860.0,4.0,0.0,0.0,1.0],[17.71248440328762,20.197706833123902,-733.6842,4.0,0.0,0.0,1.0],[20.197706833123902,22.37227645923065,0.0,4.0,0.0,1.0,1.0],[22.37227645923065,30.75990215992811,1016.5,5.0,0.0,0.0,1.0],[30.75990215992811,34.487735804682536,1860.0,6.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C517" t="n">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>[[2.7878386935804578,16.8274046597201,-1860.0,4.0,0.0,0.0,1.0],[16.8274046597201,20.337296151255007,-733.6842,4.0,0.0,0.0,1.0],[20.337296151255007,22.443231046175953,0.0,4.0,0.0,1.0,1.0],[22.443231046175953,30.164992327552756,1016.5,5.0,0.0,0.0,1.0],[30.164992327552756,37.53576445977606,1860.0,5.0,9.0,2.0,-1.0]]</t>
+          <t>[[2.7878386935804578,16.8274046597201,-1860.0,3.0,0.0,0.0,1.0],[16.8274046597201,20.337296151255007,-733.6842,3.0,0.0,0.0,1.0],[20.337296151255007,22.443231046175953,0.0,3.0,0.0,1.0,1.0],[22.443231046175953,30.164992327552756,1016.5,4.0,0.0,0.0,1.0],[30.164992327552756,37.53576445977606,1860.0,4.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>[[3.0552479507692314,18.04728954197882,-1860.0,3.0,0.0,0.0,1.0],[18.04728954197882,20.32868717542376,-733.6842,3.0,0.0,0.0,1.0],[20.32868717542376,22.6100848088687,0.0,3.0,0.0,1.0,1.0],[22.6100848088687,30.10610560447349,1016.5,4.0,0.0,0.0,1.0],[30.10610560447349,30.432019552108486,1725.15,5.0,9.0,1.0,-1.0],[30.432019552108486,35.320728766633344,1860.0,5.0,9.0,1.0,-1.0]]</t>
+          <t>[[3.0552479507692314,18.04728954197882,-1860.0,3.0,0.0,0.0,1.0],[18.04728954197882,20.32868717542376,-733.6842,2.0,0.0,0.0,1.0],[20.32868717542376,22.6100848088687,0.0,2.0,0.0,1.0,1.0],[22.6100848088687,30.10610560447349,1016.5,3.0,0.0,0.0,1.0],[30.10610560447349,30.432019552108486,1725.15,4.0,9.0,1.0,-1.0],[30.432019552108486,35.320728766633344,1860.0,4.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C519" t="n">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>[[2.828559302774794,17.378212630666162,-1860.0,2.0,0.0,0.0,1.0],[17.378212630666162,19.96481766673574,-733.6842,2.0,0.0,0.0,1.0],[19.96481766673574,22.228097073296617,0.0,2.0,0.0,1.0,1.0],[22.228097073296617,30.63456344052274,1016.5,3.0,0.0,0.0,1.0],[30.63456344052274,34.837796624135805,1860.0,3.0,9.0,0.0,-1.0]]</t>
+          <t>[[2.828559302774794,17.378212630666162,-1860.0,2.0,0.0,0.0,1.0],[17.378212630666162,19.96481766673574,-733.6842,2.0,0.0,0.0,1.0],[19.96481766673574,22.228097073296617,0.0,2.0,0.0,1.0,1.0],[22.228097073296617,30.63456344052274,1016.5,2.0,0.0,0.0,1.0],[30.63456344052274,34.837796624135805,1860.0,3.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>[[2.760839825309646,18.24087360009212,-1860.0,1.0,0.0,0.0,1.0],[18.24087360009212,20.260008440281137,-1860.0,0.0,0.0,0.0,1.0],[20.260008440281137,22.279143280470155,0.0,0.0,0.0,1.0,1.0],[22.279143280470155,30.01916016786139,0.0,1.0,0.0,1.0,1.0],[30.01916016786139,30.355682641226228,890.0,1.0,8.0,1.0,-1.0],[30.355682641226228,36.07656468842845,1860.0,1.0,8.0,1.0,-1.0]]</t>
+          <t>[[2.760839825309646,20.260008440281137,-1860.0,1.0,0.0,0.0,1.0],[20.260008440281137,26.990457907577863,0.0,0.0,0.0,1.0,1.0],[26.990457907577863,30.01916016786139,0.0,1.0,0.0,1.0,1.0],[30.01916016786139,30.355682641226228,890.0,0.0,8.0,1.0,-1.0],[30.355682641226228,36.07656468842845,1860.0,1.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>[[2.7173527521838956,25.235552994200457,-1860.0,1.0,8.0,0.0,-1.0],[25.235552994200457,26.229003004877658,-1074.7922,0.0,8.0,1.0,-1.0],[26.229003004877658,29.209353036909263,0.0,0.0,7.0,2.0,-1.0],[29.209353036909263,30.202803047586464,890.0,0.0,7.0,0.0,-1.0],[30.202803047586464,35.501203104531534,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[2.7173527521838956,25.235552994200457,-1860.0,1.0,8.0,0.0,-1.0],[25.235552994200457,26.229003004877658,-1074.7923,0.0,8.0,1.0,-1.0],[26.229003004877658,29.209353036909263,0.0,0.0,7.0,2.0,-1.0],[29.209353036909263,30.202803047586464,890.0,0.0,7.0,0.0,-1.0],[30.202803047586464,35.501203104531534,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>[[3.033755273987173,25.887433501254144,-1860.0,1.0,7.0,0.0,-1.0],[25.887433501254144,26.590623600554668,-1074.7922,0.0,7.0,0.0,-1.0],[26.590623600554668,29.403383997756755,0.0,0.0,6.0,1.0,-1.0],[29.403383997756755,30.45816914670754,890.0,0.0,6.0,0.0,-1.0],[30.45816914670754,37.84166518936303,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[3.033755273987173,25.887433501254144,-1860.0,1.0,7.0,0.0,-1.0],[25.887433501254144,26.590623600554668,-1074.7923,0.0,7.0,0.0,-1.0],[26.590623600554668,29.403383997756755,0.0,0.0,6.0,1.0,-1.0],[29.403383997756755,30.45816914670754,890.0,0.0,6.0,0.0,-1.0],[30.45816914670754,37.84166518936303,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C526" t="n">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>[[2.8988015939037197,25.708916748372157,-1860.0,1.0,6.0,0.0,-1.0],[25.708916748372157,27.070714668041912,-1074.7922,0.0,6.0,1.0,-1.0],[27.070714668041912,30.134759987298867,0.0,0.0,5.0,2.0,-1.0],[30.134759987298867,32.1774568668035,890.0,0.0,5.0,0.0,-1.0],[32.1774568668035,36.60330010573021,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[2.8988015939037197,25.708916748372157,-1860.0,1.0,6.0,0.0,-1.0],[25.708916748372157,27.070714668041912,-1074.7923,0.0,6.0,1.0,-1.0],[27.070714668041912,30.134759987298867,0.0,0.0,5.0,2.0,-1.0],[30.134759987298867,32.1774568668035,890.0,0.0,5.0,0.0,-1.0],[32.1774568668035,36.60330010573021,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>[[2.8543732486296145,26.25298389498913,-1860.0,1.0,4.0,0.0,-1.0],[26.25298389498913,29.480378466900785,0.0,0.0,4.0,2.0,-1.0],[29.480378466900785,42.79338107603637,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[2.8543732486296145,26.25298389498913,-1860.0,1.0,4.0,0.0,-1.0],[26.25298389498913,29.480378466900785,0.0,0.0,3.0,2.0,-1.0],[29.480378466900785,42.79338107603637,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>[[2.7500164488974335,25.80571477074939,-1860.0,1.0,3.0,1.0,-1.0],[25.80571477074939,29.71346024902938,0.0,0.0,3.0,2.0,-1.0],[29.71346024902938,41.43669668386936,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[2.7500164488974335,25.80571477074939,-1860.0,1.0,3.0,1.0,-1.0],[25.80571477074939,29.71346024902938,0.0,0.0,2.0,2.0,-1.0],[29.71346024902938,41.43669668386936,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C530" t="n">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>[[2.8374702402250533,25.5441163892489,-1860.0,1.0,2.0,1.0,-1.0],[25.5441163892489,29.193398806056305,0.0,0.0,2.0,2.0,-1.0],[29.193398806056305,42.9795768251065,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[2.8374702402250533,25.5441163892489,-1860.0,1.0,2.0,1.0,-1.0],[25.5441163892489,29.193398806056305,0.0,0.0,1.0,2.0,-1.0],[29.193398806056305,42.9795768251065,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>[[2.9255890984794393,25.650125412853704,-1860.0,1.0,1.0,1.0,-1.0],[25.650125412853704,28.769179416787427,0.0,0.0,1.0,2.0,-1.0],[28.769179416787427,47.037924296970665,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[2.9255890984794393,25.650125412853704,-1860.0,1.0,1.0,1.0,-1.0],[25.650125412853704,26.095704556272807,0.0,0.0,1.0,2.0,-1.0],[26.095704556272807,28.769179416787427,0.0,0.0,0.0,2.0,-1.0],[28.769179416787427,30.55149599046384,1860.0,0.0,0.0,0.0,-1.0],[30.55149599046384,47.037924296970665,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C532" t="n">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>[[2.901672760188005,21.739943251045954,-1860.0,9.0,0.0,0.0,1.0],[21.739943251045954,36.296788630345276,0.0,9.0,0.0,1.0,1.0],[36.296788630345276,45.28778136461839,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[2.901672760188005,21.739943251045954,-1860.0,8.0,0.0,0.0,1.0],[21.739943251045954,36.296788630345276,0.0,9.0,0.0,1.0,1.0],[36.296788630345276,45.28778136461839,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C538" t="n">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>[[-1.4814532064442627,21.341401455558504,-1860.0,8.0,0.0,0.0,1.0],[21.341401455558504,36.081161758101956,0.0,8.0,0.0,1.0,1.0],[36.081161758101956,36.55663789689368,890.0,8.0,8.0,4.0,-1.0],[36.55663789689368,45.59068453393645,1860.0,8.0,8.0,4.0,-1.0]]</t>
+          <t>[[-1.4814532064442627,21.341401455558504,-1860.0,7.0,0.0,0.0,1.0],[21.341401455558504,36.081161758101956,0.0,7.0,0.0,1.0,1.0],[36.081161758101956,36.55663789689368,890.0,7.0,8.0,4.0,-1.0],[36.55663789689368,45.59068453393645,1860.0,8.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C539" t="n">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>[[-3.0126129553512984,20.656689076322607,-1860.0,7.0,0.0,0.0,1.0],[20.656689076322607,35.764754202922965,0.0,7.0,0.0,1.0,1.0],[35.764754202922965,36.268356373809645,890.0,7.0,8.0,4.0,-1.0],[36.268356373809645,46.8440019624299,1860.0,7.0,8.0,4.0,-1.0]]</t>
+          <t>[[-3.0126129553512984,20.656689076322607,-1860.0,6.0,0.0,0.0,1.0],[20.656689076322607,35.764754202922965,0.0,7.0,0.0,1.0,1.0],[35.764754202922965,36.268356373809645,890.0,7.0,8.0,4.0,-1.0],[36.268356373809645,46.8440019624299,1860.0,6.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>[[-6.945689090104867,20.737775993827807,-1860.0,6.0,0.0,0.0,1.0],[20.737775993827807,36.70900584994281,0.0,6.0,0.0,1.0,1.0],[36.70900584994281,37.24138017847997,890.0,6.0,8.0,4.0,-1.0],[37.24138017847997,45.75936943507464,1860.0,6.0,8.0,4.0,-1.0]]</t>
+          <t>[[-6.945689090104867,20.737775993827807,-1860.0,5.0,0.0,0.0,1.0],[20.737775993827807,36.70900584994281,0.0,4.0,0.0,1.0,1.0],[36.70900584994281,37.24138017847997,890.0,4.0,8.0,4.0,-1.0],[37.24138017847997,45.75936943507464,1860.0,6.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C541" t="n">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>[[-11.39848926879086,21.134509917775084,-1860.0,5.0,0.0,0.0,1.0],[21.134509917775084,36.544877953516846,0.0,5.0,0.0,1.0,1.0],[36.544877953516846,45.106193528928934,1860.0,5.0,8.0,3.0,-1.0]]</t>
+          <t>[[-11.39848926879086,21.134509917775084,-1860.0,4.0,0.0,0.0,1.0],[21.134509917775084,36.544877953516846,0.0,4.0,0.0,1.0,1.0],[36.544877953516846,45.106193528928934,1860.0,5.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>[[-14.292704665772625,21.431522159172808,-1860.0,4.0,0.0,0.0,1.0],[21.431522159172808,36.31661666956674,0.0,4.0,0.0,1.0,1.0],[36.31661666956674,36.9120204499825,890.0,4.0,8.0,4.0,-1.0],[36.9120204499825,44.65226959538734,1860.0,4.0,8.0,4.0,-1.0]]</t>
+          <t>[[-14.292704665772625,21.431522159172808,-1860.0,3.0,0.0,0.0,1.0],[21.431522159172808,36.31661666956674,0.0,3.0,0.0,1.0,1.0],[36.31661666956674,36.9120204499825,890.0,3.0,8.0,4.0,-1.0],[36.9120204499825,44.65226959538734,1860.0,3.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>[[-14.821895666685798,21.07748771183696,-1860.0,3.0,0.0,0.0,1.0],[21.07748771183696,36.633887175863485,0.0,3.0,0.0,1.0,1.0],[36.633887175863485,37.830533288480915,1678.65,4.0,0.0,0.0,1.0],[37.830533288480915,44.412086907876756,1860.0,4.0,9.0,2.0,-1.0]]</t>
+          <t>[[-14.821895666685798,21.07748771183696,-1860.0,3.0,0.0,0.0,1.0],[21.07748771183696,36.633887175863485,0.0,2.0,0.0,1.0,1.0],[36.633887175863485,37.830533288480915,1678.65,3.0,0.0,0.0,1.0],[37.830533288480915,44.412086907876756,1860.0,3.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>[[-15.800245108512707,22.319923039660644,-1860.0,2.0,0.0,0.0,1.0],[22.319923039660644,36.9326541631271,0.0,2.0,0.0,1.0,1.0],[36.9326541631271,37.567990298929985,890.0,2.0,8.0,4.0,-1.0],[37.567990298929985,47.09803233597332,1860.0,2.0,8.0,4.0,-1.0]]</t>
+          <t>[[-15.800245108512707,22.319923039660644,-1860.0,2.0,0.0,0.0,1.0],[22.319923039660644,36.9326541631271,0.0,2.0,0.0,1.0,1.0],[36.9326541631271,37.567990298929985,890.0,1.0,8.0,4.0,-1.0],[37.567990298929985,47.09803233597332,1860.0,1.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>[[-14.74384651414167,18.903274861010285,-1860.0,1.0,0.0,0.0,1.0],[18.903274861010285,20.772559381852066,-1860.0,0.0,0.0,0.0,1.0],[20.772559381852066,23.264938742974433,0.0,0.0,0.0,1.0,1.0],[23.264938742974433,36.97302522914745,0.0,1.0,0.0,1.0,1.0],[36.97302522914745,46.94254267363692,1860.0,1.0,8.0,2.0,-1.0]]</t>
+          <t>[[-14.74384651414167,20.772559381852066,-1860.0,1.0,0.0,0.0,1.0],[20.772559381852066,30.742076826341535,0.0,1.0,0.0,1.0,1.0],[30.742076826341535,36.97302522914745,0.0,0.0,0.0,1.0,1.0],[36.97302522914745,46.94254267363692,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>[[-14.12082405334311,28.901135585017197,-1860.0,1.0,8.0,0.0,-1.0],[28.901135585017197,33.08382610541334,-1074.7922,0.0,8.0,0.0,-1.0],[33.08382610541334,36.66898940861003,0.0,0.0,7.0,1.0,-1.0],[36.66898940861003,37.26651662580947,890.0,0.0,7.0,0.0,-1.0],[37.26651662580947,45.0343704494023,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-14.12082405334311,28.901135585017197,-1860.0,1.0,8.0,0.0,-1.0],[28.901135585017197,33.08382610541334,-1074.7923,0.0,8.0,0.0,-1.0],[33.08382610541334,36.66898940861003,0.0,0.0,7.0,1.0,-1.0],[36.66898940861003,37.26651662580947,890.0,0.0,7.0,0.0,-1.0],[37.26651662580947,45.0343704494023,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C551" t="n">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>[[-14.23646373709396,26.961725408764313,-1860.0,1.0,7.0,0.0,-1.0],[26.961725408764313,36.51492868896334,0.0,0.0,7.0,1.0,-1.0],[36.51492868896334,44.873981559137476,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[-14.23646373709396,26.961725408764313,-1860.0,1.0,7.0,0.0,-1.0],[26.961725408764313,36.51492868896334,0.0,0.0,7.0,1.0,-1.0],[36.51492868896334,44.873981559137476,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C552" t="n">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>[[-14.952068224539028,27.02830181960754,-1860.0,1.0,6.0,0.0,-1.0],[27.02830181960754,35.29716258587884,0.0,0.0,6.0,1.0,-1.0],[35.29716258587884,48.018486841680826,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-14.952068224539028,27.02830181960754,-1860.0,1.0,6.0,0.0,-1.0],[27.02830181960754,35.29716258587884,0.0,0.0,6.0,1.0,-1.0],[35.29716258587884,48.018486841680826,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C553" t="n">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>[[-14.795484139741667,26.930122698168134,-1860.0,1.0,5.0,0.0,-1.0],[26.930122698168134,36.7479125423822,0.0,0.0,5.0,1.0,-1.0],[36.7479125423822,45.9520905213329,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-14.795484139741667,26.930122698168134,-1860.0,1.0,5.0,0.0,-1.0],[26.930122698168134,36.7479125423822,0.0,0.0,5.0,1.0,-1.0],[36.7479125423822,45.9520905213329,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C554" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>[[-14.081071884181647,26.556187147484586,-1860.0,1.0,4.0,0.0,-1.0],[26.556187147484586,36.86713346895214,0.0,0.0,4.0,1.0,-1.0],[36.86713346895214,45.96502728201175,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-14.081071884181647,26.556187147484586,-1860.0,1.0,4.0,0.0,-1.0],[26.556187147484586,36.86713346895214,0.0,0.0,4.0,1.0,-1.0],[36.86713346895214,45.96502728201175,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C555" t="n">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>[[-14.299893828677986,26.90369554479748,-1860.0,1.0,3.0,0.0,-1.0],[26.90369554479748,35.57813541289757,0.0,0.0,3.0,1.0,-1.0],[35.57813541289757,39.373202855191366,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-14.299893828677986,26.90369554479748,-1860.0,1.0,3.0,0.0,-1.0],[26.90369554479748,35.57813541289757,0.0,0.0,3.0,1.0,-1.0],[35.57813541289757,39.373202855191366,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C556" t="n">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>[[-14.694086409330586,26.662162776441107,-1860.0,1.0,2.0,0.0,-1.0],[26.662162776441107,37.40404568183636,0.0,0.0,2.0,1.0,-1.0],[37.40404568183636,38.478233972375875,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[-14.694086409330586,26.662162776441107,-1860.0,1.0,2.0,0.0,-1.0],[26.662162776441107,37.40404568183636,0.0,0.0,2.0,1.0,-1.0],[37.40404568183636,38.478233972375875,1860.0,0.0,1.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C557" t="n">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>[[-14.880460656356275,26.7239166758429,-1860.0,1.0,1.0,0.0,-1.0],[26.7239166758429,37.53024845044009,0.0,0.0,1.0,1.0,-1.0],[37.53024845044009,38.61088162789981,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-14.880460656356275,26.7239166758429,-1860.0,1.0,1.0,0.0,-1.0],[26.7239166758429,33.748032329331075,0.0,0.0,1.0,1.0,-1.0],[33.748032329331075,37.53024845044009,0.0,0.0,0.0,1.0,-1.0],[37.53024845044009,38.61088162789981,1860.0,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C558" t="n">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>[[-14.530285299219964,-0.49534455146290846,-1860.0,8.0,0.0,0.0,1.0],[-0.49534455146290846,24.455661222327414,-733.6842,8.0,0.0,0.0,1.0],[24.455661222327414,27.054724323763907,0.0,9.0,9.0,2.0,-1.0],[27.054724323763907,28.0943495643385,46.5,9.0,9.0,2.0,-1.0],[28.0943495643385,36.93116410922258,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-14.530285299219964,-0.49534455146290846,-1860.0,8.0,0.0,0.0,1.0],[-0.49534455146290846,24.455661222327414,-733.6842,8.0,0.0,0.0,1.0],[24.455661222327414,27.054724323763907,0.0,9.0,9.0,2.0,-1.0],[27.054724323763907,28.0943495643385,46.5,9.0,9.0,2.0,-1.0],[28.0943495643385,36.93116410922258,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C563" t="n">
@@ -7852,11 +7852,11 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>[[-17.621245709939604,24.49811383490921,-733.6842,0.0,0.0,0.0,1.0],[24.49811383490921,27.306071137899128,0.0,0.0,9.0,3.0,-1.0],[27.306071137899128,27.86766259849711,1725.15,2.0,9.0,1.0,-1.0],[27.86766259849711,37.97630888926083,1860.0,2.0,9.0,1.0,-1.0]]</t>
+          <t>[[-17.621245709939604,24.49811383490921,-733.6843,0.0,0.0,0.0,1.0],[24.49811383490921,27.306071137899128,0.0,0.0,9.0,3.0,-1.0],[27.306071137899128,27.86766259849711,1725.15,2.0,9.0,1.0,-1.0],[27.86766259849711,37.97630888926083,1860.0,2.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C571" t="n">
-        <v>-733.6842</v>
+        <v>-733.6843</v>
       </c>
     </row>
     <row r="572">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>[[-19.143167850157166,22.295058623737592,-1860.0,1.0,8.0,1.0,-1.0],[22.295058623737592,23.95258768269338,-1074.7922,0.0,8.0,2.0,-1.0],[23.95258768269338,26.16262642796777,0.0,0.0,7.0,3.0,-1.0],[26.16262642796777,26.715136114286363,890.0,0.0,7.0,3.0,-1.0],[26.715136114286363,35.555291095383915,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-19.143167850157166,22.295058623737592,-1860.0,1.0,8.0,1.0,-1.0],[22.295058623737592,23.95258768269338,-1074.7922,0.0,8.0,2.0,-1.0],[23.95258768269338,26.16262642796777,0.0,0.0,7.0,3.0,-1.0],[26.16262642796777,26.715136114286363,890.0001,0.0,7.0,3.0,-1.0],[26.715136114286363,35.555291095383915,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C573" t="n">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>[[-17.62081740897492,22.808883169583492,-1860.0,1.0,6.0,1.0,-1.0],[22.808883169583492,23.355230474699145,-1074.7922,0.0,6.0,2.0,-1.0],[23.355230474699145,26.086967000277422,0.0,0.0,5.0,3.0,-1.0],[26.086967000277422,26.633314305393075,890.0,0.0,5.0,3.0,-1.0],[26.633314305393075,36.46756579747485,1860.0,0.0,6.0,2.0,-1.0]]</t>
+          <t>[[-17.62081740897492,22.808883169583492,-1860.0,1.0,6.0,1.0,-1.0],[22.808883169583492,23.355230474699145,-1074.7922,0.0,6.0,2.0,-1.0],[23.355230474699145,26.086967000277422,0.0,0.0,5.0,3.0,-1.0],[26.086967000277422,26.633314305393075,890.0001,0.0,5.0,3.0,-1.0],[26.633314305393075,36.46756579747485,1860.0,0.0,6.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C575" t="n">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>[[-17.212868878855527,22.451366393779875,-1860.0,1.0,4.0,1.0,-1.0],[22.451366393779875,24.08140345977859,-1074.7922,0.0,4.0,2.0,-1.0],[24.08140345977859,26.79813190310978,0.0,0.0,3.0,3.0,-1.0],[26.79813190310978,36.57835429910207,1860.0,0.0,3.0,3.0,-1.0]]</t>
+          <t>[[-17.212868878855527,22.451366393779875,-1860.0,0.0,4.0,1.0,-1.0],[22.451366393779875,24.08140345977859,-1074.7922,0.0,4.0,2.0,-1.0],[24.08140345977859,26.79813190310978,0.0,0.0,3.0,3.0,-1.0],[26.79813190310978,36.57835429910207,1860.0,0.0,3.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C577" t="n">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>[[-17.920124183740267,23.327523859970636,-1860.0,1.0,3.0,1.0,-1.0],[23.327523859970636,23.824483474955105,-1074.7922,0.0,3.0,2.0,-1.0],[23.824483474955105,26.30928154987745,0.0,0.0,2.0,3.0,-1.0],[26.30928154987745,28.297120009815327,890.0,0.0,2.0,3.0,-1.0],[28.297120009815327,31.27887769972213,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[-17.920124183740267,23.327523859970636,-1860.0,1.0,3.0,1.0,-1.0],[23.327523859970636,23.824483474955105,-1074.7922,0.0,3.0,2.0,-1.0],[23.824483474955105,26.30928154987745,0.0,0.0,2.0,3.0,-1.0],[26.30928154987745,28.297120009815327,890.0001,0.0,2.0,3.0,-1.0],[28.297120009815327,31.27887769972213,1860.0,0.0,3.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C578" t="n">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>[[-18.453038871129028,22.97451571834117,-1860.0,1.0,3.0,0.0,-1.0],[22.97451571834117,23.473642882069722,-1074.7922,0.0,3.0,1.0,-1.0],[23.473642882069722,25.96927870071251,0.0,0.0,2.0,2.0,-1.0],[25.96927870071251,28.464914519355293,890.0,0.0,2.0,2.0,-1.0],[28.464914519355293,30.960550337998075,1860.0,0.0,3.0,1.0,-1.0]]</t>
+          <t>[[-18.453038871129028,22.97451571834117,-1860.0,1.0,3.0,0.0,-1.0],[22.97451571834117,23.473642882069722,-1074.7922,0.0,3.0,1.0,-1.0],[23.473642882069722,25.96927870071251,0.0,0.0,2.0,2.0,-1.0],[25.96927870071251,28.464914519355293,890.0001,0.0,2.0,2.0,-1.0],[28.464914519355293,30.960550337998075,1860.0,0.0,3.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C579" t="n">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>[[-18.33661349057718,20.188767897113728,-1860.0,1.0,3.0,0.0,-1.0],[20.188767897113728,23.69107529599472,-1074.7922,0.0,3.0,0.0,-1.0],[23.69107529599472,26.192723438052575,0.0,0.0,2.0,1.0,-1.0],[26.192723438052575,29.194701208521998,890.0,0.0,2.0,1.0,-1.0],[29.194701208521998,31.196019722168277,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-18.33661349057718,20.188767897113728,-1860.0,1.0,3.0,0.0,-1.0],[20.188767897113728,23.69107529599472,-1074.7922,0.0,3.0,0.0,-1.0],[23.69107529599472,26.192723438052575,0.0,0.0,2.0,1.0,-1.0],[26.192723438052575,29.194701208521998,890.0001,0.0,2.0,1.0,-1.0],[29.194701208521998,31.196019722168277,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C580" t="n">
@@ -7982,11 +7982,11 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>[[-17.325188007870292,-4.345116533696082,-1860.0,10.0,3.0,0.0,1.0],[-4.345116533696082,21.13428302671996,-1074.7922,0.0,3.0,0.0,-1.0],[21.13428302671996,23.53799996638185,0.0,0.0,2.0,1.0,-1.0],[23.53799996638185,29.787664009502766,890.0,0.0,2.0,0.0,-1.0],[29.787664009502766,30.268407397435148,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-17.325188007870292,-3.864373145763704,-1860.0,1.0,3.0,0.0,-1.0],[-3.864373145763704,21.13428302671996,-1074.7922,0.0,3.0,0.0,-1.0],[21.13428302671996,23.53799996638185,0.0,0.0,2.0,1.0,-1.0],[23.53799996638185,29.787664009502766,890.0001,0.0,2.0,0.0,-1.0],[29.787664009502766,30.268407397435148,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C581" t="n">
-        <v>890</v>
+        <v>890.0001</v>
       </c>
     </row>
     <row r="582">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>[[-17.656335934047352,-4.702199129227216,-1860.0,10.0,2.0,0.0,1.0],[-4.702199129227216,-4.203963098272595,-934.626,9.0,2.0,0.0,1.0],[-4.203963098272595,24.19549066614078,0.0,0.0,2.0,1.0,-1.0],[24.19549066614078,31.669031130460088,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-17.656335934047352,-4.203963098272595,-1860.0,1.0,2.0,0.0,-1.0],[-4.203963098272595,24.19549066614078,0.0,0.0,2.0,1.0,-1.0],[24.19549066614078,31.669031130460088,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C582" t="n">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>[[-18.4914812858837,-4.953106608294783,-1860.0,10.0,1.0,0.0,1.0],[-4.953106608294783,-4.4695932269523215,-934.626,9.0,1.0,0.0,1.0],[-4.4695932269523215,24.057696272252898,0.0,0.0,1.0,1.0,-1.0],[24.057696272252898,29.37634346701997,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-18.4914812858837,-4.4695932269523215,-1860.0,10.0,1.0,0.0,1.0],[-4.4695932269523215,21.640129365540595,0.0,0.0,1.0,1.0,-1.0],[21.640129365540595,24.057696272252898,0.0,0.0,0.0,1.0,-1.0],[24.057696272252898,26.95877656030767,1860.0,0.0,0.0,0.0,-1.0],[26.95877656030767,29.37634346701997,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C583" t="n">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>[[-17.992717946082532,-10.47895952316101,-1860.0,9.0,1.0,0.0,1.0],[-10.47895952316101,-4.733144258573962,-733.6842,9.0,1.0,0.0,1.0],[-4.733144258573962,-4.291158468990343,181.35,9.0,0.0,0.0,1.0],[-4.291158468990343,-3.849172679406724,1016.5,9.0,0.0,0.0,1.0],[-3.849172679406724,25.763875222695745,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-17.992717946082532,-10.47895952316101,-1860.0,9.0,1.0,0.0,1.0],[-10.47895952316101,-4.291158468990343,-733.6842,9.0,1.0,0.0,1.0],[-4.291158468990343,-0.31328636273777377,1860.0,0.0,0.0,0.0,-1.0],[-0.31328636273777377,25.763875222695745,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C584" t="n">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>[[-17.541201200501405,-3.9120485460436196,-1860.0,8.0,0.0,0.0,1.0],[-3.9120485460436196,15.872205307201554,-733.6842,8.0,0.0,0.0,1.0],[15.872205307201554,17.630805649712237,0.0,8.0,8.0,3.0,-1.0],[17.630805649712237,18.949755906595243,227.85,8.0,8.0,1.0,-1.0],[18.949755906595243,25.984157276637976,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-17.541201200501405,-3.9120485460436196,-1860.0,8.0,0.0,0.0,1.0],[-3.9120485460436196,15.872205307201554,-733.6842,8.0,0.0,0.0,1.0],[15.872205307201554,17.630805649712237,0.0,8.0,8.0,3.0,-1.0],[17.630805649712237,18.949755906595243,227.85,8.0,8.0,1.0,-1.0],[18.949755906595243,25.984157276637976,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C587" t="n">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>[[-14.60846950085199,15.801729690813085,-1860.0,2.0,9.0,0.0,-1.0],[15.801729690813085,16.21267832853829,-1808.4764,1.0,9.0,1.0,-1.0],[16.21267832853829,17.445524241713905,-1607.5346,0.0,8.0,1.0,-1.0],[17.445524241713905,19.500267430339925,0.0,0.0,8.0,1.0,-1.0],[19.500267430339925,19.911216068065123,227.85,1.0,8.0,0.0,-1.0],[19.911216068065123,26.075445633943183,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[-14.60846950085199,15.801729690813085,-1860.0,2.0,9.0,0.0,-1.0],[15.801729690813085,16.21267832853829,-1808.4765,1.0,9.0,1.0,-1.0],[16.21267832853829,17.445524241713905,-1607.5347,0.0,8.0,1.0,-1.0],[17.445524241713905,19.500267430339925,0.0,0.0,8.0,1.0,-1.0],[19.500267430339925,19.911216068065123,227.85,1.0,8.0,0.0,-1.0],[19.911216068065123,26.075445633943183,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C595" t="n">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>[[-13.089258523851058,14.852002584084783,-733.6842,0.0,0.0,0.0,1.0],[14.852002584084783,16.44864607596683,0.0,0.0,9.0,1.0,-1.0],[16.44864607596683,18.44445044081939,46.5,1.0,9.0,0.0,-1.0],[18.44445044081939,20.440254805671948,227.85,0.0,8.0,0.0,-1.0],[20.440254805671948,26.42766790022963,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-13.089258523851058,14.852002584084783,-733.6844,0.0,0.0,0.0,1.0],[14.852002584084783,16.44864607596683,0.0,0.0,9.0,1.0,-1.0],[16.44864607596683,18.44445044081939,46.5,1.0,9.0,0.0,-1.0],[18.44445044081939,20.440254805671948,227.85,0.0,8.0,0.0,-1.0],[20.440254805671948,26.42766790022963,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C596" t="n">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>[[-13.582656085878643,13.324792810262409,-785.2077,0.0,0.0,0.0,1.0],[13.324792810262409,14.931207669733517,0.0,0.0,8.0,1.0,-1.0],[14.931207669733517,16.537622529204626,181.35,0.0,8.0,1.0,-1.0],[16.537622529204626,26.17611168603127,1860.0,0.0,9.0,0.0,-1.0]]</t>
+          <t>[[-13.582656085878643,13.324792810262409,-785.2079,0.0,0.0,0.0,1.0],[13.324792810262409,14.931207669733517,0.0,0.0,8.0,1.0,-1.0],[14.931207669733517,16.537622529204626,181.35,0.0,8.0,1.0,-1.0],[16.537622529204626,26.17611168603127,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C597" t="n">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>[[-14.065811190081442,12.98551863422074,-1860.0,1.0,8.0,0.0,-1.0],[12.98551863422074,14.703063384970084,0.0,0.0,7.0,1.0,-1.0],[14.703063384970084,16.420608135719426,181.35,0.0,7.0,1.0,-1.0],[16.420608135719426,28.443421390964843,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-14.065811190081442,12.98551863422074,-1860.0,1.0,7.0,0.0,-1.0],[12.98551863422074,14.703063384970084,0.0,0.0,7.0,1.0,-1.0],[14.703063384970084,16.420608135719426,181.35,0.0,7.0,1.0,-1.0],[16.420608135719426,28.443421390964843,1860.0,1.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C598" t="n">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>[[-13.638813213151954,13.116121458189317,-1860.0,1.0,7.0,0.0,-1.0],[13.116121458189317,14.549421529868313,0.0,0.0,6.0,1.0,-1.0],[14.549421529868313,15.98272160154731,181.35,0.0,6.0,1.0,-1.0],[15.98272160154731,33.66008915225493,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-13.638813213151954,13.116121458189317,-1860.0,1.0,7.0,0.0,-1.0],[13.116121458189317,14.549421529868313,0.0,0.0,6.0,1.0,-1.0],[14.549421529868313,15.98272160154731,181.35,0.0,6.0,1.0,-1.0],[15.98272160154731,33.66008915225493,1860.0,1.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C599" t="n">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>[[-13.943712320387379,13.713081043081251,-1860.0,1.0,6.0,0.0,-1.0],[13.713081043081251,15.19469497326707,0.0,0.0,5.0,1.0,-1.0],[15.19469497326707,16.67630890345289,181.35,0.0,5.0,1.0,-1.0],[16.67630890345289,34.949547375744665,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-13.943712320387379,13.713081043081251,-1860.0,1.0,6.0,0.0,-1.0],[13.713081043081251,15.19469497326707,0.0,0.0,5.0,1.0,-1.0],[15.19469497326707,16.67630890345289,181.35,0.0,5.0,1.0,-1.0],[16.67630890345289,34.949547375744665,1860.0,1.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C600" t="n">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>[[-13.458419018136013,13.489774983372822,-1860.0,1.0,5.0,0.0,-1.0],[13.489774983372822,14.933428233453654,0.0,0.0,4.0,1.0,-1.0],[14.933428233453654,16.377081483534486,181.35,0.0,4.0,1.0,-1.0],[16.377081483534486,34.18213823453139,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-13.458419018136013,13.489774983372822,-1860.0,1.0,5.0,0.0,-1.0],[13.489774983372822,14.933428233453654,0.0,0.0,4.0,1.0,-1.0],[14.933428233453654,16.377081483534486,181.35,0.0,4.0,1.0,-1.0],[16.377081483534486,34.18213823453139,1860.0,1.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C601" t="n">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>[[-13.1795604552901,13.627744745986098,-1860.0,1.0,4.0,0.0,-1.0],[13.627744745986098,15.014329497776243,0.0,0.0,3.0,1.0,-1.0],[15.014329497776243,16.863109166829773,181.35,0.0,3.0,1.0,-1.0],[16.863109166829773,32.577736353784786,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-13.1795604552901,13.627744745986098,-1860.0,1.0,4.0,0.0,-1.0],[13.627744745986098,15.014329497776243,0.0,0.0,3.0,1.0,-1.0],[15.014329497776243,16.863109166829773,181.35,0.0,3.0,1.0,-1.0],[16.863109166829773,32.577736353784786,1860.0,1.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C602" t="n">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>[[-13.491455190456973,13.044121775419748,-1860.0,1.0,3.0,0.0,-1.0],[13.044121775419748,14.93952013012523,0.0,0.0,2.0,1.0,-1.0],[14.93952013012523,16.361068896154343,181.35,0.0,2.0,1.0,-1.0],[16.361068896154343,33.41965408850366,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-13.491455190456973,13.044121775419748,-1860.0,1.0,2.0,0.0,-1.0],[13.044121775419748,14.93952013012523,0.0,0.0,2.0,1.0,-1.0],[14.93952013012523,16.361068896154343,181.35,0.0,2.0,1.0,-1.0],[16.361068896154343,33.41965408850366,1860.0,1.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C603" t="n">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>[[-13.798500505043743,13.636940747544651,-1860.0,1.0,2.0,0.0,-1.0],[13.636940747544651,15.080911339786143,0.0,0.0,1.0,1.0,-1.0],[15.080911339786143,17.0062054627748,181.35,0.0,1.0,1.0,-1.0],[17.0062054627748,33.852529038925574,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-13.798500505043743,13.155617216797486,-1860.0,1.0,2.0,0.0,-1.0],[13.155617216797486,13.636940747544651,-1860.0,1.0,1.0,0.0,-1.0],[13.636940747544651,15.080911339786143,0.0,0.0,1.0,1.0,-1.0],[15.080911339786143,17.0062054627748,181.35,0.0,1.0,1.0,-1.0],[17.0062054627748,33.852529038925574,1860.0,1.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C604" t="n">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>[[-13.09164031997929,11.850995537604339,-1860.0,1.0,1.0,0.0,-1.0],[11.850995537604339,16.167990205263045,-1860.0,0.0,1.0,0.0,-1.0],[16.167990205263045,18.086654502000243,0.0,0.0,0.0,1.0,-1.0],[18.086654502000243,34.39530102426646,181.35,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-13.09164031997929,16.167990205263045,-1860.0,1.0,0.0,0.0,-1.0],[16.167990205263045,18.086654502000243,0.0,0.0,0.0,1.0,-1.0],[18.086654502000243,34.39530102426646,181.35,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C605" t="n">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>[[-13.674291219793194,12.104456180844352,-1860.0,1.0,1.0,0.0,-1.0],[12.104456180844352,14.491377236458941,0.0,0.0,1.0,1.0,-1.0],[14.491377236458941,33.58674568137564,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-13.674291219793194,12.104456180844352,-1860.0,1.0,1.0,0.0,-1.0],[12.104456180844352,13.059224603090186,0.0,0.0,1.0,1.0,-1.0],[13.059224603090186,14.491377236458941,0.0,0.0,0.0,1.0,-1.0],[14.491377236458941,33.58674568137564,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C606" t="n">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>[[-13.252081670763886,-3.6843685574201412,-1860.0,10.0,0.0,0.0,1.0],[-3.6843685574201412,34.108098240287646,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-13.252081670763886,-3.2059829017529538,-1860.0,10.0,0.0,0.0,1.0],[-3.2059829017529538,34.108098240287646,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C608" t="n">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>[[-13.04004209056855,7.333007074773429,-1860.0,8.0,0.0,0.0,1.0],[7.333007074773429,24.227730772861896,0.0,9.0,0.0,1.0,1.0],[24.227730772861896,36.15341808915964,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-13.04004209056855,7.333007074773429,-1860.0,9.0,0.0,0.0,1.0],[7.333007074773429,24.227730772861896,0.0,9.0,0.0,1.0,1.0],[24.227730772861896,36.15341808915964,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C610" t="n">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>[[-13.79743690539747,6.295463740289181,-1860.0,7.0,0.0,0.0,1.0],[6.295463740289181,25.43155959332409,0.0,8.0,0.0,1.0,1.0],[25.43155959332409,30.693985952908683,1678.65,9.0,0.0,0.0,1.0],[30.693985952908683,33.56440033086392,1860.0,9.0,9.0,1.0,-1.0]]</t>
+          <t>[[-13.79743690539747,6.295463740289181,-1860.0,8.0,0.0,0.0,1.0],[6.295463740289181,25.43155959332409,0.0,8.0,0.0,1.0,1.0],[25.43155959332409,30.693985952908683,1678.65,9.0,0.0,0.0,1.0],[30.693985952908683,33.56440033086392,1860.0,9.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C611" t="n">
@@ -8385,7 +8385,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>[[-13.477651010691503,6.5141244327980665,-1860.0,6.0,0.0,0.0,1.0],[6.5141244327980665,25.5539105694548,0.0,7.0,0.0,1.0,1.0],[25.5539105694548,29.36186779678615,1678.65,8.0,0.0,0.0,1.0],[29.36186779678615,33.645819677533915,1860.0,8.0,9.0,1.0,-1.0]]</t>
+          <t>[[-13.477651010691503,6.5141244327980665,-1860.0,7.0,0.0,0.0,1.0],[6.5141244327980665,25.5539105694548,0.0,7.0,0.0,1.0,1.0],[25.5539105694548,29.36186779678615,1678.65,8.0,0.0,0.0,1.0],[29.36186779678615,33.645819677533915,1860.0,8.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C612" t="n">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>[[-13.63629985442631,6.973972321648217,-1860.0,5.0,0.0,0.0,1.0],[6.973972321648217,23.270466600404824,0.0,6.0,0.0,1.0,1.0],[23.270466600404824,29.98078777401048,1678.65,7.0,0.0,0.0,1.0],[29.98078777401048,33.81525701607086,1860.0,7.0,9.0,1.0,-1.0]]</t>
+          <t>[[-13.63629985442631,6.973972321648217,-1860.0,6.0,0.0,0.0,1.0],[6.973972321648217,23.270466600404824,0.0,6.0,0.0,1.0,1.0],[23.270466600404824,29.98078777401048,1678.65,7.0,0.0,0.0,1.0],[29.98078777401048,33.81525701607086,1860.0,7.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C613" t="n">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>[[-12.677717925832917,6.72792425719083,-1860.0,4.0,0.0,0.0,1.0],[6.72792425719083,24.28541004183137,0.0,5.0,0.0,1.0,1.0],[24.28541004183137,29.829879236981007,1678.65,6.0,0.0,0.0,1.0],[29.829879236981007,33.064152934151636,1860.0,6.0,9.0,1.0,-1.0]]</t>
+          <t>[[-12.677717925832917,6.72792425719083,-1860.0,5.0,0.0,0.0,1.0],[6.72792425719083,24.28541004183137,0.0,5.0,0.0,1.0,1.0],[24.28541004183137,29.829879236981007,1678.65,6.0,0.0,0.0,1.0],[29.829879236981007,33.064152934151636,1860.0,6.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C614" t="n">
@@ -8450,7 +8450,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>[[-4.872993494586886,6.501520124567865,-1860.0,2.0,0.0,0.0,1.0],[6.501520124567865,23.75940285707852,0.0,2.0,0.0,1.0,1.0],[23.75940285707852,30.819445793105608,1678.65,3.0,0.0,0.0,1.0],[30.819445793105608,33.95724265356209,1860.0,3.0,9.0,1.0,-1.0]]</t>
+          <t>[[-4.872993494586886,6.501520124567865,-1860.0,2.0,0.0,0.0,1.0],[6.501520124567865,23.75940285707852,0.0,2.0,0.0,1.0,1.0],[23.75940285707852,30.819445793105608,1678.65,3.0,0.0,0.0,1.0],[30.819445793105608,33.95724265356209,1860.0,2.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C617" t="n">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>[[-4.881552307742827,6.067825225044898,-1860.0,1.0,0.0,0.0,1.0],[6.067825225044898,6.849923620244021,-1860.0,0.0,0.0,0.0,1.0],[6.849923620244021,7.632022015443144,0.0,0.0,0.0,1.0,1.0],[7.632022015443144,24.05608831462473,0.0,1.0,0.0,1.0,1.0],[24.05608831462473,29.921826278618152,1678.65,2.0,0.0,0.0,1.0],[29.921826278618152,33.83231825461377,1860.0,2.0,9.0,1.0,-1.0]]</t>
+          <t>[[-4.881552307742827,6.849923620244021,-1860.0,1.0,0.0,0.0,1.0],[6.849923620244021,19.36349794342999,0.0,1.0,0.0,1.0,1.0],[19.36349794342999,24.05608831462473,0.0,0.0,0.0,1.0,1.0],[24.05608831462473,29.921826278618152,1678.65,1.0,0.0,0.0,1.0],[29.921826278618152,33.83231825461377,1860.0,0.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C618" t="n">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>[[4.830693769807795,23.767145310053905,0.0,0.0,0.0,1.0,1.0],[23.767145310053905,29.778717227592352,1678.65,1.0,0.0,0.0,1.0],[29.778717227592352,34.58797476162311,1860.0,1.0,9.0,1.0,-1.0]]</t>
+          <t>[[4.830693769807795,23.767145310053905,0.0,0.0,0.0,1.0,1.0],[23.767145310053905,29.778717227592352,1678.65,0.0,0.0,0.0,1.0],[29.778717227592352,34.58797476162311,1860.0,0.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C619" t="n">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>[[4.967796904095384,24.25360834401886,-1860.0,1.0,8.0,1.0,-1.0],[24.25360834401886,27.760119514914038,-1074.7922,0.0,8.0,0.0,-1.0],[27.760119514914038,30.828316789447317,0.0,0.0,7.0,1.0,-1.0],[30.828316789447317,31.266630685809215,890.0,0.0,7.0,1.0,-1.0],[31.266630685809215,48.36087264392321,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[4.967796904095384,24.25360834401886,-1860.0,1.0,8.0,1.0,-1.0],[24.25360834401886,27.760119514914038,-1074.7923,0.0,8.0,0.0,-1.0],[27.760119514914038,30.828316789447317,0.0,0.0,7.0,1.0,-1.0],[30.828316789447317,31.266630685809215,890.0,0.0,7.0,1.0,-1.0],[31.266630685809215,48.36087264392321,1860.0,0.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C622" t="n">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>[[4.591093059070173,24.979428511129314,-1860.0,1.0,8.0,0.0,-1.0],[24.979428511129314,26.921174744658757,-1074.7922,0.0,8.0,0.0,-1.0],[26.921174744658757,29.83379409495292,0.0,0.0,7.0,1.0,-1.0],[29.83379409495292,52.64931233892387,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[4.591093059070173,24.979428511129314,-1860.0,1.0,8.0,0.0,-1.0],[24.979428511129314,26.921174744658757,-1074.7923,0.0,8.0,0.0,-1.0],[26.921174744658757,29.83379409495292,0.0,0.0,7.0,1.0,-1.0],[29.83379409495292,52.64931233892387,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C623" t="n">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>[[4.863091593793426,24.239072919225187,-1860.0,1.0,7.0,0.0,-1.0],[24.239072919225187,24.74896716463129,-1074.7922,0.0,7.0,1.0,-1.0],[24.74896716463129,27.808332637067878,0.0,0.0,6.0,2.0,-1.0],[27.808332637067878,30.357803864098372,890.0,0.0,6.0,0.0,-1.0],[30.357803864098372,55.34262188899722,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[4.863091593793426,24.239072919225187,-1860.0,1.0,7.0,0.0,-1.0],[24.239072919225187,24.74896716463129,-1074.7923,0.0,7.0,1.0,-1.0],[24.74896716463129,27.808332637067878,0.0,0.0,6.0,2.0,-1.0],[27.808332637067878,30.357803864098372,890.0,0.0,6.0,0.0,-1.0],[30.357803864098372,55.34262188899722,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C624" t="n">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>[[5.0936561679229095,24.37261782561748,-1860.0,1.0,6.0,0.0,-1.0],[24.37261782561748,24.893670843393007,-1074.7922,0.0,6.0,1.0,-1.0],[24.893670843393007,27.49893593227065,0.0,0.0,5.0,2.0,-1.0],[27.49893593227065,31.146307056699357,890.0,0.0,5.0,0.0,-1.0],[31.146307056699357,56.67790492770027,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[5.0936561679229095,24.37261782561748,-1860.0,1.0,6.0,0.0,-1.0],[24.37261782561748,24.893670843393007,-1074.7923,0.0,6.0,1.0,-1.0],[24.893670843393007,27.49893593227065,0.0,0.0,5.0,2.0,-1.0],[27.49893593227065,31.146307056699357,890.0,0.0,5.0,0.0,-1.0],[31.146307056699357,56.67790492770027,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C625" t="n">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>[[5.037254937043609,24.0029293191894,-1860.0,1.0,5.0,0.0,-1.0],[24.0029293191894,24.52975360758234,-1074.7922,0.0,5.0,0.0,-1.0],[24.52975360758234,27.16387504954703,0.0,0.0,4.0,1.0,-1.0],[27.16387504954703,30.324820779904663,890.0,0.0,4.0,0.0,-1.0],[30.324820779904663,57.192859487944524,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[5.037254937043609,24.0029293191894,-1860.0,1.0,5.0,0.0,-1.0],[24.0029293191894,24.52975360758234,-1074.7923,0.0,5.0,0.0,-1.0],[24.52975360758234,27.16387504954703,0.0,0.0,4.0,1.0,-1.0],[27.16387504954703,30.324820779904663,890.0,0.0,4.0,0.0,-1.0],[30.324820779904663,57.192859487944524,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C626" t="n">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>[[5.0102696048923185,24.62393903975309,-1860.0,1.0,3.0,0.0,-1.0],[24.62393903975309,27.720834213678472,0.0,0.0,3.0,1.0,-1.0],[27.720834213678472,56.10903997466116,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[5.0102696048923185,24.62393903975309,-1860.0,0.0,3.0,0.0,-1.0],[24.62393903975309,27.720834213678472,0.0,0.0,2.0,1.0,-1.0],[27.720834213678472,56.10903997466116,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C628" t="n">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>[[4.857921714079791,24.36676019334334,-1860.0,1.0,2.0,0.0,-1.0],[24.36676019334334,27.960493597418203,0.0,0.0,2.0,2.0,-1.0],[27.960493597418203,55.6835798574243,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[4.857921714079791,24.36676019334334,-1860.0,1.0,2.0,0.0,-1.0],[24.36676019334334,27.960493597418203,0.0,0.0,1.0,2.0,-1.0],[27.960493597418203,55.6835798574243,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C629" t="n">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>[[5.008691202990625,25.15708760715045,-1860.0,1.0,1.0,0.0,-1.0],[25.15708760715045,28.179347067774426,0.0,0.0,1.0,1.0,-1.0],[28.179347067774426,54.8759723032862,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[5.008691202990625,25.15708760715045,-1860.0,1.0,1.0,0.0,-1.0],[25.15708760715045,25.660797517254448,0.0,0.0,1.0,1.0,-1.0],[25.660797517254448,28.179347067774426,0.0,0.0,0.0,1.0,-1.0],[28.179347067774426,30.697896618294404,1860.0,0.0,0.0,0.0,-1.0],[30.697896618294404,54.8759723032862,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C630" t="n">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>[[5.100775592433641,16.0172212623511,-1860.0,8.0,0.0,0.0,1.0],[16.0172212623511,21.97164617321517,-733.6842,8.0,0.0,0.0,1.0],[21.97164617321517,24.452656552741864,0.0,8.0,0.0,1.0,1.0],[24.452656552741864,33.384293919037965,1016.5,9.0,0.0,0.0,1.0],[33.384293919037965,54.224781107062206,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[5.100775592433641,16.0172212623511,-1860.0,7.0,0.0,0.0,1.0],[16.0172212623511,21.97164617321517,-733.6843,8.0,0.0,0.0,1.0],[21.97164617321517,24.452656552741864,0.0,7.0,0.0,1.0,1.0],[24.452656552741864,33.384293919037965,1016.5,9.0,0.0,0.0,1.0],[33.384293919037965,54.224781107062206,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C634" t="n">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>[[4.992893814078394,16.03823118937139,-1860.0,7.0,0.0,0.0,1.0],[16.03823118937139,22.349852546681674,-733.6842,7.0,0.0,0.0,1.0],[22.349852546681674,24.979694778894295,0.0,7.0,0.0,1.0,1.0],[24.979694778894295,34.44712681485972,1016.5,8.0,0.0,0.0,1.0],[34.44712681485972,57.06377001188824,1860.0,8.0,1.0,0.0,1.0]]</t>
+          <t>[[4.992893814078394,16.03823118937139,-1860.0,6.0,0.0,0.0,1.0],[16.03823118937139,22.349852546681674,-733.6843,6.0,0.0,0.0,1.0],[22.349852546681674,24.979694778894295,0.0,6.0,0.0,1.0,1.0],[24.979694778894295,34.44712681485972,1016.5,7.0,0.0,0.0,1.0],[34.44712681485972,57.06377001188824,1860.0,8.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C635" t="n">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>[[5.024863077657301,15.319835764701056,-1860.0,6.0,0.0,0.0,1.0],[15.319835764701056,20.98207074257512,-733.6842,6.0,0.0,0.0,1.0],[20.98207074257512,23.55581391433606,0.0,6.0,0.0,1.0,1.0],[23.55581391433606,33.850786601379816,1016.5,7.0,0.0,0.0,1.0],[33.850786601379816,55.984977878523885,1860.0,7.0,1.0,0.0,1.0]]</t>
+          <t>[[5.024863077657301,15.319835764701056,-1860.0,5.0,0.0,0.0,1.0],[15.319835764701056,20.98207074257512,-733.6843,5.0,0.0,0.0,1.0],[20.98207074257512,23.55581391433606,0.0,5.0,0.0,1.0,1.0],[23.55581391433606,33.850786601379816,1016.5,6.0,0.0,0.0,1.0],[33.850786601379816,55.984977878523885,1860.0,6.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C636" t="n">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>[[5.075011052085991,15.038088377698118,-1860.0,5.0,0.0,0.0,1.0],[15.038088377698118,21.8549307583801,-733.6842,5.0,0.0,0.0,1.0],[21.8549307583801,24.476793212488555,0.0,5.0,0.0,1.0,1.0],[24.476793212488555,32.342380574813916,1016.5,6.0,0.0,0.0,1.0],[32.342380574813916,56.98788764343339,1860.0,6.0,1.0,0.0,1.0]]</t>
+          <t>[[5.075011052085991,15.038088377698118,-1860.0,3.0,0.0,0.0,1.0],[15.038088377698118,21.8549307583801,-733.6843,4.0,0.0,0.0,1.0],[21.8549307583801,24.476793212488555,0.0,4.0,0.0,1.0,1.0],[24.476793212488555,32.342380574813916,1016.5,4.0,0.0,0.0,1.0],[32.342380574813916,56.98788764343339,1860.0,6.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C637" t="n">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>[[5.049031821720391,16.308173777922356,-1860.0,4.0,0.0,0.0,1.0],[16.308173777922356,21.425965576195974,-733.6842,4.0,0.0,0.0,1.0],[21.425965576195974,23.47308229550542,0.0,4.0,0.0,1.0,1.0],[23.47308229550542,33.1968867122253,1016.5,5.0,0.0,0.0,1.0],[33.1968867122253,55.71517062462923,1860.0,5.0,1.0,0.0,1.0]]</t>
+          <t>[[5.049031821720391,16.308173777922356,-1860.0,3.0,0.0,0.0,1.0],[16.308173777922356,21.425965576195974,-733.6843,3.0,0.0,0.0,1.0],[21.425965576195974,23.47308229550542,0.0,3.0,0.0,1.0,1.0],[23.47308229550542,33.1968867122253,1016.5,4.0,0.0,0.0,1.0],[33.1968867122253,55.71517062462923,1860.0,4.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C638" t="n">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>[[5.062513955862454,15.982296530286714,-1860.0,3.0,0.0,0.0,1.0],[15.982296530286714,21.442187817498844,-733.6842,3.0,0.0,0.0,1.0],[21.442187817498844,23.92395658441345,0.0,3.0,0.0,1.0,1.0],[23.92395658441345,32.85832414530603,1016.5,4.0,0.0,0.0,1.0],[32.85832414530603,54.20153554077163,1860.0,4.0,1.0,0.0,1.0]]</t>
+          <t>[[5.062513955862454,15.982296530286714,-1860.0,3.0,0.0,0.0,1.0],[15.982296530286714,21.442187817498844,-733.6843,2.0,0.0,0.0,1.0],[21.442187817498844,23.92395658441345,0.0,2.0,0.0,1.0,1.0],[23.92395658441345,32.85832414530603,1016.5,3.0,0.0,0.0,1.0],[32.85832414530603,54.20153554077163,1860.0,3.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C639" t="n">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>[[5.149124104043402,15.561247222066516,-1860.0,2.0,0.0,0.0,1.0],[15.561247222066516,20.76730878107807,-733.6842,2.0,0.0,0.0,1.0],[20.76730878107807,22.849733404682695,0.0,2.0,0.0,1.0,1.0],[22.849733404682695,34.82367499040927,1016.5,3.0,0.0,0.0,1.0],[34.82367499040927,56.68913353825781,1860.0,3.0,1.0,0.0,1.0]]</t>
+          <t>[[5.149124104043402,15.561247222066516,-1860.0,1.0,0.0,0.0,1.0],[15.561247222066516,20.76730878107807,-733.6843,2.0,0.0,0.0,1.0],[20.76730878107807,22.849733404682695,0.0,2.0,0.0,1.0,1.0],[22.849733404682695,34.82367499040927,1016.5,2.0,0.0,0.0,1.0],[34.82367499040927,56.68913353825781,1860.0,3.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C640" t="n">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>[[12.453519927190623,21.744944337543433,-1860.0,2.0,0.0,0.0,1.0],[21.744944337543433,30.1514711850055,-733.6842,2.0,0.0,0.0,1.0],[30.1514711850055,33.248612655123104,0.0,2.0,0.0,1.0,1.0],[33.248612655123104,38.557998032467566,1016.5,3.0,0.0,0.0,1.0],[38.557998032467566,56.25594929028244,1860.0,3.0,9.0,1.0,-1.0]]</t>
+          <t>[[12.453519927190623,21.744944337543433,-1860.0,1.0,0.0,0.0,1.0],[21.744944337543433,30.1514711850055,-733.6843,2.0,0.0,0.0,1.0],[30.1514711850055,33.248612655123104,0.0,2.0,0.0,1.0,1.0],[33.248612655123104,38.557998032467566,1016.5,2.0,0.0,0.0,1.0],[38.557998032467566,56.25594929028244,1860.0,3.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C641" t="n">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>[[14.359218967168415,21.612356946148715,-1860.0,1.0,0.0,0.0,1.0],[21.612356946148715,29.718805275597287,-733.6842,1.0,0.0,0.0,1.0],[29.718805275597287,33.13204667747037,0.0,1.0,0.0,1.0,1.0],[33.13204667747037,38.25190878027999,1016.5,2.0,0.0,0.0,1.0],[38.25190878027999,56.59808131534781,1860.0,2.0,9.0,1.0,-1.0]]</t>
+          <t>[[14.359218967168415,21.612356946148715,-1860.0,1.0,0.0,0.0,1.0],[21.612356946148715,29.718805275597287,-733.6843,1.0,0.0,0.0,1.0],[29.718805275597287,33.13204667747037,0.0,1.0,0.0,1.0,1.0],[33.13204667747037,38.25190878027999,1016.5,2.0,0.0,0.0,1.0],[38.25190878027999,56.59808131534781,1860.0,2.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C642" t="n">
@@ -8788,11 +8788,11 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>[[15.468694675348974,30.718274688690588,-733.6842,0.0,0.0,0.0,1.0],[30.718274688690588,34.33001732342939,0.0,0.0,0.0,1.0,1.0],[34.33001732342939,39.94828364413419,1016.5,1.0,0.0,0.0,1.0],[39.94828364413419,55.19786365747581,1860.0,1.0,9.0,1.0,-1.0]]</t>
+          <t>[[15.468694675348974,27.909141528338186,-733.6844,0.0,0.0,0.0,1.0],[27.909141528338186,30.718274688690588,-733.6843,0.0,0.0,0.0,1.0],[30.718274688690588,34.33001732342939,0.0,0.0,0.0,1.0,1.0],[34.33001732342939,39.94828364413419,1016.5,0.0,0.0,0.0,1.0],[39.94828364413419,55.19786365747581,1860.0,1.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C643" t="n">
-        <v>-733.6842</v>
+        <v>-733.6844</v>
       </c>
     </row>
     <row r="644">
@@ -8801,11 +8801,11 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>[[15.433312970188537,39.84677261349068,-0.0,0.0,0.0,1.0,1.0],[39.84677261349068,40.26056006507207,890.0,0.0,8.0,2.0,-1.0],[40.26056006507207,56.398270676746364,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[15.433312970188537,39.84677261349068,0.0,0.0,0.0,1.0,1.0],[39.84677261349068,40.26056006507207,890.0,0.0,8.0,2.0,-1.0],[40.26056006507207,56.398270676746364,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C644" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="645">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>[[15.37756823849231,39.594717827547726,-0.0,0.0,0.0,1.0,1.0],[39.594717827547726,40.00517799007409,890.0,0.0,8.0,1.0,-1.0],[40.00517799007409,56.01312432860224,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[15.37756823849231,39.594717827547726,0.0,0.0,0.0,1.0,1.0],[39.594717827547726,40.00517799007409,890.0,0.0,8.0,1.0,-1.0],[40.00517799007409,56.01312432860224,1860.0,0.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C645" t="n">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>[[15.010904772646576,34.85850389486829,-1860.0,1.0,8.0,0.0,-1.0],[34.85850389486829,35.70308258092028,-1074.7922,0.0,8.0,0.0,-1.0],[35.70308258092028,39.50368666815423,0.0,0.0,7.0,1.0,-1.0],[39.50368666815423,40.34826535420621,890.0,0.0,7.0,1.0,-1.0],[40.34826535420621,56.81754973221998,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[15.010904772646576,34.85850389486829,-1860.0,1.0,8.0,0.0,-1.0],[34.85850389486829,35.70308258092028,-1074.7921,0.0,8.0,0.0,-1.0],[35.70308258092028,39.50368666815423,0.0,0.0,7.0,1.0,-1.0],[39.50368666815423,40.34826535420621,890.0001,0.0,7.0,1.0,-1.0],[40.34826535420621,56.81754973221998,1860.0,0.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C646" t="n">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>[[15.740607208219268,33.310480943479895,-1860.0,1.0,7.0,0.0,-1.0],[33.310480943479895,34.87224749772528,-1074.7922,0.0,7.0,0.0,-1.0],[34.87224749772528,38.776663883338756,0.0,0.0,6.0,1.0,-1.0],[38.776663883338756,54.39432942579264,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[15.740607208219268,33.310480943479895,-1860.0,1.0,7.0,0.0,-1.0],[33.310480943479895,34.87224749772528,-1074.7921,0.0,7.0,0.0,-1.0],[34.87224749772528,38.776663883338756,0.0,0.0,6.0,1.0,-1.0],[38.776663883338756,54.39432942579264,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C647" t="n">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>[[15.001412810804764,34.90126157782096,-1860.0,1.0,6.0,0.0,-1.0],[34.90126157782096,35.31584176046713,-1074.7922,0.0,6.0,0.0,-1.0],[35.31584176046713,39.461643586928844,0.0,0.0,5.0,1.0,-1.0],[39.461643586928844,56.04485089277568,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[15.001412810804764,34.90126157782096,-1860.0,1.0,6.0,0.0,-1.0],[34.90126157782096,35.31584176046713,-1074.7921,0.0,6.0,0.0,-1.0],[35.31584176046713,39.461643586928844,0.0,0.0,5.0,1.0,-1.0],[39.461643586928844,56.04485089277568,1860.0,0.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C648" t="n">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>[[15.093806695932079,32.88485232806318,-1860.0,1.0,5.0,0.0,-1.0],[32.88485232806318,35.31090400517196,-1074.7922,0.0,5.0,0.0,-1.0],[35.31090400517196,38.949981520835145,0.0,0.0,4.0,1.0,-1.0],[38.949981520835145,39.75866541320474,890.0,0.0,4.0,0.0,-1.0],[39.75866541320474,55.12365936822706,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[15.093806695932079,32.88485232806318,-1860.0,1.0,5.0,0.0,-1.0],[32.88485232806318,35.31090400517196,-1074.7921,0.0,5.0,0.0,-1.0],[35.31090400517196,38.949981520835145,0.0,0.0,4.0,1.0,-1.0],[38.949981520835145,39.75866541320474,890.0001,0.0,4.0,0.0,-1.0],[39.75866541320474,55.12365936822706,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C649" t="n">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>[[15.081344426556138,27.67290722465218,-1860.0,1.0,5.0,0.0,-1.0],[27.67290722465218,34.14856809224443,-1074.7922,0.0,5.0,0.0,-1.0],[34.14856809224443,38.105916400217474,0.0,0.0,4.0,1.0,-1.0],[38.105916400217474,39.54495214857131,890.0,0.0,4.0,0.0,-1.0],[39.54495214857131,50.697479198313516,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[15.081344426556138,27.67290722465218,-1860.0,1.0,5.0,0.0,-1.0],[27.67290722465218,34.14856809224443,-1074.7921,0.0,5.0,0.0,-1.0],[34.14856809224443,38.105916400217474,0.0,0.0,4.0,1.0,-1.0],[38.105916400217474,39.54495214857131,890.0001,0.0,4.0,0.0,-1.0],[39.54495214857131,50.697479198313516,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C650" t="n">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>[[14.77468045156605,30.73523133969364,-1860.0,1.0,4.0,0.0,-1.0],[30.73523133969364,33.39532315438157,-1074.7922,0.0,4.0,0.0,-1.0],[33.39532315438157,36.72043792274149,0.0,0.0,3.0,1.0,-1.0],[36.72043792274149,39.38052973742942,890.0,0.0,3.0,0.0,-1.0],[39.38052973742942,47.6933166583292,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[14.77468045156605,30.73523133969364,-1860.0,1.0,4.0,0.0,-1.0],[30.73523133969364,33.39532315438157,-1074.7921,0.0,4.0,0.0,-1.0],[33.39532315438157,36.72043792274149,0.0,0.0,3.0,1.0,-1.0],[36.72043792274149,39.38052973742942,890.0001,0.0,3.0,0.0,-1.0],[39.38052973742942,47.6933166583292,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C651" t="n">
@@ -8905,11 +8905,11 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>[[15.751388302345143,29.827492769927723,-1860.0,1.0,3.0,0.0,-1.0],[29.827492769927723,34.519527592455255,-1074.7922,0.0,3.0,0.0,-1.0],[34.519527592455255,38.20612638158402,0.0,0.0,2.0,1.0,-1.0],[38.20612638158402,39.88185310391528,890.0,0.0,2.0,0.0,-1.0],[39.88185310391528,48.930777404504084,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[15.751388302345143,29.827492769927723,-1860.0,1.0,3.0,0.0,-1.0],[29.827492769927723,34.519527592455255,-1074.7921,0.0,3.0,0.0,-1.0],[34.519527592455255,38.20612638158402,0.0,0.0,2.0,1.0,-1.0],[38.20612638158402,39.88185310391528,890.0001,0.0,2.0,0.0,-1.0],[39.88185310391528,48.930777404504084,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C652" t="n">
-        <v>890</v>
+        <v>890.0001</v>
       </c>
     </row>
     <row r="653">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>[[15.878218514382214,30.989303834002033,-1860.0,1.0,2.0,0.0,-1.0],[30.989303834002033,36.77652799896281,-0.0,0.0,1.0,1.0,-1.0],[36.77652799896281,47.707951421666515,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[15.878218514382214,30.989303834002033,-1860.0,1.0,2.0,0.0,-1.0],[30.989303834002033,36.77652799896281,0.0,0.0,2.0,1.0,-1.0],[36.77652799896281,47.707951421666515,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C653" t="n">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>[[15.177786281558943,30.55278578257377,-1860.0,1.0,1.0,0.0,-1.0],[30.55278578257377,33.49693462319364,-0.0,0.0,1.0,1.0,-1.0],[33.49693462319364,37.09533876172902,0.0,0.0,0.0,1.0,-1.0],[37.09533876172902,37.42246641068678,1860.0,0.0,0.0,0.0,-1.0],[37.42246641068678,47.56342352837742,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[15.177786281558943,30.55278578257377,-1860.0,1.0,1.0,0.0,-1.0],[30.55278578257377,37.09533876172902,0.0,0.0,1.0,1.0,-1.0],[37.09533876172902,47.56342352837742,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C654" t="n">
@@ -8944,11 +8944,11 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>[[15.774416554386047,29.372975476177313,-1860.0,1.0,0.0,0.0,-1.0],[29.372975476177313,46.3711741284164,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[15.774416554386047,29.372975476177313,-1860.0,1.0,0.0,0.0,-1.0],[29.372975476177313,46.3711741284164,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C655" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="656">
@@ -8957,7 +8957,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>[[15.134100086077074,23.042745215831857,-1860.0,9.0,0.0,1.0,1.0],[23.042745215831857,23.651102533505302,-733.6842,9.0,0.0,1.0,1.0],[23.651102533505302,45.2477873109126,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[15.134100086077074,23.042745215831857,-1860.0,7.0,0.0,1.0,1.0],[23.042745215831857,23.651102533505302,-733.6842,9.0,0.0,1.0,1.0],[23.651102533505302,45.2477873109126,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C656" t="n">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>[[15.59322238749069,24.223458261848442,-1860.0,8.0,0.0,0.0,1.0],[24.223458261848442,28.230353489228833,-733.6842,8.0,0.0,0.0,1.0],[28.230353489228833,31.312580587213745,0.0,8.0,0.0,1.0,1.0],[31.312580587213745,35.011253104795635,1016.5,9.0,0.0,0.0,1.0],[35.011253104795635,46.10727065754133,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[15.59322238749069,24.223458261848442,-1860.0,7.0,0.0,0.0,1.0],[24.223458261848442,28.230353489228833,-733.6842,8.0,0.0,0.0,1.0],[28.230353489228833,31.312580587213745,0.0,7.0,0.0,1.0,1.0],[31.312580587213745,35.011253104795635,1016.5,9.0,0.0,0.0,1.0],[35.011253104795635,46.10727065754133,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C658" t="n">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>[[15.757141210793566,23.390326556607754,-1860.0,7.0,0.0,0.0,1.0],[23.390326556607754,29.191547419426534,-733.6842,7.0,0.0,0.0,1.0],[29.191547419426534,32.550148971584775,0.0,7.0,0.0,1.0,1.0],[32.550148971584775,34.68744086841275,1016.5,8.0,0.0,0.0,1.0],[34.68744086841275,35.29809569607788,1725.15,9.0,9.0,2.0,-1.0],[35.29809569607788,45.98455518021775,1860.0,9.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.757141210793566,23.390326556607754,-1860.0,6.0,0.0,0.0,1.0],[23.390326556607754,29.191547419426534,-733.6842,7.0,0.0,0.0,1.0],[29.191547419426534,32.550148971584775,0.0,6.0,0.0,1.0,1.0],[32.550148971584775,34.68744086841275,1016.5,8.0,0.0,0.0,1.0],[34.68744086841275,35.29809569607788,1725.15,8.0,9.0,2.0,-1.0],[35.29809569607788,45.98455518021775,1860.0,9.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C659" t="n">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>[[15.412417416526957,23.307904819403745,-1860.0,6.0,0.0,0.0,1.0],[23.307904819403745,28.9005417297748,-733.6842,6.0,0.0,0.0,1.0],[28.9005417297748,32.19032814764013,0.0,6.0,0.0,1.0,1.0],[32.19032814764013,34.49317864014586,1016.5,7.0,0.0,0.0,1.0],[34.49317864014586,34.82215728193239,1725.15,8.0,9.0,2.0,-1.0],[34.82215728193239,47.9813029533937,1860.0,8.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.412417416526957,23.307904819403745,-1860.0,6.0,0.0,0.0,1.0],[23.307904819403745,28.9005417297748,-733.6842,5.0,0.0,0.0,1.0],[28.9005417297748,32.19032814764013,0.0,5.0,0.0,1.0,1.0],[32.19032814764013,34.49317864014586,1016.5,7.0,0.0,0.0,1.0],[34.49317864014586,34.82215728193239,1725.15,8.0,9.0,2.0,-1.0],[34.82215728193239,47.9813029533937,1860.0,8.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C660" t="n">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>[[15.480965077534327,22.737637267054176,-1860.0,5.0,0.0,0.0,1.0],[22.737637267054176,28.612086182379766,-733.6842,5.0,0.0,0.0,1.0],[28.612086182379766,31.722088549316844,0.0,5.0,0.0,1.0,1.0],[31.722088549316844,34.140979279156795,1016.5,6.0,0.0,0.0,1.0],[34.140979279156795,34.832090916253925,1725.15,7.0,9.0,2.0,-1.0],[34.832090916253925,49.69099111384219,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.480965077534327,22.737637267054176,-1860.0,5.0,0.0,0.0,1.0],[22.737637267054176,28.612086182379766,-733.6842,4.0,0.0,0.0,1.0],[28.612086182379766,31.722088549316844,0.0,4.0,0.0,1.0,1.0],[31.722088549316844,34.140979279156795,1016.5,4.0,0.0,0.0,1.0],[34.140979279156795,34.832090916253925,1725.15,7.0,9.0,2.0,-1.0],[34.832090916253925,49.69099111384219,1860.0,7.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C661" t="n">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>[[15.301263784589397,19.08752914840641,-1860.0,4.0,0.0,0.0,1.0],[19.08752914840641,28.381089586866356,-733.6842,4.0,0.0,0.0,1.0],[28.381089586866356,31.478943066353004,0.0,4.0,0.0,1.0,1.0],[31.478943066353004,34.23259060367447,1016.5,5.0,0.0,0.0,1.0],[34.23259060367447,34.57679654583965,1725.15,6.0,9.0,2.0,-1.0],[34.57679654583965,49.37765205894252,1860.0,6.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.301263784589397,19.08752914840641,-1860.0,3.0,0.0,0.0,1.0],[19.08752914840641,28.381089586866356,-733.6842,3.0,0.0,0.0,1.0],[28.381089586866356,31.478943066353004,0.0,3.0,0.0,1.0,1.0],[31.478943066353004,34.23259060367447,1016.5,4.0,0.0,0.0,1.0],[34.23259060367447,34.57679654583965,1725.15,5.0,9.0,2.0,-1.0],[34.57679654583965,49.37765205894252,1860.0,5.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C662" t="n">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>[[15.319409572035747,27.97448690278405,-1860.0,4.0,0.0,0.0,1.0],[27.97448690278405,35.07367662491115,-0.0,4.0,0.0,1.0,1.0],[35.07367662491115,45.87679141945238,1860.0,5.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.319409572035747,27.97448690278405,-1860.0,3.0,0.0,0.0,1.0],[27.97448690278405,35.07367662491115,0.0,3.0,0.0,1.0,1.0],[35.07367662491115,45.87679141945238,1860.0,4.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C663" t="n">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>[[15.875033184735637,27.98434482472492,-1860.0,3.0,0.0,0.0,1.0],[27.98434482472492,34.644466226719025,-0.0,3.0,0.0,1.0,1.0],[34.644466226719025,35.249931808718486,890.0,3.0,8.0,4.0,-1.0],[35.249931808718486,45.84557949370911,1860.0,3.0,8.0,4.0,-1.0]]</t>
+          <t>[[15.875033184735637,27.98434482472492,-1860.0,1.0,0.0,0.0,1.0],[27.98434482472492,34.644466226719025,0.0,2.0,0.0,1.0,1.0],[34.644466226719025,35.249931808718486,890.0,2.0,8.0,4.0,-1.0],[35.249931808718486,45.84557949370911,1860.0,2.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C664" t="n">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>[[7.40668292284102,32.0729403673296,-1860.0,3.0,0.0,0.0,1.0],[32.0729403673296,32.458350639899734,-1074.7923,3.0,9.0,2.0,-1.0],[32.458350639899734,35.92704309303094,0.0,2.0,7.0,1.0,-1.0],[35.92704309303094,36.31245336560107,1071.35,2.0,7.0,1.0,-1.0],[36.31245336560107,45.56229990728429,1860.0,2.0,7.0,1.0,-1.0]]</t>
+          <t>[[7.40668292284102,32.0729403673296,-1860.0,1.0,0.0,0.0,1.0],[32.0729403673296,32.458350639899734,-1074.7922,2.0,9.0,2.0,-1.0],[32.458350639899734,35.92704309303094,0.0,2.0,7.0,1.0,-1.0],[35.92704309303094,36.31245336560107,1071.35,2.0,7.0,1.0,-1.0],[36.31245336560107,45.56229990728429,1860.0,1.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C665" t="n">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>[[7.342765194682687,31.577713215216676,-1860.0,2.0,0.0,0.0,1.0],[31.577713215216676,35.09568954077806,0.0,2.0,8.0,3.0,-1.0],[35.09568954077806,35.87746205756948,890.0,2.0,8.0,3.0,-1.0],[35.87746205756948,46.040504775857926,1860.0,2.0,8.0,3.0,-1.0]]</t>
+          <t>[[7.342765194682687,31.577713215216676,-1860.0,1.0,0.0,0.0,1.0],[31.577713215216676,35.09568954077806,0.0,2.0,8.0,3.0,-1.0],[35.09568954077806,35.87746205756948,890.0,2.0,8.0,3.0,-1.0],[35.87746205756948,46.040504775857926,1860.0,1.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C666" t="n">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>[[6.9510885856512665,31.628901835611902,-1860.0,1.0,0.0,0.0,1.0],[31.628901835611902,32.412324478467795,-1074.7923,1.0,9.0,2.0,-1.0],[32.412324478467795,35.937726371319314,0.0,1.0,8.0,3.0,-1.0],[35.937726371319314,36.32943769274726,890.0,1.0,8.0,3.0,-1.0],[36.32943769274726,45.73050940701798,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[6.9510885856512665,31.628901835611902,-1860.0,0.0,0.0,0.0,1.0],[31.628901835611902,32.412324478467795,-1074.7922,1.0,9.0,2.0,-1.0],[32.412324478467795,35.937726371319314,0.0,1.0,8.0,3.0,-1.0],[35.937726371319314,36.32943769274726,890.0,1.0,8.0,3.0,-1.0],[36.32943769274726,45.73050940701798,1860.0,1.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C667" t="n">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>[[7.168922608885759,34.13795349870542,-0.0,0.0,0.0,1.0,1.0],[34.13795349870542,35.382678001312485,890.0,0.0,8.0,3.0,-1.0],[35.382678001312485,48.24483119491879,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[7.168922608885759,34.13795349870542,0.0,0.0,0.0,1.0,1.0],[34.13795349870542,35.382678001312485,890.0,0.0,8.0,3.0,-1.0],[35.382678001312485,48.24483119491879,1860.0,0.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C668" t="n">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>[[6.937129663466531,29.632533295052465,-1860.0,1.0,8.0,2.0,-1.0],[29.632533295052465,30.037808359902215,-1074.7923,0.0,8.0,2.0,-1.0],[30.037808359902215,33.2800088787002,0.0,0.0,7.0,3.0,-1.0],[33.2800088787002,34.901109138099194,890.0,0.0,7.0,3.0,-1.0],[34.901109138099194,47.05936108359166,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[6.937129663466531,29.632533295052465,-1860.0,1.0,8.0,2.0,-1.0],[29.632533295052465,30.037808359902215,-1074.7922,0.0,8.0,2.0,-1.0],[30.037808359902215,33.2800088787002,0.0,0.0,7.0,3.0,-1.0],[33.2800088787002,34.901109138099194,890.0,0.0,7.0,3.0,-1.0],[34.901109138099194,47.05936108359166,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C669" t="n">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>[[7.417254319787326,28.14665665296946,-1860.0,1.0,8.0,0.0,-1.0],[28.14665665296946,29.166135456240713,-1074.7923,0.0,8.0,1.0,-1.0],[29.166135456240713,32.56439813381156,0.0,0.0,7.0,2.0,-1.0],[32.56439813381156,34.26352947259698,890.0,0.0,7.0,2.0,-1.0],[34.26352947259698,41.06005482773866,1860.0,0.0,7.0,2.0,-1.0]]</t>
+          <t>[[7.417254319787326,28.14665665296946,-1860.0,1.0,8.0,0.0,-1.0],[28.14665665296946,29.166135456240713,-1074.7922,0.0,8.0,1.0,-1.0],[29.166135456240713,32.56439813381156,0.0,0.0,7.0,2.0,-1.0],[32.56439813381156,34.26352947259698,890.0,0.0,7.0,2.0,-1.0],[34.26352947259698,41.06005482773866,1860.0,0.0,7.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C670" t="n">
@@ -9152,7 +9152,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>[[7.22917318841805,27.595961505092752,-1860.0,1.0,8.0,0.0,-1.0],[27.595961505092752,28.868885774884923,-1074.7923,0.0,8.0,1.0,-1.0],[28.868885774884923,32.05119644936534,0.0,0.0,7.0,2.0,-1.0],[32.05119644936534,32.68765858426143,890.0,0.0,7.0,1.0,-1.0],[32.68765858426143,38.734048865774234,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[7.22917318841805,27.595961505092752,-1860.0,1.0,8.0,0.0,-1.0],[27.595961505092752,28.868885774884923,-1074.7922,0.0,8.0,1.0,-1.0],[28.868885774884923,32.05119644936534,0.0,0.0,7.0,2.0,-1.0],[32.05119644936534,32.68765858426143,890.0,0.0,7.0,1.0,-1.0],[32.68765858426143,38.734048865774234,1860.0,0.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C671" t="n">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>[[7.07979083730359,27.449390922018026,-1860.0,1.0,7.0,0.0,-1.0],[27.449390922018026,28.139885840143936,-1074.7923,0.0,7.0,0.0,-1.0],[28.139885840143936,30.90186551264759,0.0,0.0,6.0,1.0,-1.0],[30.90186551264759,32.28285534889942,890.0,0.0,6.0,1.0,-1.0],[32.28285534889942,41.25928928453629,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[7.07979083730359,27.449390922018026,-1860.0,1.0,7.0,0.0,-1.0],[27.449390922018026,28.139885840143936,-1074.7922,0.0,7.0,0.0,-1.0],[28.139885840143936,30.90186551264759,0.0,0.0,6.0,1.0,-1.0],[30.90186551264759,32.28285534889942,890.0,0.0,6.0,1.0,-1.0],[32.28285534889942,41.25928928453629,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C672" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>[[6.855898764790677,27.84861379160557,-1860.0,1.0,5.0,0.0,-1.0],[27.84861379160557,28.23029951936584,-1074.7923,0.0,5.0,0.0,-1.0],[28.23029951936584,31.665471069208277,0.0,0.0,4.0,1.0,-1.0],[31.665471069208277,44.642785813057486,1860.0,0.0,4.0,1.0,-1.0]]</t>
+          <t>[[6.855898764790677,27.84861379160557,-1860.0,1.0,5.0,0.0,-1.0],[27.84861379160557,28.23029951936584,-1074.7922,0.0,5.0,0.0,-1.0],[28.23029951936584,31.665471069208277,0.0,0.0,4.0,1.0,-1.0],[31.665471069208277,44.642785813057486,1860.0,0.0,4.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C674" t="n">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>[[6.422290305579039,28.485493283549324,-1860.0,1.0,4.0,0.0,-1.0],[28.485493283549324,29.233398469243234,-1074.7923,0.0,4.0,1.0,-1.0],[29.233398469243234,32.225019212018864,0.0,0.0,3.0,2.0,-1.0],[32.225019212018864,32.59897180486582,890.0,0.0,3.0,2.0,-1.0],[32.59897180486582,43.443596997427484,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[6.422290305579039,28.485493283549324,-1860.0,1.0,4.0,0.0,-1.0],[28.485493283549324,29.233398469243234,-1074.7922,0.0,4.0,1.0,-1.0],[29.233398469243234,32.225019212018864,0.0,0.0,3.0,2.0,-1.0],[32.225019212018864,32.59897180486582,890.0,0.0,3.0,2.0,-1.0],[32.59897180486582,43.443596997427484,1860.0,0.0,3.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C675" t="n">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>[[7.070425708983416,28.78504312001573,-1860.0,1.0,3.0,0.0,-1.0],[28.78504312001573,29.49699778922991,-1074.7923,0.0,3.0,0.0,-1.0],[29.49699778922991,32.70079380069369,0.0,0.0,2.0,1.0,-1.0],[32.70079380069369,35.548612477550385,890.0,0.0,2.0,1.0,-1.0],[35.548612477550385,42.31218183508504,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[7.070425708983416,28.78504312001573,-1860.0,1.0,3.0,0.0,-1.0],[28.78504312001573,29.49699778922991,-1074.7922,0.0,3.0,0.0,-1.0],[29.49699778922991,32.70079380069369,0.0,0.0,2.0,1.0,-1.0],[32.70079380069369,35.548612477550385,890.0,0.0,2.0,1.0,-1.0],[35.548612477550385,42.31218183508504,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C676" t="n">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>[[7.116012772742423,24.391889204313728,-1860.0,9.0,3.0,2.0,1.0],[24.391889204313728,25.494604721222537,-1808.4765,9.0,3.0,2.0,1.0],[25.494604721222537,29.537894949888162,-1074.7923,0.0,3.0,0.0,-1.0],[29.537894949888162,32.47846966164498,0.0,0.0,2.0,1.0,-1.0],[32.47846966164498,33.94875701752339,890.0,0.0,2.0,1.0,-1.0],[33.94875701752339,43.50562483073305,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[7.116012772742423,24.391889204313728,-1860.0,9.0,3.0,2.0,1.0],[24.391889204313728,25.494604721222537,-1808.4764,9.0,3.0,2.0,1.0],[25.494604721222537,29.537894949888162,-1074.7922,0.0,3.0,0.0,-1.0],[29.537894949888162,32.47846966164498,0.0,0.0,2.0,1.0,-1.0],[32.47846966164498,33.94875701752339,890.0,0.0,2.0,1.0,-1.0],[33.94875701752339,43.50562483073305,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C677" t="n">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>[[6.815609251831358,24.449312384869366,-1860.0,10.0,2.0,0.0,1.0],[24.449312384869366,29.847384772534063,-1074.7923,0.0,2.0,0.0,-1.0],[29.847384772534063,33.08622820513288,0.0,0.0,1.0,1.0,-1.0],[33.08622820513288,37.764557607775615,890.0,0.0,1.0,0.0,-1.0],[37.764557607775615,42.44288701041835,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[6.815609251831358,24.449312384869366,-1860.0,10.0,2.0,0.0,1.0],[24.449312384869366,29.847384772534063,-1074.7922,0.0,2.0,0.0,-1.0],[29.847384772534063,33.08622820513288,0.0,0.0,1.0,1.0,-1.0],[33.08622820513288,37.764557607775615,890.0,0.0,1.0,0.0,-1.0],[37.764557607775615,42.44288701041835,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C678" t="n">
@@ -9269,11 +9269,11 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>[[6.826923434851289,23.88813063111298,-1860.0,9.0,1.0,1.0,1.0],[23.88813063111298,24.27588534011893,-1808.4765,9.0,1.0,1.0,1.0],[24.27588534011893,26.990168303160562,0.0,9.0,1.0,1.0,1.0],[26.990168303160562,27.37792301216651,46.5,10.0,1.0,0.0,1.0],[27.37792301216651,45.214639626440096,890.0,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[6.826923434851289,23.88813063111298,-1860.0,9.0,1.0,1.0,1.0],[23.88813063111298,24.27588534011893,-1808.4764,9.0,1.0,1.0,1.0],[24.27588534011893,26.990168303160562,0.0,9.0,1.0,1.0,1.0],[26.990168303160562,27.37792301216651,46.5,10.0,1.0,0.0,1.0],[27.37792301216651,45.214639626440096,890.0001,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C680" t="n">
-        <v>890</v>
+        <v>890.0001</v>
       </c>
     </row>
     <row r="681">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>[[7.224868158370898,26.004920315026013,-1860.0,9.0,0.0,1.0,1.0],[26.004920315026013,36.68377350214362,-0.0,9.0,0.0,1.0,1.0],[36.68377350214362,43.680263521289646,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[7.224868158370898,26.004920315026013,-1860.0,9.0,0.0,1.0,1.0],[26.004920315026013,36.68377350214362,0.0,9.0,0.0,1.0,1.0],[36.68377350214362,43.680263521289646,662.15,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C682" t="n">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>[[7.185375415205917,26.35311924123216,-1860.0,8.0,0.0,1.0,1.0],[26.35311924123216,35.03285229452706,-0.0,8.0,0.0,1.0,1.0],[35.03285229452706,35.75616338230164,890.0,8.0,8.0,4.0,-1.0],[35.75616338230164,42.98927426004739,1860.0,8.0,9.0,3.0,-1.0]]</t>
+          <t>[[7.185375415205917,26.35311924123216,-1860.0,8.0,0.0,1.0,1.0],[26.35311924123216,35.03285229452706,0.0,8.0,0.0,1.0,1.0],[35.03285229452706,35.75616338230164,889.9999,8.0,8.0,4.0,-1.0],[35.75616338230164,42.98927426004739,1860.0,8.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C683" t="n">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>[[7.121039743720916,26.710328764446032,-1860.0,7.0,0.0,1.0,1.0],[26.710328764446032,36.5049732748086,-0.0,7.0,0.0,1.0,1.0],[36.5049732748086,36.8677378863035,890.0,7.0,8.0,3.0,-1.0],[36.8677378863035,43.03473628171697,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[7.121039743720916,26.710328764446032,-1860.0,7.0,0.0,1.0,1.0],[26.710328764446032,36.5049732748086,0.0,7.0,0.0,1.0,1.0],[36.5049732748086,36.8677378863035,889.9999,7.0,8.0,3.0,-1.0],[36.8677378863035,43.03473628171697,1860.0,7.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C684" t="n">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>[[7.019629382299565,26.105943105379367,-1860.0,6.0,0.0,1.0,1.0],[26.105943105379367,36.412552515842464,-0.0,6.0,0.0,1.0,1.0],[36.412552515842464,37.55773133922725,890.0,6.0,8.0,4.0,-1.0],[37.55773133922725,44.81053055399757,1860.0,6.0,8.0,4.0,-1.0]]</t>
+          <t>[[7.019629382299565,26.105943105379367,-1860.0,5.0,0.0,1.0,1.0],[26.105943105379367,36.412552515842464,0.0,4.0,0.0,1.0,1.0],[36.412552515842464,37.55773133922725,889.9999,4.0,8.0,4.0,-1.0],[37.55773133922725,44.81053055399757,1860.0,5.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C685" t="n">
@@ -9347,11 +9347,11 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>[[5.855215861552942,24.168189152101355,-1860.0,5.0,0.0,0.0,1.0],[24.168189152101355,36.25475152386331,-0.0,5.0,0.0,1.0,1.0],[36.25475152386331,36.621010989674275,890.0,5.0,8.0,4.0,-1.0],[36.621010989674275,42.114902976838806,1860.0,5.0,9.0,3.0,-1.0]]</t>
+          <t>[[5.855215861552942,24.168189152101355,-1860.0,4.0,0.0,0.0,1.0],[24.168189152101355,36.25475152386331,0.0,4.0,0.0,1.0,1.0],[36.25475152386331,36.621010989674275,889.9999,4.0,8.0,4.0,-1.0],[36.621010989674275,42.114902976838806,1860.0,3.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C686" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="687">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>[[5.797994855764833,32.81892929969216,-1860.0,5.0,0.0,0.0,1.0],[32.81892929969216,37.4510894900797,-0.0,5.0,0.0,1.0,1.0],[37.4510894900797,44.013316426462055,1860.0,5.0,8.0,3.0,-1.0]]</t>
+          <t>[[5.797994855764833,32.81892929969216,-1860.0,4.0,0.0,0.0,1.0],[32.81892929969216,37.4510894900797,0.0,4.0,0.0,1.0,1.0],[37.4510894900797,44.013316426462055,1860.0,3.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C687" t="n">
@@ -9373,7 +9373,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>[[5.420225279167751,33.84564490494072,-1860.0,4.0,0.0,0.0,1.0],[33.84564490494072,34.235034214882816,-873.8504,3.0,8.0,3.0,-1.0],[34.235034214882816,37.73953800436168,0.0,3.0,7.0,4.0,-1.0],[37.73953800436168,43.969766963435205,1860.0,3.0,8.0,3.0,-1.0]]</t>
+          <t>[[5.420225279167751,33.84564490494072,-1860.0,3.0,0.0,0.0,1.0],[33.84564490494072,34.235034214882816,-873.8505,2.0,8.0,3.0,-1.0],[34.235034214882816,37.73953800436168,0.0,2.0,7.0,4.0,-1.0],[37.73953800436168,43.969766963435205,1860.0,2.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C688" t="n">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>[[5.7508207852407525,33.001741461744125,-1860.0,3.0,0.0,0.0,1.0],[33.001741461744125,36.78659155570293,0.0,2.0,7.0,4.0,-1.0],[36.78659155570293,37.92204658389057,1071.35,2.0,7.0,4.0,-1.0],[37.92204658389057,43.220836715432895,1860.0,2.0,7.0,4.0,-1.0]]</t>
+          <t>[[5.7508207852407525,33.001741461744125,-1860.0,2.0,0.0,0.0,1.0],[33.001741461744125,36.78659155570293,0.0,2.0,7.0,4.0,-1.0],[36.78659155570293,37.92204658389057,1071.3499,2.0,7.0,4.0,-1.0],[37.92204658389057,43.220836715432895,1860.0,2.0,7.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C689" t="n">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>[[5.964350820839753,32.520769149082675,-1860.0,2.0,0.0,0.0,1.0],[32.520769149082675,36.03558922193835,0.0,1.0,7.0,4.0,-1.0],[36.03558922193835,37.98826704019151,1071.35,1.0,7.0,1.0,-1.0],[37.98826704019151,44.62737162225224,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[5.964350820839753,32.520769149082675,-1860.0,2.0,0.0,0.0,1.0],[32.520769149082675,36.03558922193835,0.0,1.0,7.0,4.0,-1.0],[36.03558922193835,37.98826704019151,1071.3499,1.0,7.0,1.0,-1.0],[37.98826704019151,44.62737162225224,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C690" t="n">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>[[5.752687575372794,32.6346037524853,-1860.0,1.0,0.0,0.0,1.0],[32.6346037524853,36.14094064515214,0.0,0.0,7.0,5.0,-1.0],[36.14094064515214,37.309719609374426,1071.35,0.0,7.0,5.0,-1.0],[37.309719609374426,44.32239339470812,1860.0,0.0,7.0,5.0,-1.0]]</t>
+          <t>[[5.752687575372794,32.6346037524853,-1860.0,1.0,0.0,0.0,1.0],[32.6346037524853,36.14094064515214,0.0,0.0,7.0,5.0,-1.0],[36.14094064515214,37.309719609374426,1071.3499,0.0,7.0,5.0,-1.0],[37.309719609374426,44.32239339470812,1860.0,0.0,7.0,5.0,-1.0]]</t>
         </is>
       </c>
       <c r="C691" t="n">
@@ -9425,11 +9425,11 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>[[6.19610098460995,37.06424312311912,-0.0,0.0,0.0,1.0,1.0],[37.06424312311912,37.43172100572042,890.0,0.0,8.0,2.0,-1.0],[37.43172100572042,42.576411362138614,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[6.19610098460995,37.06424312311912,0.0,0.0,0.0,1.0,1.0],[37.06424312311912,37.43172100572042,889.9999,0.0,8.0,2.0,-1.0],[37.43172100572042,42.576411362138614,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C692" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="693">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>[[5.777144260757365,35.54331894192165,-0.0,0.0,0.0,1.0,1.0],[35.54331894192165,36.023418533553325,890.0,0.0,8.0,0.0,-1.0],[36.023418533553325,53.30700383229388,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[5.777144260757365,35.54331894192165,0.0,0.0,0.0,1.0,1.0],[35.54331894192165,36.023418533553325,889.9999,0.0,8.0,0.0,-1.0],[36.023418533553325,53.30700383229388,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C693" t="n">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>[[5.942806062990978,31.221650593240938,-1860.0,1.0,7.0,0.0,-1.0],[31.221650593240938,31.853621706497186,-1074.7923,0.0,7.0,1.0,-1.0],[31.853621706497186,35.01347727277843,0.0,0.0,6.0,2.0,-1.0],[35.01347727277843,36.27741949929093,890.0,0.0,6.0,2.0,-1.0],[36.27741949929093,68.50794627535963,1860.0,0.0,6.0,2.0,-1.0]]</t>
+          <t>[[5.942806062990978,31.221650593240938,-1860.0,1.0,7.0,0.0,-1.0],[31.221650593240938,31.853621706497186,-1074.7923,0.0,7.0,1.0,-1.0],[31.853621706497186,35.01347727277843,0.0,0.0,6.0,2.0,-1.0],[35.01347727277843,36.27741949929093,889.9999,0.0,6.0,2.0,-1.0],[36.27741949929093,68.50794627535963,1860.0,0.0,6.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C695" t="n">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>[[5.644910302815902,30.8937013071726,-1860.0,1.0,6.0,0.0,-1.0],[30.8937013071726,32.04137362555245,-1074.7923,0.0,6.0,1.0,-1.0],[32.04137362555245,35.48439058069199,0.0,0.0,5.0,2.0,-1.0],[35.48439058069199,37.20589905826177,890.0,0.0,5.0,2.0,-1.0],[37.20589905826177,62.45469006261847,1860.0,0.0,5.0,2.0,-1.0]]</t>
+          <t>[[5.644910302815902,30.8937013071726,-1860.0,1.0,6.0,0.0,-1.0],[30.8937013071726,32.04137362555245,-1074.7923,0.0,6.0,1.0,-1.0],[32.04137362555245,35.48439058069199,0.0,0.0,5.0,2.0,-1.0],[35.48439058069199,37.20589905826177,889.9999,0.0,5.0,2.0,-1.0],[37.20589905826177,62.45469006261847,1860.0,0.0,5.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C696" t="n">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>[[5.656569383363265,31.483819955773455,-1860.0,1.0,4.0,0.0,-1.0],[31.483819955773455,32.71368903065013,-1074.7923,0.0,4.0,1.0,-1.0],[32.71368903065013,36.403296255280154,0.0,0.0,3.0,2.0,-1.0],[36.403296255280154,37.01823079271849,890.0,0.0,3.0,2.0,-1.0],[37.01823079271849,66.5350885897587,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[5.656569383363265,31.483819955773455,-1860.0,1.0,4.0,0.0,-1.0],[31.483819955773455,32.71368903065013,-1074.7923,0.0,4.0,1.0,-1.0],[32.71368903065013,36.403296255280154,0.0,0.0,3.0,2.0,-1.0],[36.403296255280154,37.01823079271849,889.9999,0.0,3.0,2.0,-1.0],[37.01823079271849,66.5350885897587,1860.0,0.0,3.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C698" t="n">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>[[5.949061243550825,31.691487132188282,-1860.0,10.0,11.0,2.0,0.0],[31.691487132188282,34.75606164274036,0.0,9.0,11.0,3.0,0.0],[34.75606164274036,35.368976544850774,890.0,0.0,2.0,1.0,-1.0],[35.368976544850774,66.62763655248197,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[5.949061243550825,31.691487132188282,-1860.0,10.0,11.0,2.0,0.0],[31.691487132188282,34.75606164274036,0.0,9.0,11.0,3.0,0.0],[34.75606164274036,35.368976544850774,889.9999,0.0,2.0,1.0,-1.0],[35.368976544850774,66.62763655248197,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C699" t="n">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>[[5.9211837771289675,31.90178804470698,-1860.0,9.0,1.0,2.0,1.0],[31.90178804470698,32.50598814395298,-1607.5347,8.0,1.0,3.0,1.0],[32.50598814395298,33.110188243198984,-822.3269,9.0,10.0,4.0,0.0],[33.110188243198984,36.73538883867498,0.0,9.0,10.0,4.0,0.0],[36.73538883867498,37.94378903716698,890.0,0.0,1.0,1.0,-1.0],[37.94378903716698,65.736993602483,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[5.9211837771289675,31.90178804470698,-1860.0,9.0,1.0,2.0,1.0],[31.90178804470698,32.50598814395298,-1607.5347,8.0,1.0,3.0,1.0],[32.50598814395298,33.110188243198984,-822.327,9.0,10.0,4.0,0.0],[33.110188243198984,36.73538883867498,0.0,9.0,10.0,4.0,0.0],[36.73538883867498,37.94378903716698,889.9999,0.0,1.0,1.0,-1.0],[37.94378903716698,65.736993602483,1860.0,0.0,1.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C700" t="n">
@@ -9542,11 +9542,11 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>[[5.5820891349112465,32.32630314018349,-1860.0,9.0,2.0,0.0,1.0],[32.32630314018349,35.89219834088645,0.0,9.0,1.0,1.0,1.0],[35.89219834088645,36.48651420767028,227.85,9.0,1.0,1.0,1.0],[36.48651420767028,37.67514594123794,890.0,0.0,1.0,0.0,-1.0],[37.67514594123794,64.41935994651018,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[5.5820891349112465,32.32630314018349,-1860.0,9.0,2.0,0.0,1.0],[32.32630314018349,35.89219834088645,0.0,9.0,1.0,1.0,1.0],[35.89219834088645,36.48651420767028,227.8499,9.0,1.0,1.0,1.0],[36.48651420767028,37.67514594123794,889.9999,0.0,1.0,0.0,-1.0],[37.67514594123794,64.41935994651018,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C701" t="n">
-        <v>227.85</v>
+        <v>227.8499</v>
       </c>
     </row>
     <row r="702">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>[[5.8823909272670205,32.29880920212269,-1860.0,9.0,1.0,1.0,1.0],[32.29880920212269,36.31869893960072,0.0,9.0,0.0,1.0,1.0],[36.31869893960072,62.73511721445639,1860.0,9.0,1.0,1.0,1.0]]</t>
+          <t>[[5.8823909272670205,32.29880920212269,-1860.0,8.0,1.0,1.0,1.0],[32.29880920212269,36.31869893960072,0.0,8.0,1.0,1.0,1.0],[36.31869893960072,62.73511721445639,1860.0,9.0,1.0,1.0,1.0]]</t>
         </is>
       </c>
       <c r="C702" t="n">
@@ -9568,11 +9568,11 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>[[5.980859745441576,32.362751141045614,-1860.0,9.0,0.0,1.0,1.0],[32.362751141045614,38.811657926637714,-0.0,9.0,0.0,1.0,1.0],[38.811657926637714,64.02102081577047,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[5.980859745441576,32.362751141045614,-1860.0,9.0,0.0,1.0,1.0],[32.362751141045614,38.811657926637714,0.0,8.0,0.0,1.0,1.0],[38.811657926637714,64.02102081577047,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C703" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="704">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>[[5.551586064375953,34.682302039284565,-1860.0,9.0,0.0,0.0,1.0],[34.682302039284565,38.93053145229207,-0.0,9.0,0.0,3.0,1.0],[38.93053145229207,65.63368776262496,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[5.551586064375953,34.682302039284565,-1860.0,8.0,0.0,0.0,1.0],[34.682302039284565,38.93053145229207,0.0,8.0,0.0,3.0,1.0],[38.93053145229207,65.63368776262496,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C704" t="n">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>[[5.519737223169096,33.328697471364436,-1860.0,8.0,0.0,0.0,1.0],[33.328697471364436,39.8371775294527,-0.0,8.0,0.0,3.0,1.0],[39.8371775294527,41.0205375400142,890.0,8.0,8.0,2.0,-1.0],[41.0205375400142,64.09605774596352,1860.0,8.0,9.0,1.0,-1.0]]</t>
+          <t>[[5.519737223169096,33.328697471364436,-1860.0,6.0,0.0,0.0,1.0],[33.328697471364436,39.8371775294527,0.0,8.0,0.0,3.0,1.0],[39.8371775294527,41.0205375400142,890.0,8.0,8.0,2.0,-1.0],[41.0205375400142,64.09605774596352,1860.0,8.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C705" t="n">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>[[5.8738382526313515,34.02257256186337,-1860.0,7.0,0.0,0.0,1.0],[34.02257256186337,38.71402828006871,-0.0,7.0,0.0,3.0,1.0],[38.71402828006871,63.930602765422385,1860.0,7.0,8.0,2.0,-1.0]]</t>
+          <t>[[5.8738382526313515,34.02257256186337,-1860.0,5.0,0.0,0.0,1.0],[34.02257256186337,38.71402828006871,0.0,7.0,0.0,3.0,1.0],[38.71402828006871,63.930602765422385,1860.0,5.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C706" t="n">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>[[5.790447701973391,33.61829338027952,-1860.0,6.0,0.0,0.0,1.0],[33.61829338027952,39.53911160970635,-0.0,6.0,0.0,3.0,1.0],[39.53911160970635,40.131193432649034,890.0,6.0,8.0,3.0,-1.0],[40.131193432649034,64.40654817329906,1860.0,6.0,8.0,3.0,-1.0]]</t>
+          <t>[[5.790447701973391,33.61829338027952,-1860.0,4.0,0.0,0.0,1.0],[33.61829338027952,39.53911160970635,0.0,4.0,0.0,3.0,1.0],[39.53911160970635,40.131193432649034,890.0,5.0,8.0,3.0,-1.0],[40.131193432649034,64.40654817329906,1860.0,6.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C707" t="n">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>[[5.717840236276732,34.20607486027302,-1860.0,5.0,0.0,0.0,1.0],[34.20607486027302,34.82538430862077,-1074.7923,5.0,9.0,3.0,-1.0],[34.82538430862077,38.54124099870724,0.0,5.0,8.0,4.0,-1.0],[38.54124099870724,39.77985989540272,890.0,5.0,8.0,4.0,-1.0],[39.77985989540272,67.02947562270352,1860.0,5.0,8.0,4.0,-1.0]]</t>
+          <t>[[5.717840236276732,34.20607486027302,-1860.0,3.0,0.0,0.0,1.0],[34.20607486027302,34.82538430862077,-1074.7922,4.0,9.0,3.0,-1.0],[34.82538430862077,38.54124099870724,0.0,4.0,8.0,4.0,-1.0],[38.54124099870724,39.77985989540272,890.0,4.0,8.0,4.0,-1.0],[39.77985989540272,67.02947562270352,1860.0,5.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C708" t="n">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>[[5.59923945864782,33.54709545904373,-1860.0,4.0,0.0,0.0,1.0],[33.54709545904373,34.154657546008856,-1074.7923,4.0,9.0,3.0,-1.0],[34.154657546008856,37.80003006779963,0.0,4.0,8.0,4.0,-1.0],[37.80003006779963,38.407592154764764,890.0,4.0,8.0,1.0,-1.0],[38.407592154764764,65.74788606819554,1860.0,4.0,8.0,1.0,-1.0]]</t>
+          <t>[[5.59923945864782,33.54709545904373,-1860.0,3.0,0.0,0.0,1.0],[33.54709545904373,34.154657546008856,-1074.7922,3.0,9.0,3.0,-1.0],[34.154657546008856,37.80003006779963,0.0,3.0,8.0,4.0,-1.0],[37.80003006779963,38.407592154764764,890.0,3.0,8.0,1.0,-1.0],[38.407592154764764,65.74788606819554,1860.0,3.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C709" t="n">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>[[10.505498645660388,34.93527156472982,-1860.0,3.0,0.0,0.0,1.0],[34.93527156472982,39.278342305897716,0.0,3.0,0.0,3.0,1.0],[39.278342305897716,64.25099906761314,1860.0,3.0,8.0,4.0,-1.0]]</t>
+          <t>[[10.505498645660388,34.93527156472982,-1860.0,2.0,0.0,0.0,1.0],[34.93527156472982,39.278342305897716,0.0,1.0,0.0,3.0,1.0],[39.278342305897716,64.25099906761314,1860.0,2.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C710" t="n">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>[[17.0354249272596,34.30955869369576,-1860.0,2.0,0.0,0.0,1.0],[34.30955869369576,39.107929184372466,-0.0,2.0,0.0,3.0,1.0],[39.107929184372466,40.06760328250781,890.0,2.0,8.0,2.0,-1.0],[40.06760328250781,64.53929278495903,1860.0,2.0,8.0,2.0,-1.0]]</t>
+          <t>[[17.0354249272596,34.30955869369576,-1860.0,1.0,0.0,0.0,1.0],[34.30955869369576,39.107929184372466,0.0,1.0,0.0,3.0,1.0],[39.107929184372466,40.06760328250781,890.0,2.0,8.0,2.0,-1.0],[40.06760328250781,64.53929278495903,1860.0,2.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C711" t="n">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>[[16.245864004337356,34.34927316690133,-1860.0,1.0,0.0,0.0,1.0],[34.34927316690133,38.99117295217414,-0.0,1.0,0.0,3.0,1.0],[38.99117295217414,40.383742887755986,890.0,1.0,8.0,3.0,-1.0],[40.383742887755986,62.20067187853821,1860.0,1.0,8.0,3.0,-1.0]]</t>
+          <t>[[16.245864004337356,34.34927316690133,-1860.0,0.0,0.0,0.0,1.0],[34.34927316690133,35.277653123955886,0.0,1.0,0.0,3.0,1.0],[35.277653123955886,38.99117295217414,0.0,0.0,0.0,3.0,1.0],[38.99117295217414,40.383742887755986,890.0,1.0,8.0,3.0,-1.0],[40.383742887755986,62.20067187853821,1860.0,1.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C712" t="n">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>[[13.377518634125957,38.178981092299246,-0.0,0.0,0.0,1.0,1.0],[38.178981092299246,40.163098088953106,1678.65,1.0,0.0,1.0,1.0],[40.163098088953106,62.484414301309066,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[13.377518634125957,38.178981092299246,0.0,0.0,0.0,1.0,1.0],[38.178981092299246,40.163098088953106,1678.65,1.0,0.0,1.0,1.0],[40.163098088953106,62.484414301309066,1860.0,1.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C713" t="n">
@@ -9711,11 +9711,11 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>[[10.100087511346796,29.88787855184674,-1860.0,1.0,0.0,0.0,1.0],[29.88787855184674,39.2321132098606,-0.0,1.0,0.0,1.0,1.0],[39.2321132098606,64.51651287272165,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[10.100087511346796,29.88787855184674,-1860.0,0.0,0.0,0.0,1.0],[29.88787855184674,35.384487174207834,0.0,1.0,0.0,1.0,1.0],[35.384487174207834,38.13279148538838,0.0,0.0,0.0,1.0,1.0],[38.13279148538838,39.2321132098606,0.0,1.0,0.0,1.0,1.0],[39.2321132098606,64.51651287272165,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C714" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="715">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>[[6.038010189969462,35.23858817463015,-1860.0,1.0,0.0,0.0,1.0],[35.23858817463015,36.40661129401657,-873.8504,0.0,8.0,0.0,-1.0],[36.40661129401657,40.49469221186907,0.0,0.0,7.0,1.0,-1.0],[40.49469221186907,41.6627153312555,1071.35,0.0,7.0,0.0,-1.0],[41.6627153312555,63.855154599597626,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[6.038010189969462,35.23858817463015,-1860.0,0.0,0.0,0.0,1.0],[35.23858817463015,36.40661129401657,-873.8504,0.0,8.0,0.0,-1.0],[36.40661129401657,40.49469221186907,0.0,0.0,7.0,1.0,-1.0],[40.49469221186907,41.6627153312555,1071.35,0.0,7.0,0.0,-1.0],[41.6627153312555,63.855154599597626,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C715" t="n">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>[[5.9133631656834655,37.28989980832542,-0.0,0.0,0.0,1.0,1.0],[37.28989980832542,39.61408770778038,890.0,0.0,8.0,1.0,-1.0],[39.61408770778038,63.43701367719371,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[5.9133631656834655,37.28989980832542,0.0,0.0,0.0,1.0,1.0],[37.28989980832542,39.61408770778038,890.0,0.0,8.0,1.0,-1.0],[39.61408770778038,63.43701367719371,1860.0,0.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C716" t="n">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>[[5.8700633407018366,32.30276536943349,-1860.0,1.0,8.0,2.0,-1.0],[32.30276536943349,33.504251825284925,-1074.7923,0.0,8.0,0.0,-1.0],[33.504251825284925,37.10871119283924,0.0,0.0,7.0,1.0,-1.0],[37.10871119283924,39.51168410454211,890.0,0.0,7.0,1.0,-1.0],[39.51168410454211,65.34364290534803,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[5.8700633407018366,32.30276536943349,-1860.0,1.0,8.0,2.0,-1.0],[32.30276536943349,33.504251825284925,-1074.7922,0.0,8.0,0.0,-1.0],[33.504251825284925,37.10871119283924,0.0,0.0,7.0,1.0,-1.0],[37.10871119283924,39.51168410454211,890.0,0.0,7.0,1.0,-1.0],[39.51168410454211,65.34364290534803,1860.0,0.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C717" t="n">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>[[5.629739286392475,31.895303771490912,-1860.0,1.0,7.0,0.0,-1.0],[31.895303771490912,35.065285692106244,-1074.7923,0.0,7.0,0.0,-1.0],[35.065285692106244,38.68812217280947,0.0,0.0,6.0,1.0,-1.0],[38.68812217280947,39.593831292985286,890.0,0.0,6.0,1.0,-1.0],[39.593831292985286,50.46234073509498,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[5.629739286392475,31.895303771490912,-1860.0,1.0,7.0,0.0,-1.0],[31.895303771490912,35.065285692106244,-1074.7922,0.0,7.0,0.0,-1.0],[35.065285692106244,38.68812217280947,0.0,0.0,6.0,1.0,-1.0],[38.68812217280947,39.593831292985286,890.0,0.0,6.0,1.0,-1.0],[39.593831292985286,50.46234073509498,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C718" t="n">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>[[6.003789211278378,32.55206763164108,-1860.0,1.0,6.0,0.0,-1.0],[32.55206763164108,35.411112999987836,-1074.7923,0.0,6.0,0.0,-1.0],[35.411112999987836,39.08702847357652,0.0,0.0,5.0,1.0,-1.0],[39.08702847357652,41.12920373668134,890.0,0.0,5.0,1.0,-1.0],[41.12920373668134,46.43885942075388,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[6.003789211278378,32.55206763164108,-1860.0,1.0,6.0,0.0,-1.0],[32.55206763164108,35.411112999987836,-1074.7922,0.0,6.0,0.0,-1.0],[35.411112999987836,39.08702847357652,0.0,0.0,5.0,1.0,-1.0],[39.08702847357652,41.12920373668134,890.0,0.0,5.0,1.0,-1.0],[41.12920373668134,46.43885942075388,1860.0,0.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C719" t="n">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>[[5.538603565668832,31.641517815382105,-1860.0,1.0,6.0,1.0,-1.0],[31.641517815382105,33.19990075566349,-1074.7923,0.0,6.0,1.0,-1.0],[33.19990075566349,36.70626237129662,0.0,0.0,5.0,2.0,-1.0],[36.70626237129662,37.09585810636697,890.0,0.0,5.0,0.0,-1.0],[37.09585810636697,44.10858133763322,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[5.538603565668832,31.641517815382105,-1860.0,1.0,6.0,1.0,-1.0],[31.641517815382105,33.19990075566349,-1074.7922,0.0,6.0,1.0,-1.0],[33.19990075566349,36.70626237129662,0.0,0.0,5.0,2.0,-1.0],[36.70626237129662,37.09585810636697,890.0,0.0,5.0,0.0,-1.0],[37.09585810636697,44.10858133763322,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C720" t="n">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>[[6.075732337210046,31.84029389353122,-1860.0,1.0,5.0,1.0,-1.0],[31.84029389353122,32.58709277922169,-1074.7923,0.0,5.0,0.0,-1.0],[32.58709277922169,35.94768776482881,0.0,0.0,4.0,1.0,-1.0],[35.94768776482881,38.56148386474545,890.0,0.0,4.0,0.0,-1.0],[38.56148386474545,43.04227717888826,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[6.075732337210046,31.84029389353122,-1860.0,1.0,5.0,1.0,-1.0],[31.84029389353122,32.58709277922169,-1074.7922,0.0,5.0,0.0,-1.0],[32.58709277922169,35.94768776482881,0.0,0.0,4.0,1.0,-1.0],[35.94768776482881,38.56148386474545,890.0,0.0,4.0,0.0,-1.0],[38.56148386474545,43.04227717888826,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C721" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>[[6.323637585308626,31.845397912843964,-1860.0,1.0,4.0,0.0,-1.0],[31.845397912843964,32.19986680628195,-1074.7923,0.0,4.0,0.0,-1.0],[32.19986680628195,35.744555740661866,0.0,0.0,3.0,1.0,-1.0],[35.744555740661866,37.87136910128981,890.0,0.0,3.0,0.0,-1.0],[37.87136910128981,41.416058035669714,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[6.323637585308626,31.845397912843964,-1860.0,1.0,4.0,0.0,-1.0],[31.845397912843964,32.19986680628195,-1074.7922,0.0,4.0,0.0,-1.0],[32.19986680628195,35.744555740661866,0.0,0.0,3.0,1.0,-1.0],[35.744555740661866,37.87136910128981,890.0,0.0,3.0,0.0,-1.0],[37.87136910128981,41.416058035669714,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C722" t="n">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>[[5.532599802694209,32.41959273462963,-1860.0,1.0,3.0,0.0,-1.0],[32.41959273462963,32.82089113659882,-1074.7923,0.0,3.0,1.0,-1.0],[32.82089113659882,36.43257675432149,0.0,0.0,2.0,2.0,-1.0],[36.43257675432149,38.840367166136595,890.0,0.0,2.0,0.0,-1.0],[38.840367166136595,45.261141597643565,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[5.532599802694209,32.41959273462963,-1860.0,1.0,3.0,0.0,-1.0],[32.41959273462963,32.82089113659882,-1074.7922,0.0,3.0,1.0,-1.0],[32.82089113659882,36.43257675432149,0.0,0.0,2.0,2.0,-1.0],[36.43257675432149,38.840367166136595,890.0,0.0,2.0,0.0,-1.0],[38.840367166136595,45.261141597643565,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C723" t="n">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>[[5.807691584223856,31.43842393144155,-1860.0,1.0,2.0,1.0,-1.0],[31.43842393144155,31.809883820531663,-1074.7923,0.0,2.0,0.0,-1.0],[31.809883820531663,35.15302282234266,0.0,0.0,1.0,1.0,-1.0],[35.15302282234266,40.724921158694336,890.0,0.0,1.0,0.0,-1.0],[40.724921158694336,42.582220604144894,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[5.807691584223856,31.43842393144155,-1860.0,1.0,2.0,1.0,-1.0],[31.43842393144155,31.809883820531663,-1074.7922,0.0,2.0,0.0,-1.0],[31.809883820531663,35.15302282234266,0.0,0.0,1.0,1.0,-1.0],[35.15302282234266,40.724921158694336,890.0,0.0,1.0,0.0,-1.0],[40.724921158694336,42.582220604144894,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C724" t="n">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>[[5.863834486850254,31.473342677814987,-1860.0,1.0,1.0,0.0,-1.0],[31.473342677814987,33.025434083328,-0.0,0.0,1.0,2.0,-1.0],[33.025434083328,36.51763974573228,0.0,0.0,0.0,2.0,-1.0],[36.51763974573228,37.29368544848879,1860.0,0.0,0.0,0.0,-1.0],[37.29368544848879,44.27809677329735,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[5.863834486850254,31.473342677814987,-1860.0,1.0,1.0,0.0,-1.0],[31.473342677814987,36.51763974573228,0.0,0.0,1.0,2.0,-1.0],[36.51763974573228,44.27809677329735,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C725" t="n">
@@ -9867,11 +9867,11 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>[[6.274995285997301,31.837474971500754,-1860.0,1.0,0.0,1.0,-1.0],[31.837474971500754,41.918452875642956,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[6.274995285997301,31.837474971500754,-1860.0,1.0,0.0,1.0,-1.0],[31.837474971500754,41.918452875642956,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C726" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="727">
@@ -9880,11 +9880,11 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>[[5.722181504183003,31.073599830421916,-1860.0,1.0,0.0,0.0,-1.0],[31.073599830421916,41.576330279863754,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[5.722181504183003,31.073599830421916,-1860.0,1.0,0.0,0.0,-1.0],[31.073599830421916,41.576330279863754,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C727" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="728">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>[[6.08874873479854,28.614641867900705,-1860.0,9.0,0.0,0.0,1.0],[28.614641867900705,28.990073420119074,-1074.7923,9.0,9.0,2.0,-1.0],[28.990073420119074,32.368957390084404,0.0,9.0,8.0,3.0,-1.0],[32.368957390084404,43.25647240441712,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[6.08874873479854,28.614641867900705,-1860.0,8.0,0.0,0.0,1.0],[28.614641867900705,28.990073420119074,-1074.7922,8.0,9.0,2.0,-1.0],[28.990073420119074,32.368957390084404,0.0,8.0,8.0,3.0,-1.0],[32.368957390084404,43.25647240441712,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C730" t="n">
@@ -9932,7 +9932,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>[[6.093610436480207,29.864418878405466,-1860.0,8.0,0.0,0.0,1.0],[29.864418878405466,30.25410426269932,-873.8505,7.0,8.0,1.0,-1.0],[30.25410426269932,33.761272721344035,0.0,7.0,8.0,1.0,-1.0],[33.761272721344035,44.672463481572024,1860.0,8.0,8.0,0.0,-1.0]]</t>
+          <t>[[6.093610436480207,29.864418878405466,-1860.0,7.0,0.0,0.0,1.0],[29.864418878405466,30.25410426269932,-873.8504,7.0,8.0,1.0,-1.0],[30.25410426269932,33.761272721344035,0.0,6.0,8.0,1.0,-1.0],[33.761272721344035,44.672463481572024,1860.0,8.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C731" t="n">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>[[5.940295990748728,29.46027690807245,-1860.0,7.0,0.0,0.0,1.0],[29.46027690807245,30.218985969921604,-873.8505,6.0,8.0,4.0,-1.0],[30.218985969921604,33.25382221731821,0.0,6.0,7.0,5.0,-1.0],[33.25382221731821,33.63317674824279,1071.35,6.0,7.0,5.0,-1.0],[33.63317674824279,43.49639455228177,1860.0,6.0,7.0,5.0,-1.0]]</t>
+          <t>[[5.940295990748728,29.46027690807245,-1860.0,7.0,0.0,0.0,1.0],[29.46027690807245,30.218985969921604,-873.8504,5.0,8.0,4.0,-1.0],[30.218985969921604,33.25382221731821,0.0,6.0,7.0,5.0,-1.0],[33.25382221731821,33.63317674824279,1071.35,6.0,7.0,5.0,-1.0],[33.63317674824279,43.49639455228177,1860.0,5.0,7.0,5.0,-1.0]]</t>
         </is>
       </c>
       <c r="C732" t="n">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>[[5.792876763597392,29.695944878509668,-1860.0,6.0,0.0,0.0,1.0],[29.695944878509668,30.07535865811145,-1074.7923,6.0,9.0,2.0,-1.0],[30.07535865811145,33.11066889492571,0.0,6.0,8.0,3.0,-1.0],[33.11066889492571,33.49008267452749,890.0,6.0,8.0,3.0,-1.0],[33.49008267452749,43.35484094417383,1860.0,6.0,8.0,3.0,-1.0]]</t>
+          <t>[[5.792876763597392,29.695944878509668,-1860.0,5.0,0.0,0.0,1.0],[29.695944878509668,30.07535865811145,-1074.7922,5.0,9.0,2.0,-1.0],[30.07535865811145,33.11066889492571,0.0,6.0,8.0,3.0,-1.0],[33.11066889492571,33.49008267452749,890.0,4.0,8.0,3.0,-1.0],[33.49008267452749,43.35484094417383,1860.0,5.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C733" t="n">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>[[5.920771901706709,29.45730616428769,-1860.0,5.0,0.0,0.0,1.0],[29.45730616428769,32.54406475610159,0.0,4.0,7.0,4.0,-1.0],[32.54406475610159,32.92990958007833,1071.35,4.0,7.0,4.0,-1.0],[32.92990958007833,44.119409475403714,1860.0,4.0,8.0,3.0,-1.0]]</t>
+          <t>[[5.920771901706709,29.45730616428769,-1860.0,4.0,0.0,0.0,1.0],[29.45730616428769,32.54406475610159,0.0,3.0,7.0,4.0,-1.0],[32.54406475610159,32.92990958007833,1071.35,3.0,7.0,4.0,-1.0],[32.92990958007833,44.119409475403714,1860.0,3.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C734" t="n">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>[[5.729929070450166,28.72834939554622,-1860.0,4.0,0.0,0.0,1.0],[28.72834939554622,29.09929165885422,-1074.7923,4.0,9.0,2.0,-1.0],[29.09929165885422,32.437772028626235,0.0,4.0,8.0,3.0,-1.0],[32.437772028626235,42.45321313794226,1860.0,4.0,9.0,2.0,-1.0]]</t>
+          <t>[[5.729929070450166,28.72834939554622,-1860.0,4.0,0.0,0.0,1.0],[28.72834939554622,29.09929165885422,-1074.7922,3.0,9.0,2.0,-1.0],[29.09929165885422,32.437772028626235,0.0,3.0,8.0,3.0,-1.0],[32.437772028626235,42.45321313794226,1860.0,3.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C735" t="n">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>[[6.028534461864241,29.182923856584985,-1860.0,3.0,0.0,0.0,1.0],[29.182923856584985,29.55638175004822,-873.8505,2.0,8.0,3.0,-1.0],[29.55638175004822,32.917502791217366,0.0,2.0,7.0,4.0,-1.0],[32.917502791217366,43.000865914724784,1860.0,2.0,8.0,1.0,-1.0]]</t>
+          <t>[[6.028534461864241,29.182923856584985,-1860.0,2.0,0.0,0.0,1.0],[29.182923856584985,29.55638175004822,-873.8504,2.0,8.0,3.0,-1.0],[29.55638175004822,32.917502791217366,0.0,2.0,7.0,4.0,-1.0],[32.917502791217366,43.000865914724784,1860.0,2.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C736" t="n">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>[[5.904617264301909,28.885789318489433,-1860.0,2.0,0.0,0.0,1.0],[28.885789318489433,30.4438348814852,-873.8505,1.0,8.0,3.0,-1.0],[30.4438348814852,33.559926007476726,0.0,1.0,7.0,4.0,-1.0],[33.559926007476726,44.46624494844708,1860.0,1.0,7.0,4.0,-1.0]]</t>
+          <t>[[5.904617264301909,28.885789318489433,-1860.0,2.0,0.0,0.0,1.0],[28.885789318489433,30.4438348814852,-873.8504,1.0,8.0,3.0,-1.0],[30.4438348814852,33.559926007476726,0.0,1.0,7.0,4.0,-1.0],[33.559926007476726,44.46624494844708,1860.0,1.0,7.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C737" t="n">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>[[5.834823644290232,29.464308432555832,-1860.0,1.0,0.0,0.0,1.0],[29.464308432555832,29.851677035642155,-873.8505,0.0,8.0,4.0,-1.0],[29.851677035642155,32.95062586033272,0.0,0.0,7.0,5.0,-1.0],[32.95062586033272,33.337994463419044,1071.35,0.0,7.0,2.0,-1.0],[33.337994463419044,44.18431534983604,1860.0,0.0,7.0,2.0,-1.0]]</t>
+          <t>[[5.834823644290232,29.464308432555832,-1860.0,1.0,0.0,0.0,1.0],[29.464308432555832,29.851677035642155,-873.8504,0.0,8.0,4.0,-1.0],[29.851677035642155,32.95062586033272,0.0,0.0,7.0,5.0,-1.0],[32.95062586033272,33.337994463419044,1071.35,0.0,7.0,2.0,-1.0],[33.337994463419044,44.18431534983604,1860.0,0.0,7.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C738" t="n">
@@ -10036,7 +10036,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>[[14.603709426006594,31.69296770568061,-0.0,0.0,0.0,1.0,1.0],[31.69296770568061,31.973119480757227,890.0,0.0,8.0,2.0,-1.0],[31.973119480757227,42.338735158592286,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[14.603709426006594,31.69296770568061,0.0,0.0,0.0,1.0,1.0],[31.69296770568061,31.973119480757227,890.0,0.0,8.0,2.0,-1.0],[31.973119480757227,42.338735158592286,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C739" t="n">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>[[14.245771520889912,26.922191625735785,-1860.0,1.0,8.0,3.0,-1.0],[26.922191625735785,28.733108783570913,-1074.7923,0.0,8.0,2.0,-1.0],[28.733108783570913,31.75130404662945,0.0,0.0,8.0,2.0,-1.0],[31.75130404662945,32.35494309924116,708.65,1.0,8.0,1.0,-1.0],[32.35494309924116,44.12590462516947,1860.0,1.0,8.0,1.0,-1.0]]</t>
+          <t>[[14.245771520889912,26.922191625735785,-1860.0,1.0,8.0,3.0,-1.0],[26.922191625735785,28.733108783570913,-1074.7922,0.0,8.0,2.0,-1.0],[28.733108783570913,31.75130404662945,0.0,0.0,8.0,2.0,-1.0],[31.75130404662945,32.35494309924116,708.65,1.0,8.0,1.0,-1.0],[32.35494309924116,44.12590462516947,1860.0,1.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C740" t="n">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>[[13.63758398867611,28.437049312171897,-1860.0,1.0,6.0,3.0,-1.0],[28.437049312171897,28.739079216733035,-1074.7923,0.0,6.0,2.0,-1.0],[28.739079216733035,32.061408166905565,0.0,0.0,5.0,3.0,-1.0],[32.061408166905565,43.53854454022883,1860.0,0.0,5.0,2.0,-1.0]]</t>
+          <t>[[13.63758398867611,28.437049312171897,-1860.0,1.0,6.0,3.0,-1.0],[28.437049312171897,28.739079216733035,-1074.7922,0.0,6.0,2.0,-1.0],[28.739079216733035,32.061408166905565,0.0,0.0,5.0,3.0,-1.0],[32.061408166905565,43.53854454022883,1860.0,0.0,5.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C742" t="n">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>[[15.114865484076022,27.020927533341908,-1860.0,1.0,5.0,1.0,-1.0],[27.020927533341908,28.34382331659367,-1074.7923,0.0,5.0,2.0,-1.0],[28.34382331659367,31.51877319639791,0.0,0.0,5.0,2.0,-1.0],[31.51877319639791,31.783352353048265,708.65,1.0,5.0,1.0,-1.0],[31.783352353048265,41.30820199246097,1860.0,1.0,5.0,1.0,-1.0]]</t>
+          <t>[[15.114865484076022,27.020927533341908,-1860.0,1.0,5.0,1.0,-1.0],[27.020927533341908,28.34382331659367,-1074.7922,0.0,5.0,2.0,-1.0],[28.34382331659367,31.51877319639791,0.0,0.0,5.0,2.0,-1.0],[31.51877319639791,31.783352353048265,708.65,1.0,5.0,1.0,-1.0],[31.783352353048265,41.30820199246097,1860.0,1.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C743" t="n">
@@ -10101,7 +10101,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>[[14.10266160291317,27.256677252821802,-1860.0,1.0,4.0,2.0,-1.0],[27.256677252821802,29.449013194473242,-1074.7923,0.0,4.0,2.0,-1.0],[29.449013194473242,32.46347511424397,0.0,0.0,4.0,2.0,-1.0],[32.46347511424397,33.285601092363265,708.65,1.0,4.0,1.0,-1.0],[33.285601092363265,41.23281888084973,1860.0,1.0,5.0,0.0,-1.0]]</t>
+          <t>[[14.10266160291317,27.256677252821802,-1860.0,1.0,4.0,2.0,-1.0],[27.256677252821802,29.449013194473242,-1074.7922,0.0,4.0,2.0,-1.0],[29.449013194473242,32.46347511424397,0.0,0.0,4.0,2.0,-1.0],[32.46347511424397,33.285601092363265,708.65,1.0,4.0,1.0,-1.0],[33.285601092363265,41.23281888084973,1860.0,1.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C744" t="n">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>[[14.814695644686502,29.37746717540806,-1860.0,1.0,3.0,1.0,-1.0],[29.37746717540806,29.674666594402378,-1074.7923,0.0,3.0,2.0,-1.0],[29.674666594402378,32.94386020333987,0.0,0.0,2.0,3.0,-1.0],[32.94386020333987,44.23743812512394,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[14.814695644686502,29.37746717540806,-1860.0,0.0,3.0,1.0,-1.0],[29.37746717540806,29.674666594402378,-1074.7922,0.0,3.0,2.0,-1.0],[29.674666594402378,32.94386020333987,0.0,0.0,2.0,3.0,-1.0],[32.94386020333987,44.23743812512394,1860.0,0.0,3.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C745" t="n">
